--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApi_document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D1DF87-B0EB-497A-B987-2361882C4EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A38FF6-5D34-4CF4-914B-2F9F09507E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="0" windowWidth="28770" windowHeight="15495" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="1123">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -5063,6 +5063,10 @@
   </si>
   <si>
     <t>monster002</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill033</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -13903,7 +13907,8 @@
     <col min="8" max="8" width="14" style="5" customWidth="1"/>
     <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
     <col min="10" max="12" width="9.875" style="18" customWidth="1"/>
-    <col min="13" max="14" width="12.625" style="18" customWidth="1"/>
+    <col min="13" max="13" width="25.5" style="18" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.625" style="18" customWidth="1"/>
     <col min="15" max="15" width="27.125" style="5" customWidth="1"/>
     <col min="16" max="16" width="7.5" style="5" customWidth="1"/>
     <col min="17" max="17" width="15.125" style="5" customWidth="1"/>
@@ -15378,7 +15383,7 @@
     </row>
     <row r="36" spans="3:17">
       <c r="C36" s="43" t="s">
-        <v>1056</v>
+        <v>1122</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>53</v>

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25A38FF6-5D34-4CF4-914B-2F9F09507E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CD3580-E22F-4820-8EB3-08D1CF5871A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -5114,7 +5114,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5136,12 +5136,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5213,7 +5207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5296,8 +5290,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -10221,7 +10216,7 @@
       <c r="D47" s="47">
         <v>1</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="E47" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F47" s="9">
@@ -10250,7 +10245,7 @@
         <f>D47+1</f>
         <v>2</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="E48" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F48" s="9">
@@ -10272,14 +10267,14 @@
       <c r="B49" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="47">
         <f t="shared" ref="D49:D78" si="5">D48+1</f>
         <v>3</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="E49" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F49" s="9">
@@ -10308,7 +10303,7 @@
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F50" s="9">
@@ -10337,7 +10332,7 @@
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F51" s="9">
@@ -10366,7 +10361,7 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="E52" s="19" t="s">
+      <c r="E52" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F52" s="9">
@@ -10395,7 +10390,7 @@
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="E53" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F53" s="9">
@@ -10424,7 +10419,7 @@
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F54" s="9">
@@ -10453,7 +10448,7 @@
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F55" s="9">
@@ -10482,7 +10477,7 @@
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F56" s="9">
@@ -10504,14 +10499,14 @@
       <c r="B57" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="47">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F57" s="9">
@@ -10533,14 +10528,14 @@
       <c r="B58" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="47">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F58" s="9">
@@ -10562,14 +10557,14 @@
       <c r="B59" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="47">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="E59" s="19" t="s">
+      <c r="E59" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F59" s="9">
@@ -10598,7 +10593,7 @@
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="E60" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F60" s="9">
@@ -10627,7 +10622,7 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="E61" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F61" s="9">
@@ -10649,14 +10644,14 @@
       <c r="B62" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="47">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="E62" s="19" t="s">
+      <c r="E62" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F62" s="9">
@@ -10685,7 +10680,7 @@
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="E63" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F63" s="9">
@@ -10706,14 +10701,14 @@
       <c r="B64" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="47">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="E64" s="19" t="s">
+      <c r="E64" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F64" s="9">
@@ -10734,14 +10729,14 @@
       <c r="B65" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="47" t="s">
         <v>248</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="47">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="E65" s="19" t="s">
+      <c r="E65" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F65" s="9">
@@ -10762,14 +10757,14 @@
       <c r="B66" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="47">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="E66" s="48" t="s">
         <v>125</v>
       </c>
       <c r="F66" s="9">

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CD3580-E22F-4820-8EB3-08D1CF5871A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DABA1D8-FA22-4B02-914F-E0D8C362A598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -5207,7 +5207,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5290,9 +5290,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="パーセント" xfId="1" builtinId="5"/>
@@ -7663,13 +7660,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>165902</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>149436</xdr:rowOff>
+      <xdr:rowOff>145034</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>308885</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>156875</xdr:rowOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>99108</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -7687,8 +7684,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="2887331" y="6340686"/>
-          <a:ext cx="823340" cy="2130153"/>
+          <a:off x="2900137" y="6028122"/>
+          <a:ext cx="826542" cy="2139221"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -8093,7 +8090,7 @@
       <xdr:col>8</xdr:col>
       <xdr:colOff>593280</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>72486</xdr:rowOff>
+      <xdr:rowOff>165311</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
@@ -8117,8 +8114,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="6061751" y="7972633"/>
-          <a:ext cx="4885232" cy="547728"/>
+          <a:off x="6061751" y="8065458"/>
+          <a:ext cx="4885232" cy="454903"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -8146,13 +8143,13 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>308885</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>78923</xdr:rowOff>
+      <xdr:rowOff>78919</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>593280</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>112056</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -8167,10 +8164,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3726679" y="7642894"/>
-          <a:ext cx="2335072" cy="1601960"/>
-          <a:chOff x="3726679" y="7642894"/>
-          <a:chExt cx="2335072" cy="1601960"/>
+          <a:off x="3726679" y="7642890"/>
+          <a:ext cx="2335072" cy="1882107"/>
+          <a:chOff x="3726679" y="7642891"/>
+          <a:chExt cx="2335072" cy="1468663"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
@@ -8186,10 +8183,10 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="3726679" y="7642894"/>
-            <a:ext cx="2238566" cy="1601960"/>
+            <a:off x="3726679" y="7642891"/>
+            <a:ext cx="2238566" cy="1468663"/>
             <a:chOff x="3595464" y="7579840"/>
-            <a:chExt cx="2256175" cy="1641481"/>
+            <a:chExt cx="2256175" cy="1504896"/>
           </a:xfrm>
         </xdr:grpSpPr>
         <xdr:sp macro="" textlink="">
@@ -8206,7 +8203,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="3705886" y="7579840"/>
-              <a:ext cx="2145753" cy="1641481"/>
+              <a:ext cx="2145753" cy="1504896"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8282,7 +8279,7 @@
               <a:pPr algn="l"/>
               <a:r>
                 <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-                <a:t>購入日</a:t>
+                <a:t>個数</a:t>
               </a:r>
               <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
             </a:p>
@@ -10210,13 +10207,13 @@
       <c r="B47" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C47" s="46" t="s">
+      <c r="C47" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="D47" s="47">
+      <c r="D47" s="8">
         <v>1</v>
       </c>
-      <c r="E47" s="48" t="s">
+      <c r="E47" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F47" s="9">
@@ -10238,14 +10235,14 @@
       <c r="B48" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C48" s="46" t="s">
+      <c r="C48" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="D48" s="47">
+      <c r="D48" s="8">
         <f>D47+1</f>
         <v>2</v>
       </c>
-      <c r="E48" s="48" t="s">
+      <c r="E48" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F48" s="9">
@@ -10267,14 +10264,14 @@
       <c r="B49" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C49" s="46" t="s">
+      <c r="C49" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D49" s="47">
+      <c r="D49" s="8">
         <f t="shared" ref="D49:D78" si="5">D48+1</f>
         <v>3</v>
       </c>
-      <c r="E49" s="48" t="s">
+      <c r="E49" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F49" s="9">
@@ -10296,14 +10293,14 @@
       <c r="B50" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C50" s="46" t="s">
+      <c r="C50" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D50" s="47">
+      <c r="D50" s="8">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="E50" s="48" t="s">
+      <c r="E50" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F50" s="9">
@@ -10325,14 +10322,14 @@
       <c r="B51" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C51" s="46" t="s">
+      <c r="C51" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="D51" s="47">
+      <c r="D51" s="8">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="E51" s="48" t="s">
+      <c r="E51" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F51" s="9">
@@ -10354,14 +10351,14 @@
       <c r="B52" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C52" s="46" t="s">
+      <c r="C52" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="47">
+      <c r="D52" s="8">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="E52" s="48" t="s">
+      <c r="E52" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F52" s="9">
@@ -10383,14 +10380,14 @@
       <c r="B53" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C53" s="46" t="s">
+      <c r="C53" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="D53" s="47">
+      <c r="D53" s="8">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="E53" s="48" t="s">
+      <c r="E53" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F53" s="9">
@@ -10412,14 +10409,14 @@
       <c r="B54" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C54" s="46" t="s">
+      <c r="C54" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D54" s="47">
+      <c r="D54" s="8">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="E54" s="48" t="s">
+      <c r="E54" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F54" s="9">
@@ -10441,14 +10438,14 @@
       <c r="B55" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C55" s="46" t="s">
+      <c r="C55" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="D55" s="47">
+      <c r="D55" s="8">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="E55" s="48" t="s">
+      <c r="E55" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F55" s="9">
@@ -10470,14 +10467,14 @@
       <c r="B56" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C56" s="46" t="s">
+      <c r="C56" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D56" s="47">
+      <c r="D56" s="8">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="E56" s="48" t="s">
+      <c r="E56" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F56" s="9">
@@ -10499,14 +10496,14 @@
       <c r="B57" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C57" s="46" t="s">
+      <c r="C57" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="D57" s="47">
+      <c r="D57" s="8">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="E57" s="48" t="s">
+      <c r="E57" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F57" s="9">
@@ -10528,14 +10525,14 @@
       <c r="B58" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C58" s="46" t="s">
+      <c r="C58" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="D58" s="47">
+      <c r="D58" s="8">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="E58" s="48" t="s">
+      <c r="E58" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F58" s="9">
@@ -10557,14 +10554,14 @@
       <c r="B59" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C59" s="46" t="s">
+      <c r="C59" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="D59" s="47">
+      <c r="D59" s="8">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="E59" s="48" t="s">
+      <c r="E59" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F59" s="9">
@@ -10586,14 +10583,14 @@
       <c r="B60" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C60" s="46" t="s">
+      <c r="C60" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="D60" s="47">
+      <c r="D60" s="8">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="E60" s="48" t="s">
+      <c r="E60" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F60" s="9">
@@ -10615,14 +10612,14 @@
       <c r="B61" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C61" s="46" t="s">
+      <c r="C61" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="D61" s="47">
+      <c r="D61" s="8">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="E61" s="48" t="s">
+      <c r="E61" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F61" s="9">
@@ -10644,14 +10641,14 @@
       <c r="B62" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C62" s="46" t="s">
+      <c r="C62" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="D62" s="47">
+      <c r="D62" s="8">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
-      <c r="E62" s="48" t="s">
+      <c r="E62" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F62" s="9">
@@ -10673,14 +10670,14 @@
       <c r="B63" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C63" s="47" t="s">
+      <c r="C63" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="D63" s="47">
+      <c r="D63" s="8">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="E63" s="48" t="s">
+      <c r="E63" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F63" s="9">
@@ -10701,14 +10698,14 @@
       <c r="B64" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C64" s="47" t="s">
+      <c r="C64" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="D64" s="47">
+      <c r="D64" s="8">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F64" s="9">
@@ -10729,14 +10726,14 @@
       <c r="B65" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C65" s="47" t="s">
+      <c r="C65" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="D65" s="47">
+      <c r="D65" s="8">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="E65" s="48" t="s">
+      <c r="E65" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F65" s="9">
@@ -10757,14 +10754,14 @@
       <c r="B66" s="43" t="s">
         <v>532</v>
       </c>
-      <c r="C66" s="47" t="s">
+      <c r="C66" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D66" s="47">
+      <c r="D66" s="8">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="E66" s="48" t="s">
+      <c r="E66" s="19" t="s">
         <v>125</v>
       </c>
       <c r="F66" s="9">

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DABA1D8-FA22-4B02-914F-E0D8C362A598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B65537-0C2C-4288-A354-F799BFE770EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-135" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BE87D7-DD42-48EB-8C54-FFF7CFB47FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C36968-3B0A-44E9-B478-80C6C75D449E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15225" activeTab="7" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3133" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3155" uniqueCount="1144">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -5240,6 +5240,28 @@
     <rPh sb="30" eb="31">
       <t>メイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>code008</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>モンスター能力値</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>設定種類</t>
+    <rPh sb="0" eb="2">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>使用モンスター</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9163,7 +9185,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:K86"/>
+  <dimension ref="B3:K90"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9" style="5"/>
@@ -11340,7 +11362,7 @@
         <v>125</v>
       </c>
       <c r="J80" s="5" t="str">
-        <f t="shared" ref="J80:J86" si="7">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;D80&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;");"</f>
+        <f t="shared" ref="J80:J90" si="7">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;D80&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code007',1,'一般','',0,0.0,'');</v>
       </c>
     </row>
@@ -11504,6 +11526,110 @@
       <c r="J86" s="5" t="str">
         <f t="shared" si="7"/>
         <v>INSERT INTO m_code VALUES ('code007',91,'統括管理者','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10">
+      <c r="B87" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10">
+      <c r="B88" s="43" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D88" s="8">
+        <v>1</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F88" s="9">
+        <v>0</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H88" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J88" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code008',1,'モンスター能力値','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10">
+      <c r="B89" s="43" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D89" s="8">
+        <v>2</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F89" s="9">
+        <v>0</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H89" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J89" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code008',2,'モンスタースキル','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10">
+      <c r="B90" s="43" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D90" s="8">
+        <v>3</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F90" s="9">
+        <v>0</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H90" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J90" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code008',3,'使用モンスター','',0,0.0,'');</v>
       </c>
     </row>
   </sheetData>
@@ -34655,7 +34781,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE71EC6-0DD3-461C-A8FC-74E22154B7A5}">
-  <dimension ref="A4:H14"/>
+  <dimension ref="A4:H13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="3.875" style="1" customWidth="1"/>
@@ -34744,13 +34870,13 @@
         <v>1139</v>
       </c>
     </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="1" t="s">
+        <v>1132</v>
+      </c>
+    </row>
     <row r="13" spans="1:8">
       <c r="B13" s="1" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" s="1" t="s">
         <v>1133</v>
       </c>
     </row>

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A0C9BC-481D-46DD-BE58-2DF696445551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08DD634-B5F8-4EE5-9592-7CC169A5B608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3155" uniqueCount="1144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3155" uniqueCount="1145">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -5266,6 +5266,10 @@
     <rPh sb="35" eb="37">
       <t>サイテイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill044</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -11652,9 +11656,7 @@
   <cols>
     <col min="1" max="2" width="7.5" style="5" customWidth="1"/>
     <col min="3" max="3" width="13.75" style="5" customWidth="1"/>
-    <col min="4" max="4" width="19.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="5.125" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="30.625" style="5" customWidth="1"/>
     <col min="7" max="7" width="11" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.25" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.75" style="5" customWidth="1"/>
@@ -13079,13 +13081,13 @@
         <v>effectskill031.gif</v>
       </c>
       <c r="N34" s="20">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="O34" s="13"/>
       <c r="P34" s="40"/>
       <c r="Q34" s="5" t="str">
         <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C34&amp;"'"&amp;","&amp;"'"&amp;D34&amp;"'"&amp;","&amp;VLOOKUP(F34,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G34,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H34,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I34,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J34&amp;","&amp;K34&amp;","&amp;L34&amp;","&amp;"'"&amp;M34&amp;"'"&amp;","&amp;N34&amp;","&amp;IF(O34="","''","'"&amp;O34&amp;"'")&amp;");"</f>
-        <v>INSERT INTO m_skill VALUES ('skill031','ホーリーバースト',3,5,0,3,50,50,0.0,'effectskill031.gif',1400,'');</v>
+        <v>INSERT INTO m_skill VALUES ('skill031','ホーリーバースト',3,5,0,3,50,50,0.0,'effectskill031.gif',1500,'');</v>
       </c>
     </row>
     <row r="35" spans="3:17">
@@ -13639,7 +13641,7 @@
     </row>
     <row r="47" spans="3:17">
       <c r="C47" s="43" t="s">
-        <v>1074</v>
+        <v>1144</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>76</v>

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08DD634-B5F8-4EE5-9592-7CC169A5B608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC318959-0B1E-498F-A498-E0C4D4894398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3155" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3161" uniqueCount="1146">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -5270,6 +5270,13 @@
   </si>
   <si>
     <t>skill044</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>猛毒</t>
+    <rPh sb="0" eb="2">
+      <t>モウドク</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9196,7 +9203,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:K90"/>
+  <dimension ref="B3:K91"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="9" style="5"/>
@@ -9290,7 +9297,7 @@
       </c>
       <c r="I6" s="18"/>
       <c r="J6" s="5" t="str">
-        <f t="shared" ref="J6:J69" si="1">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;D6&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;");"</f>
+        <f t="shared" ref="J6:J70" si="1">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;D6&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code001',1,'火','',0,0.0,'');</v>
       </c>
     </row>
@@ -9526,7 +9533,7 @@
         <v>79</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" ref="D15:D21" si="2">D14+1</f>
+        <f t="shared" ref="D15:D20" si="2">D14+1</f>
         <v>2</v>
       </c>
       <c r="E15" s="19" t="s">
@@ -9694,7 +9701,7 @@
         <v>74</v>
       </c>
       <c r="D21" s="8">
-        <f t="shared" si="2"/>
+        <f>D20+1</f>
         <v>8</v>
       </c>
       <c r="E21" s="19" t="s">
@@ -9710,72 +9717,71 @@
         <v>143</v>
       </c>
       <c r="J21" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;D21&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code002',8,'オートヒール','',3,0.0,'param2: 継続ターン数');</v>
       </c>
     </row>
     <row r="22" spans="2:10">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="43" t="s">
+        <v>526</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D22" s="8">
+        <f>D21+1</f>
+        <v>9</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="J22" s="5" t="str">
+        <f t="shared" ref="J22" si="3">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;D22&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code002',9,'猛毒','',3,0.0,'param2: 継続ターン数');</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C23" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E23" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I22" s="18"/>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="43" t="s">
-        <v>527</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D23" s="8">
-        <v>0</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="9">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>125</v>
-      </c>
       <c r="I23" s="18"/>
-      <c r="J23" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code003',0,'無','',0,0.0,'');</v>
-      </c>
     </row>
     <row r="24" spans="2:10">
       <c r="B24" s="43" t="s">
         <v>527</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>27</v>
+      <c r="C24" s="9" t="s">
+        <v>134</v>
       </c>
       <c r="D24" s="8">
-        <f>D23+1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>125</v>
@@ -9792,19 +9798,19 @@
       <c r="I24" s="18"/>
       <c r="J24" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code003',1,'敵ランダム','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code003',0,'無','',0,0.0,'');</v>
       </c>
     </row>
     <row r="25" spans="2:10">
       <c r="B25" s="43" t="s">
         <v>527</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>32</v>
+      <c r="C25" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="D25" s="8">
-        <f t="shared" ref="D25:D31" si="3">D24+1</f>
-        <v>2</v>
+        <f>D24+1</f>
+        <v>1</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>125</v>
@@ -9821,7 +9827,7 @@
       <c r="I25" s="18"/>
       <c r="J25" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code003',2,'敵全体','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code003',1,'敵ランダム','',0,0.0,'');</v>
       </c>
     </row>
     <row r="26" spans="2:10">
@@ -9829,11 +9835,11 @@
         <v>527</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" si="3"/>
-        <v>3</v>
+        <f t="shared" ref="D26:D32" si="4">D25+1</f>
+        <v>2</v>
       </c>
       <c r="E26" s="19" t="s">
         <v>125</v>
@@ -9850,7 +9856,7 @@
       <c r="I26" s="18"/>
       <c r="J26" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code003',3,'敵ランダム・敵全体','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code003',2,'敵全体','',0,0.0,'');</v>
       </c>
     </row>
     <row r="27" spans="2:10">
@@ -9858,11 +9864,11 @@
         <v>527</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <f t="shared" si="4"/>
+        <v>3</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>125</v>
@@ -9879,7 +9885,7 @@
       <c r="I27" s="18"/>
       <c r="J27" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code003',4,'敵ランダム・複数回','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code003',3,'敵ランダム・敵全体','',0,0.0,'');</v>
       </c>
     </row>
     <row r="28" spans="2:10">
@@ -9887,11 +9893,11 @@
         <v>527</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>4</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>125</v>
@@ -9908,7 +9914,7 @@
       <c r="I28" s="18"/>
       <c r="J28" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code003',5,'自身','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code003',4,'敵ランダム・複数回','',0,0.0,'');</v>
       </c>
     </row>
     <row r="29" spans="2:10">
@@ -9916,11 +9922,11 @@
         <v>527</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" si="3"/>
-        <v>6</v>
+        <f t="shared" si="4"/>
+        <v>5</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>125</v>
@@ -9937,7 +9943,7 @@
       <c r="I29" s="18"/>
       <c r="J29" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code003',6,'味方ランダム','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code003',5,'自身','',0,0.0,'');</v>
       </c>
     </row>
     <row r="30" spans="2:10">
@@ -9945,11 +9951,11 @@
         <v>527</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D30" s="8">
-        <f t="shared" si="3"/>
-        <v>7</v>
+        <f t="shared" si="4"/>
+        <v>6</v>
       </c>
       <c r="E30" s="19" t="s">
         <v>125</v>
@@ -9966,7 +9972,7 @@
       <c r="I30" s="18"/>
       <c r="J30" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code003',7,'味方全体','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code003',6,'味方ランダム','',0,0.0,'');</v>
       </c>
     </row>
     <row r="31" spans="2:10">
@@ -9974,11 +9980,11 @@
         <v>527</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" si="3"/>
-        <v>8</v>
+        <f t="shared" si="4"/>
+        <v>7</v>
       </c>
       <c r="E31" s="19" t="s">
         <v>125</v>
@@ -9995,71 +10001,71 @@
       <c r="I31" s="18"/>
       <c r="J31" s="5" t="str">
         <f t="shared" si="1"/>
+        <v>INSERT INTO m_code VALUES ('code003',7,'味方全体','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="43" t="s">
+        <v>527</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" s="8">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I32" s="18"/>
+      <c r="J32" s="5" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO m_code VALUES ('code003',8,'味方ランダム・味方全体','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="32" spans="2:10">
-      <c r="B32" s="6" t="s">
+    <row r="33" spans="2:10">
+      <c r="B33" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C33" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F33" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G33" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I32" s="18"/>
-    </row>
-    <row r="33" spans="2:10">
-      <c r="B33" s="43" t="s">
-        <v>528</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="8">
-        <v>0</v>
-      </c>
-      <c r="E33" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F33" s="9">
-        <v>0</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>125</v>
-      </c>
       <c r="I33" s="18"/>
-      <c r="J33" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code004',0,'無','',0,0.0,'');</v>
-      </c>
     </row>
     <row r="34" spans="2:10">
       <c r="B34" s="43" t="s">
         <v>528</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="D34" s="8">
-        <f>D33+1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>125</v>
@@ -10076,7 +10082,7 @@
       <c r="I34" s="18"/>
       <c r="J34" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code004',1,'打撃攻撃','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code004',0,'無','',0,0.0,'');</v>
       </c>
     </row>
     <row r="35" spans="2:10">
@@ -10084,11 +10090,11 @@
         <v>528</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D35" s="8">
-        <f t="shared" ref="D35:D41" si="4">D34+1</f>
-        <v>2</v>
+        <f>D34+1</f>
+        <v>1</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>125</v>
@@ -10105,7 +10111,7 @@
       <c r="I35" s="18"/>
       <c r="J35" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code004',2,'斬撃攻撃','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code004',1,'打撃攻撃','',0,0.0,'');</v>
       </c>
     </row>
     <row r="36" spans="2:10">
@@ -10113,11 +10119,11 @@
         <v>528</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D36" s="8">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f t="shared" ref="D36:D42" si="5">D35+1</f>
+        <v>2</v>
       </c>
       <c r="E36" s="19" t="s">
         <v>125</v>
@@ -10134,19 +10140,19 @@
       <c r="I36" s="18"/>
       <c r="J36" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code004',3,'攻撃魔法','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code004',2,'斬撃攻撃','',0,0.0,'');</v>
       </c>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="43" t="s">
         <v>528</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>150</v>
+      <c r="C37" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="D37" s="8">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="5"/>
+        <v>3</v>
       </c>
       <c r="E37" s="19" t="s">
         <v>125</v>
@@ -10163,7 +10169,7 @@
       <c r="I37" s="18"/>
       <c r="J37" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code004',4,'割合攻撃','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code004',3,'攻撃魔法','',0,0.0,'');</v>
       </c>
     </row>
     <row r="38" spans="2:10">
@@ -10171,11 +10177,11 @@
         <v>528</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D38" s="8">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>4</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>125</v>
@@ -10192,7 +10198,7 @@
       <c r="I38" s="18"/>
       <c r="J38" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code004',5,'即死攻撃','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code004',4,'割合攻撃','',0,0.0,'');</v>
       </c>
     </row>
     <row r="39" spans="2:10">
@@ -10200,11 +10206,11 @@
         <v>528</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="D39" s="8">
-        <f t="shared" si="4"/>
-        <v>6</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>125</v>
@@ -10221,7 +10227,7 @@
       <c r="I39" s="18"/>
       <c r="J39" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code004',6,'回復','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code004',5,'即死攻撃','',0,0.0,'');</v>
       </c>
     </row>
     <row r="40" spans="2:10">
@@ -10229,11 +10235,11 @@
         <v>528</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D40" s="8">
-        <f t="shared" si="4"/>
-        <v>7</v>
+        <f t="shared" si="5"/>
+        <v>6</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>125</v>
@@ -10250,7 +10256,7 @@
       <c r="I40" s="18"/>
       <c r="J40" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code004',7,'状態','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code004',6,'回復','',0,0.0,'');</v>
       </c>
     </row>
     <row r="41" spans="2:10">
@@ -10258,11 +10264,11 @@
         <v>528</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="D41" s="8">
-        <f t="shared" si="4"/>
-        <v>8</v>
+        <f t="shared" si="5"/>
+        <v>7</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>125</v>
@@ -10279,71 +10285,71 @@
       <c r="I41" s="18"/>
       <c r="J41" s="5" t="str">
         <f t="shared" si="1"/>
+        <v>INSERT INTO m_code VALUES ('code004',7,'状態','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="43" t="s">
+        <v>528</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="8">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F42" s="9">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="18"/>
+      <c r="J42" s="5" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO m_code VALUES ('code004',8,'休み','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="42" spans="2:10">
-      <c r="B42" s="6" t="s">
+    <row r="43" spans="2:10">
+      <c r="B43" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D43" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E43" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F43" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G43" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="H43" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I42" s="18"/>
-    </row>
-    <row r="43" spans="2:10">
-      <c r="B43" s="43" t="s">
-        <v>529</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" s="8">
-        <v>1</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F43" s="9">
-        <v>0</v>
-      </c>
-      <c r="G43" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>125</v>
-      </c>
       <c r="I43" s="18"/>
-      <c r="J43" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code005',1,'クリティカルダメージ補正','',0,0.25,'');</v>
-      </c>
     </row>
     <row r="44" spans="2:10">
       <c r="B44" s="43" t="s">
         <v>529</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D44" s="8">
-        <f>D43+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" s="19" t="s">
         <v>125</v>
@@ -10352,7 +10358,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="9">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H44" s="19" t="s">
         <v>125</v>
@@ -10360,7 +10366,7 @@
       <c r="I44" s="18"/>
       <c r="J44" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code005',2,'行動スピード補正','',0,0.3,'');</v>
+        <v>INSERT INTO m_code VALUES ('code005',1,'クリティカルダメージ補正','',0,0.25,'');</v>
       </c>
     </row>
     <row r="45" spans="2:10">
@@ -10368,11 +10374,11 @@
         <v>529</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D45" s="8">
         <f>D44+1</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>125</v>
@@ -10381,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="9">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H45" s="19" t="s">
         <v>125</v>
@@ -10389,71 +10395,71 @@
       <c r="I45" s="18"/>
       <c r="J45" s="5" t="str">
         <f t="shared" si="1"/>
+        <v>INSERT INTO m_code VALUES ('code005',2,'行動スピード補正','',0,0.3,'');</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="43" t="s">
+        <v>529</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="8">
+        <f>D45+1</f>
+        <v>3</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0.15</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="I46" s="18"/>
+      <c r="J46" s="5" t="str">
+        <f t="shared" si="1"/>
         <v>INSERT INTO m_code VALUES ('code005',3,'弱点ダメージ補正','',0,0.15,'');</v>
       </c>
     </row>
-    <row r="46" spans="2:10">
-      <c r="B46" s="6" t="s">
+    <row r="47" spans="2:10">
+      <c r="B47" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C47" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D47" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E47" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F47" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G47" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="H47" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="I46" s="18"/>
-    </row>
-    <row r="47" spans="2:10">
-      <c r="B47" s="43" t="s">
-        <v>530</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D47" s="8">
-        <v>1</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F47" s="9">
-        <v>0</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>125</v>
-      </c>
       <c r="I47" s="18"/>
-      <c r="J47" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',1,'キラービー','',0,0.0,'');</v>
-      </c>
     </row>
     <row r="48" spans="2:10">
       <c r="B48" s="43" t="s">
         <v>530</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D48" s="8">
-        <f>D47+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>125</v>
@@ -10470,7 +10476,7 @@
       <c r="I48" s="18"/>
       <c r="J48" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',2,'カーミラ','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',1,'キラービー','',0,0.0,'');</v>
       </c>
     </row>
     <row r="49" spans="2:10">
@@ -10478,11 +10484,11 @@
         <v>530</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D49" s="8">
-        <f t="shared" ref="D49:D78" si="5">D48+1</f>
-        <v>3</v>
+        <f>D48+1</f>
+        <v>2</v>
       </c>
       <c r="E49" s="19" t="s">
         <v>125</v>
@@ -10499,7 +10505,7 @@
       <c r="I49" s="18"/>
       <c r="J49" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',3,'デーモン','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',2,'カーミラ','',0,0.0,'');</v>
       </c>
     </row>
     <row r="50" spans="2:10">
@@ -10507,11 +10513,11 @@
         <v>530</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="D50" s="8">
-        <f t="shared" si="5"/>
-        <v>4</v>
+        <f t="shared" ref="D50:D79" si="6">D49+1</f>
+        <v>3</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>125</v>
@@ -10528,7 +10534,7 @@
       <c r="I50" s="18"/>
       <c r="J50" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',4,'ゴブリン','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',3,'デーモン','',0,0.0,'');</v>
       </c>
     </row>
     <row r="51" spans="2:10">
@@ -10536,11 +10542,11 @@
         <v>530</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>203</v>
+        <v>101</v>
       </c>
       <c r="D51" s="8">
-        <f t="shared" si="5"/>
-        <v>5</v>
+        <f t="shared" si="6"/>
+        <v>4</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>125</v>
@@ -10557,7 +10563,7 @@
       <c r="I51" s="18"/>
       <c r="J51" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',5,'マシンゴーレム','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',4,'ゴブリン','',0,0.0,'');</v>
       </c>
     </row>
     <row r="52" spans="2:10">
@@ -10565,11 +10571,11 @@
         <v>530</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="D52" s="8">
-        <f t="shared" si="5"/>
-        <v>6</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>125</v>
@@ -10586,7 +10592,7 @@
       <c r="I52" s="18"/>
       <c r="J52" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',6,'ハーピー','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',5,'マシンゴーレム','',0,0.0,'');</v>
       </c>
     </row>
     <row r="53" spans="2:10">
@@ -10594,11 +10600,11 @@
         <v>530</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="D53" s="8">
-        <f t="shared" si="5"/>
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>6</v>
       </c>
       <c r="E53" s="19" t="s">
         <v>125</v>
@@ -10615,7 +10621,7 @@
       <c r="I53" s="18"/>
       <c r="J53" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',7,'アーマーナイト','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',6,'ハーピー','',0,0.0,'');</v>
       </c>
     </row>
     <row r="54" spans="2:10">
@@ -10623,11 +10629,11 @@
         <v>530</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>102</v>
+        <v>206</v>
       </c>
       <c r="D54" s="8">
-        <f t="shared" si="5"/>
-        <v>8</v>
+        <f t="shared" si="6"/>
+        <v>7</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>125</v>
@@ -10644,7 +10650,7 @@
       <c r="I54" s="18"/>
       <c r="J54" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',8,'マジシャン','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',7,'アーマーナイト','',0,0.0,'');</v>
       </c>
     </row>
     <row r="55" spans="2:10">
@@ -10652,11 +10658,11 @@
         <v>530</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="D55" s="8">
-        <f t="shared" si="5"/>
-        <v>9</v>
+        <f t="shared" si="6"/>
+        <v>8</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>125</v>
@@ -10673,7 +10679,7 @@
       <c r="I55" s="18"/>
       <c r="J55" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',9,'マイコニド','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',8,'マジシャン','',0,0.0,'');</v>
       </c>
     </row>
     <row r="56" spans="2:10">
@@ -10681,11 +10687,11 @@
         <v>530</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D56" s="8">
-        <f t="shared" si="5"/>
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>9</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>125</v>
@@ -10702,7 +10708,7 @@
       <c r="I56" s="18"/>
       <c r="J56" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',10,'ニードルバード','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',9,'マイコニド','',0,0.0,'');</v>
       </c>
     </row>
     <row r="57" spans="2:10">
@@ -10710,11 +10716,11 @@
         <v>530</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D57" s="8">
-        <f t="shared" si="5"/>
-        <v>11</v>
+        <f t="shared" si="6"/>
+        <v>10</v>
       </c>
       <c r="E57" s="19" t="s">
         <v>125</v>
@@ -10731,7 +10737,7 @@
       <c r="I57" s="18"/>
       <c r="J57" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',11,'プチドラゴン','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',10,'ニードルバード','',0,0.0,'');</v>
       </c>
     </row>
     <row r="58" spans="2:10">
@@ -10739,11 +10745,11 @@
         <v>530</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D58" s="8">
-        <f t="shared" si="5"/>
-        <v>12</v>
+        <f t="shared" si="6"/>
+        <v>11</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>125</v>
@@ -10760,7 +10766,7 @@
       <c r="I58" s="18"/>
       <c r="J58" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',12,'ポト','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',11,'プチドラゴン','',0,0.0,'');</v>
       </c>
     </row>
     <row r="59" spans="2:10">
@@ -10768,11 +10774,11 @@
         <v>530</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D59" s="8">
-        <f t="shared" si="5"/>
-        <v>13</v>
+        <f t="shared" si="6"/>
+        <v>12</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>125</v>
@@ -10789,7 +10795,7 @@
       <c r="I59" s="18"/>
       <c r="J59" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',13,'プリースト','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',12,'ポト','',0,0.0,'');</v>
       </c>
     </row>
     <row r="60" spans="2:10">
@@ -10797,11 +10803,11 @@
         <v>530</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D60" s="8">
-        <f t="shared" si="5"/>
-        <v>14</v>
+        <f t="shared" si="6"/>
+        <v>13</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>125</v>
@@ -10818,7 +10824,7 @@
       <c r="I60" s="18"/>
       <c r="J60" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',14,'ラビ','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',13,'プリースト','',0,0.0,'');</v>
       </c>
     </row>
     <row r="61" spans="2:10">
@@ -10826,11 +10832,11 @@
         <v>530</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="D61" s="8">
-        <f t="shared" si="5"/>
-        <v>15</v>
+        <f t="shared" si="6"/>
+        <v>14</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>125</v>
@@ -10847,7 +10853,7 @@
       <c r="I61" s="18"/>
       <c r="J61" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',15,'グリーンスライム','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',14,'ラビ','',0,0.0,'');</v>
       </c>
     </row>
     <row r="62" spans="2:10">
@@ -10855,11 +10861,11 @@
         <v>530</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D62" s="8">
-        <f t="shared" si="5"/>
-        <v>16</v>
+        <f t="shared" si="6"/>
+        <v>15</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>125</v>
@@ -10876,19 +10882,19 @@
       <c r="I62" s="18"/>
       <c r="J62" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',16,'イビルソード','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',15,'グリーンスライム','',0,0.0,'');</v>
       </c>
     </row>
     <row r="63" spans="2:10">
       <c r="B63" s="43" t="s">
         <v>530</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>279</v>
+      <c r="C63" s="9" t="s">
+        <v>196</v>
       </c>
       <c r="D63" s="8">
-        <f t="shared" si="5"/>
-        <v>17</v>
+        <f t="shared" si="6"/>
+        <v>16</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>125</v>
@@ -10902,9 +10908,10 @@
       <c r="H63" s="19" t="s">
         <v>125</v>
       </c>
+      <c r="I63" s="18"/>
       <c r="J63" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',17,'ウルフ','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',16,'イビルソード','',0,0.0,'');</v>
       </c>
     </row>
     <row r="64" spans="2:10">
@@ -10912,11 +10919,11 @@
         <v>530</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D64" s="8">
-        <f t="shared" si="5"/>
-        <v>18</v>
+        <f t="shared" si="6"/>
+        <v>17</v>
       </c>
       <c r="E64" s="19" t="s">
         <v>125</v>
@@ -10932,7 +10939,7 @@
       </c>
       <c r="J64" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',18,'ダック','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',17,'ウルフ','',0,0.0,'');</v>
       </c>
     </row>
     <row r="65" spans="2:10">
@@ -10940,11 +10947,11 @@
         <v>530</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="D65" s="8">
-        <f t="shared" si="5"/>
-        <v>19</v>
+        <f t="shared" si="6"/>
+        <v>18</v>
       </c>
       <c r="E65" s="19" t="s">
         <v>125</v>
@@ -10960,7 +10967,7 @@
       </c>
       <c r="J65" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',19,'モールベア','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',18,'ダック','',0,0.0,'');</v>
       </c>
     </row>
     <row r="66" spans="2:10">
@@ -10968,11 +10975,11 @@
         <v>530</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="D66" s="8">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="E66" s="19" t="s">
         <v>125</v>
@@ -10988,7 +10995,7 @@
       </c>
       <c r="J66" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',20,'ギャルビー','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',19,'モールベア','',0,0.0,'');</v>
       </c>
     </row>
     <row r="67" spans="2:10">
@@ -10996,11 +11003,11 @@
         <v>530</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="D67" s="8">
-        <f t="shared" si="5"/>
-        <v>21</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="E67" s="19" t="s">
         <v>125</v>
@@ -11016,7 +11023,7 @@
       </c>
       <c r="J67" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',21,'サハギン','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',20,'ギャルビー','',0,0.0,'');</v>
       </c>
     </row>
     <row r="68" spans="2:10">
@@ -11024,11 +11031,11 @@
         <v>530</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="D68" s="8">
-        <f t="shared" si="5"/>
-        <v>22</v>
+        <f t="shared" si="6"/>
+        <v>21</v>
       </c>
       <c r="E68" s="19" t="s">
         <v>125</v>
@@ -11044,7 +11051,7 @@
       </c>
       <c r="J68" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',22,'クロウラー','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',21,'サハギン','',0,0.0,'');</v>
       </c>
     </row>
     <row r="69" spans="2:10">
@@ -11052,11 +11059,11 @@
         <v>530</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>292</v>
+        <v>209</v>
       </c>
       <c r="D69" s="8">
-        <f t="shared" si="5"/>
-        <v>23</v>
+        <f t="shared" si="6"/>
+        <v>22</v>
       </c>
       <c r="E69" s="19" t="s">
         <v>125</v>
@@ -11072,7 +11079,7 @@
       </c>
       <c r="J69" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_code VALUES ('code006',23,'パックン','',0,0.0,'');</v>
+        <v>INSERT INTO m_code VALUES ('code006',22,'クロウラー','',0,0.0,'');</v>
       </c>
     </row>
     <row r="70" spans="2:10">
@@ -11080,11 +11087,11 @@
         <v>530</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="D70" s="8">
-        <f t="shared" si="5"/>
-        <v>24</v>
+        <f t="shared" si="6"/>
+        <v>23</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>125</v>
@@ -11099,8 +11106,8 @@
         <v>125</v>
       </c>
       <c r="J70" s="5" t="str">
-        <f t="shared" ref="J70:J78" si="6">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;D70&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code006',24,'チビデビル','',0,0.0,'');</v>
+        <f t="shared" si="1"/>
+        <v>INSERT INTO m_code VALUES ('code006',23,'パックン','',0,0.0,'');</v>
       </c>
     </row>
     <row r="71" spans="2:10">
@@ -11108,11 +11115,11 @@
         <v>530</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D71" s="8">
-        <f t="shared" si="5"/>
-        <v>25</v>
+        <f t="shared" si="6"/>
+        <v>24</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>125</v>
@@ -11127,8 +11134,8 @@
         <v>125</v>
       </c>
       <c r="J71" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>INSERT INTO m_code VALUES ('code006',25,'オーガボックス','',0,0.0,'');</v>
+        <f t="shared" ref="J71:J79" si="7">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;D71&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code006',24,'チビデビル','',0,0.0,'');</v>
       </c>
     </row>
     <row r="72" spans="2:10">
@@ -11136,11 +11143,11 @@
         <v>530</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D72" s="8">
-        <f t="shared" si="5"/>
-        <v>26</v>
+        <f t="shared" si="6"/>
+        <v>25</v>
       </c>
       <c r="E72" s="19" t="s">
         <v>125</v>
@@ -11155,8 +11162,8 @@
         <v>125</v>
       </c>
       <c r="J72" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>INSERT INTO m_code VALUES ('code006',26,'バレッテ','',0,0.0,'');</v>
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code006',25,'オーガボックス','',0,0.0,'');</v>
       </c>
     </row>
     <row r="73" spans="2:10">
@@ -11164,11 +11171,11 @@
         <v>530</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D73" s="8">
-        <f t="shared" si="5"/>
-        <v>27</v>
+        <f t="shared" si="6"/>
+        <v>26</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>125</v>
@@ -11183,8 +11190,8 @@
         <v>125</v>
       </c>
       <c r="J73" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>INSERT INTO m_code VALUES ('code006',27,'バシリスク','',0,0.0,'');</v>
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code006',26,'バレッテ','',0,0.0,'');</v>
       </c>
     </row>
     <row r="74" spans="2:10">
@@ -11192,11 +11199,11 @@
         <v>530</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D74" s="8">
-        <f t="shared" si="5"/>
-        <v>28</v>
+        <f t="shared" si="6"/>
+        <v>27</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>125</v>
@@ -11211,8 +11218,8 @@
         <v>125</v>
       </c>
       <c r="J74" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>INSERT INTO m_code VALUES ('code006',28,'スペクター','',0,0.0,'');</v>
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code006',27,'バシリスク','',0,0.0,'');</v>
       </c>
     </row>
     <row r="75" spans="2:10">
@@ -11220,11 +11227,11 @@
         <v>530</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D75" s="8">
-        <f t="shared" si="5"/>
-        <v>29</v>
+        <f t="shared" si="6"/>
+        <v>28</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>125</v>
@@ -11239,8 +11246,8 @@
         <v>125</v>
       </c>
       <c r="J75" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>INSERT INTO m_code VALUES ('code006',29,'ユニコーンヘッド','',0,0.0,'');</v>
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code006',28,'スペクター','',0,0.0,'');</v>
       </c>
     </row>
     <row r="76" spans="2:10">
@@ -11248,11 +11255,11 @@
         <v>530</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>211</v>
+        <v>265</v>
       </c>
       <c r="D76" s="8">
-        <f t="shared" si="5"/>
-        <v>30</v>
+        <f t="shared" si="6"/>
+        <v>29</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>125</v>
@@ -11267,8 +11274,8 @@
         <v>125</v>
       </c>
       <c r="J76" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>INSERT INTO m_code VALUES ('code006',30,'シェイプシフター','',0,0.0,'');</v>
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code006',29,'ユニコーンヘッド','',0,0.0,'');</v>
       </c>
     </row>
     <row r="77" spans="2:10">
@@ -11276,11 +11283,11 @@
         <v>530</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D77" s="8">
-        <f t="shared" si="5"/>
-        <v>31</v>
+        <f t="shared" si="6"/>
+        <v>30</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>125</v>
@@ -11295,8 +11302,8 @@
         <v>125</v>
       </c>
       <c r="J77" s="5" t="str">
-        <f t="shared" si="6"/>
-        <v>INSERT INTO m_code VALUES ('code006',31,'ボルダー','',0,0.0,'');</v>
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code006',30,'シェイプシフター','',0,0.0,'');</v>
       </c>
     </row>
     <row r="78" spans="2:10">
@@ -11304,11 +11311,11 @@
         <v>530</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>297</v>
+        <v>213</v>
       </c>
       <c r="D78" s="8">
-        <f t="shared" si="5"/>
-        <v>32</v>
+        <f t="shared" si="6"/>
+        <v>31</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>125</v>
@@ -11323,58 +11330,59 @@
         <v>125</v>
       </c>
       <c r="J78" s="5" t="str">
+        <f t="shared" si="7"/>
+        <v>INSERT INTO m_code VALUES ('code006',31,'ボルダー','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10">
+      <c r="B79" s="43" t="s">
+        <v>530</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D79" s="8">
         <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F79" s="9">
+        <v>0</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H79" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J79" s="5" t="str">
+        <f t="shared" si="7"/>
         <v>INSERT INTO m_code VALUES ('code006',32,'パンプキンボム','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="79" spans="2:10">
-      <c r="B79" s="6" t="s">
+    <row r="80" spans="2:10">
+      <c r="B80" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C80" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D80" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E79" s="6" t="s">
+      <c r="E80" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F80" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G79" s="6" t="s">
+      <c r="G80" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H79" s="6" t="s">
+      <c r="H80" s="6" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10">
-      <c r="B80" s="43" t="s">
-        <v>531</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="D80" s="8">
-        <v>1</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F80" s="9">
-        <v>0</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="H80" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="J80" s="5" t="str">
-        <f t="shared" ref="J80:J90" si="7">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;D80&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code007',1,'一般','',0,0.0,'');</v>
       </c>
     </row>
     <row r="81" spans="2:10">
@@ -11382,10 +11390,10 @@
         <v>531</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D81" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" s="19" t="s">
         <v>125</v>
@@ -11400,8 +11408,8 @@
         <v>125</v>
       </c>
       <c r="J81" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>INSERT INTO m_code VALUES ('code007',2,'優良','',0,0.0,'');</v>
+        <f t="shared" ref="J81:J91" si="8">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;D81&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;");"</f>
+        <v>INSERT INTO m_code VALUES ('code007',1,'一般','',0,0.0,'');</v>
       </c>
     </row>
     <row r="82" spans="2:10">
@@ -11409,10 +11417,10 @@
         <v>531</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D82" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>125</v>
@@ -11427,8 +11435,8 @@
         <v>125</v>
       </c>
       <c r="J82" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>INSERT INTO m_code VALUES ('code007',3,'カモ','',0,0.0,'');</v>
+        <f t="shared" si="8"/>
+        <v>INSERT INTO m_code VALUES ('code007',2,'優良','',0,0.0,'');</v>
       </c>
     </row>
     <row r="83" spans="2:10">
@@ -11436,10 +11444,10 @@
         <v>531</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D83" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E83" s="19" t="s">
         <v>125</v>
@@ -11454,8 +11462,8 @@
         <v>125</v>
       </c>
       <c r="J83" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>INSERT INTO m_code VALUES ('code007',4,'要注意','',0,0.0,'');</v>
+        <f t="shared" si="8"/>
+        <v>INSERT INTO m_code VALUES ('code007',3,'カモ','',0,0.0,'');</v>
       </c>
     </row>
     <row r="84" spans="2:10">
@@ -11463,10 +11471,10 @@
         <v>531</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D84" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E84" s="19" t="s">
         <v>125</v>
@@ -11481,8 +11489,8 @@
         <v>125</v>
       </c>
       <c r="J84" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>INSERT INTO m_code VALUES ('code007',5,'ブラックリスト','',0,0.0,'');</v>
+        <f t="shared" si="8"/>
+        <v>INSERT INTO m_code VALUES ('code007',4,'要注意','',0,0.0,'');</v>
       </c>
     </row>
     <row r="85" spans="2:10">
@@ -11490,10 +11498,10 @@
         <v>531</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D85" s="8">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="E85" s="19" t="s">
         <v>125</v>
@@ -11508,8 +11516,8 @@
         <v>125</v>
       </c>
       <c r="J85" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>INSERT INTO m_code VALUES ('code007',90,'管理者','',0,0.0,'');</v>
+        <f t="shared" si="8"/>
+        <v>INSERT INTO m_code VALUES ('code007',5,'ブラックリスト','',0,0.0,'');</v>
       </c>
     </row>
     <row r="86" spans="2:10">
@@ -11517,10 +11525,10 @@
         <v>531</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D86" s="8">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E86" s="19" t="s">
         <v>125</v>
@@ -11535,58 +11543,58 @@
         <v>125</v>
       </c>
       <c r="J86" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>INSERT INTO m_code VALUES ('code007',90,'管理者','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10">
+      <c r="B87" s="43" t="s">
+        <v>531</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="D87" s="8">
+        <v>91</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F87" s="9">
+        <v>0</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H87" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J87" s="5" t="str">
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code007',91,'統括管理者','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="87" spans="2:10">
-      <c r="B87" s="6" t="s">
+    <row r="88" spans="2:10">
+      <c r="B88" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C88" s="6" t="s">
         <v>1141</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D88" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E87" s="6" t="s">
+      <c r="E88" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F87" s="6" t="s">
+      <c r="F88" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="G87" s="6" t="s">
+      <c r="G88" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H87" s="6" t="s">
+      <c r="H88" s="6" t="s">
         <v>126</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10">
-      <c r="B88" s="43" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D88" s="8">
-        <v>1</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F88" s="9">
-        <v>0</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="H88" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="J88" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>INSERT INTO m_code VALUES ('code008',1,'モンスター能力値','',0,0.0,'');</v>
       </c>
     </row>
     <row r="89" spans="2:10">
@@ -11594,10 +11602,10 @@
         <v>1139</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>1129</v>
+        <v>1140</v>
       </c>
       <c r="D89" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="19" t="s">
         <v>125</v>
@@ -11612,8 +11620,8 @@
         <v>125</v>
       </c>
       <c r="J89" s="5" t="str">
-        <f t="shared" si="7"/>
-        <v>INSERT INTO m_code VALUES ('code008',2,'モンスタースキル','',0,0.0,'');</v>
+        <f t="shared" si="8"/>
+        <v>INSERT INTO m_code VALUES ('code008',1,'モンスター能力値','',0,0.0,'');</v>
       </c>
     </row>
     <row r="90" spans="2:10">
@@ -11621,10 +11629,10 @@
         <v>1139</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
       <c r="D90" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E90" s="19" t="s">
         <v>125</v>
@@ -11639,7 +11647,34 @@
         <v>125</v>
       </c>
       <c r="J90" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
+        <v>INSERT INTO m_code VALUES ('code008',2,'モンスタースキル','',0,0.0,'');</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10">
+      <c r="B91" s="43" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D91" s="8">
+        <v>3</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F91" s="9">
+        <v>0</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H91" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="J91" s="5" t="str">
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code008',3,'使用モンスター','',0,0.0,'');</v>
       </c>
     </row>
@@ -11748,7 +11783,7 @@
       <c r="O4" s="13"/>
       <c r="P4" s="40"/>
       <c r="Q4" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C4&amp;"'"&amp;","&amp;"'"&amp;D4&amp;"'"&amp;","&amp;VLOOKUP(F4,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G4,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H4,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I4,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J4&amp;","&amp;K4&amp;","&amp;L4&amp;","&amp;"'"&amp;M4&amp;"'"&amp;","&amp;N4&amp;","&amp;IF(O4="","''","'"&amp;O4&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C4&amp;"'"&amp;","&amp;"'"&amp;D4&amp;"'"&amp;","&amp;VLOOKUP(F4,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G4,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H4,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I4,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J4&amp;","&amp;K4&amp;","&amp;L4&amp;","&amp;"'"&amp;M4&amp;"'"&amp;","&amp;N4&amp;","&amp;IF(O4="","''","'"&amp;O4&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill001','打撃',1,0,0,1,10,10,0.1,'effectskill001.gif',1000,'');</v>
       </c>
     </row>
@@ -11790,7 +11825,7 @@
       <c r="O5" s="13"/>
       <c r="P5" s="40"/>
       <c r="Q5" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C5&amp;"'"&amp;","&amp;"'"&amp;D5&amp;"'"&amp;","&amp;VLOOKUP(F5,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G5,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H5,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I5,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J5&amp;","&amp;K5&amp;","&amp;L5&amp;","&amp;"'"&amp;M5&amp;"'"&amp;","&amp;N5&amp;","&amp;IF(O5="","''","'"&amp;O5&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C5&amp;"'"&amp;","&amp;"'"&amp;D5&amp;"'"&amp;","&amp;VLOOKUP(F5,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G5,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H5,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I5,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J5&amp;","&amp;K5&amp;","&amp;L5&amp;","&amp;"'"&amp;M5&amp;"'"&amp;","&amp;N5&amp;","&amp;IF(O5="","''","'"&amp;O5&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill002','正拳突き',1,0,0,1,20,20,0.1,'effectskill002.gif',550,'');</v>
       </c>
     </row>
@@ -11835,7 +11870,7 @@
       <c r="O6" s="13"/>
       <c r="P6" s="40"/>
       <c r="Q6" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C6&amp;"'"&amp;","&amp;"'"&amp;D6&amp;"'"&amp;","&amp;VLOOKUP(F6,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G6,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H6,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I6,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J6&amp;","&amp;K6&amp;","&amp;L6&amp;","&amp;"'"&amp;M6&amp;"'"&amp;","&amp;N6&amp;","&amp;IF(O6="","''","'"&amp;O6&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C6&amp;"'"&amp;","&amp;"'"&amp;D6&amp;"'"&amp;","&amp;VLOOKUP(F6,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G6,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H6,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I6,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J6&amp;","&amp;K6&amp;","&amp;L6&amp;","&amp;"'"&amp;M6&amp;"'"&amp;","&amp;N6&amp;","&amp;IF(O6="","''","'"&amp;O6&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill003','ライジングドラゴン',1,0,0,1,30,30,0.1,'effectskill003.gif',700,'');</v>
       </c>
     </row>
@@ -11880,7 +11915,7 @@
       <c r="O7" s="13"/>
       <c r="P7" s="40"/>
       <c r="Q7" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C7&amp;"'"&amp;","&amp;"'"&amp;D7&amp;"'"&amp;","&amp;VLOOKUP(F7,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G7,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H7,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I7,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J7&amp;","&amp;K7&amp;","&amp;L7&amp;","&amp;"'"&amp;M7&amp;"'"&amp;","&amp;N7&amp;","&amp;IF(O7="","''","'"&amp;O7&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C7&amp;"'"&amp;","&amp;"'"&amp;D7&amp;"'"&amp;","&amp;VLOOKUP(F7,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G7,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H7,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I7,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J7&amp;","&amp;K7&amp;","&amp;L7&amp;","&amp;"'"&amp;M7&amp;"'"&amp;","&amp;N7&amp;","&amp;IF(O7="","''","'"&amp;O7&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill004','リアルインパクト',1,0,0,1,50,50,0.1,'effectskill004.gif',900,'');</v>
       </c>
     </row>
@@ -11922,7 +11957,7 @@
       <c r="O8" s="13"/>
       <c r="P8" s="40"/>
       <c r="Q8" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C8&amp;"'"&amp;","&amp;"'"&amp;D8&amp;"'"&amp;","&amp;VLOOKUP(F8,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G8,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H8,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I8,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J8&amp;","&amp;K8&amp;","&amp;L8&amp;","&amp;"'"&amp;M8&amp;"'"&amp;","&amp;N8&amp;","&amp;IF(O8="","''","'"&amp;O8&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C8&amp;"'"&amp;","&amp;"'"&amp;D8&amp;"'"&amp;","&amp;VLOOKUP(F8,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G8,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H8,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I8,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J8&amp;","&amp;K8&amp;","&amp;L8&amp;","&amp;"'"&amp;M8&amp;"'"&amp;","&amp;N8&amp;","&amp;IF(O8="","''","'"&amp;O8&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill005','回し蹴り',1,0,0,2,15,15,0.1,'effectskill005.gif',1000,'');</v>
       </c>
     </row>
@@ -11967,7 +12002,7 @@
       <c r="O9" s="13"/>
       <c r="P9" s="40"/>
       <c r="Q9" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C9&amp;"'"&amp;","&amp;"'"&amp;D9&amp;"'"&amp;","&amp;VLOOKUP(F9,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G9,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H9,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I9,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J9&amp;","&amp;K9&amp;","&amp;L9&amp;","&amp;"'"&amp;M9&amp;"'"&amp;","&amp;N9&amp;","&amp;IF(O9="","''","'"&amp;O9&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C9&amp;"'"&amp;","&amp;"'"&amp;D9&amp;"'"&amp;","&amp;VLOOKUP(F9,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G9,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H9,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I9,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J9&amp;","&amp;K9&amp;","&amp;L9&amp;","&amp;"'"&amp;M9&amp;"'"&amp;","&amp;N9&amp;","&amp;IF(O9="","''","'"&amp;O9&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill006','ムーンサルト',1,0,0,2,25,25,0.1,'effectskill006.gif',1000,'');</v>
       </c>
     </row>
@@ -12012,7 +12047,7 @@
       <c r="O10" s="13"/>
       <c r="P10" s="40"/>
       <c r="Q10" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C10&amp;"'"&amp;","&amp;"'"&amp;D10&amp;"'"&amp;","&amp;VLOOKUP(F10,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G10,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H10,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I10,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J10&amp;","&amp;K10&amp;","&amp;L10&amp;","&amp;"'"&amp;M10&amp;"'"&amp;","&amp;N10&amp;","&amp;IF(O10="","''","'"&amp;O10&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C10&amp;"'"&amp;","&amp;"'"&amp;D10&amp;"'"&amp;","&amp;VLOOKUP(F10,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G10,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H10,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I10,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J10&amp;","&amp;K10&amp;","&amp;L10&amp;","&amp;"'"&amp;M10&amp;"'"&amp;","&amp;N10&amp;","&amp;IF(O10="","''","'"&amp;O10&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill007','ダンスマカブル',1,0,0,2,35,35,0.1,'effectskill007.gif',1000,'');</v>
       </c>
     </row>
@@ -12057,7 +12092,7 @@
       <c r="O11" s="13"/>
       <c r="P11" s="40"/>
       <c r="Q11" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C11&amp;"'"&amp;","&amp;"'"&amp;D11&amp;"'"&amp;","&amp;VLOOKUP(F11,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G11,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H11,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I11,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J11&amp;","&amp;K11&amp;","&amp;L11&amp;","&amp;"'"&amp;M11&amp;"'"&amp;","&amp;N11&amp;","&amp;IF(O11="","''","'"&amp;O11&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C11&amp;"'"&amp;","&amp;"'"&amp;D11&amp;"'"&amp;","&amp;VLOOKUP(F11,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G11,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H11,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I11,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J11&amp;","&amp;K11&amp;","&amp;L11&amp;","&amp;"'"&amp;M11&amp;"'"&amp;","&amp;N11&amp;","&amp;IF(O11="","''","'"&amp;O11&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill008','クレイジーダンス',1,0,0,2,45,45,0.1,'effectskill008.gif',1000,'');</v>
       </c>
     </row>
@@ -12099,7 +12134,7 @@
       <c r="O12" s="13"/>
       <c r="P12" s="40"/>
       <c r="Q12" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C12&amp;"'"&amp;","&amp;"'"&amp;D12&amp;"'"&amp;","&amp;VLOOKUP(F12,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G12,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H12,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I12,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J12&amp;","&amp;K12&amp;","&amp;L12&amp;","&amp;"'"&amp;M12&amp;"'"&amp;","&amp;N12&amp;","&amp;IF(O12="","''","'"&amp;O12&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C12&amp;"'"&amp;","&amp;"'"&amp;D12&amp;"'"&amp;","&amp;VLOOKUP(F12,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G12,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H12,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I12,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J12&amp;","&amp;K12&amp;","&amp;L12&amp;","&amp;"'"&amp;M12&amp;"'"&amp;","&amp;N12&amp;","&amp;IF(O12="","''","'"&amp;O12&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill009','斬撃',2,0,0,1,10,10,0.1,'effectskill009.gif',600,'');</v>
       </c>
     </row>
@@ -12144,7 +12179,7 @@
       <c r="O13" s="13"/>
       <c r="P13" s="40"/>
       <c r="Q13" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C13&amp;"'"&amp;","&amp;"'"&amp;D13&amp;"'"&amp;","&amp;VLOOKUP(F13,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G13,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H13,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I13,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J13&amp;","&amp;K13&amp;","&amp;L13&amp;","&amp;"'"&amp;M13&amp;"'"&amp;","&amp;N13&amp;","&amp;IF(O13="","''","'"&amp;O13&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C13&amp;"'"&amp;","&amp;"'"&amp;D13&amp;"'"&amp;","&amp;VLOOKUP(F13,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G13,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H13,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I13,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J13&amp;","&amp;K13&amp;","&amp;L13&amp;","&amp;"'"&amp;M13&amp;"'"&amp;","&amp;N13&amp;","&amp;IF(O13="","''","'"&amp;O13&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill010','剣の舞',2,0,0,1,20,20,0.1,'effectskill010.gif',600,'');</v>
       </c>
     </row>
@@ -12189,7 +12224,7 @@
       <c r="O14" s="13"/>
       <c r="P14" s="40"/>
       <c r="Q14" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C14&amp;"'"&amp;","&amp;"'"&amp;D14&amp;"'"&amp;","&amp;VLOOKUP(F14,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G14,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H14,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I14,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J14&amp;","&amp;K14&amp;","&amp;L14&amp;","&amp;"'"&amp;M14&amp;"'"&amp;","&amp;N14&amp;","&amp;IF(O14="","''","'"&amp;O14&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C14&amp;"'"&amp;","&amp;"'"&amp;D14&amp;"'"&amp;","&amp;VLOOKUP(F14,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G14,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H14,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I14,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J14&amp;","&amp;K14&amp;","&amp;L14&amp;","&amp;"'"&amp;M14&amp;"'"&amp;","&amp;N14&amp;","&amp;IF(O14="","''","'"&amp;O14&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill011','渾身斬り',2,0,0,1,30,30,0.1,'effectskill011.gif',800,'');</v>
       </c>
     </row>
@@ -12234,7 +12269,7 @@
       <c r="O15" s="13"/>
       <c r="P15" s="40"/>
       <c r="Q15" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C15&amp;"'"&amp;","&amp;"'"&amp;D15&amp;"'"&amp;","&amp;VLOOKUP(F15,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G15,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H15,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I15,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J15&amp;","&amp;K15&amp;","&amp;L15&amp;","&amp;"'"&amp;M15&amp;"'"&amp;","&amp;N15&amp;","&amp;IF(O15="","''","'"&amp;O15&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C15&amp;"'"&amp;","&amp;"'"&amp;D15&amp;"'"&amp;","&amp;VLOOKUP(F15,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G15,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H15,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I15,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J15&amp;","&amp;K15&amp;","&amp;L15&amp;","&amp;"'"&amp;M15&amp;"'"&amp;","&amp;N15&amp;","&amp;IF(O15="","''","'"&amp;O15&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill012','次元斬',2,0,0,1,50,50,0.1,'effectskill012.gif',1000,'');</v>
       </c>
     </row>
@@ -12276,7 +12311,7 @@
       <c r="O16" s="13"/>
       <c r="P16" s="40"/>
       <c r="Q16" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C16&amp;"'"&amp;","&amp;"'"&amp;D16&amp;"'"&amp;","&amp;VLOOKUP(F16,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G16,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H16,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I16,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J16&amp;","&amp;K16&amp;","&amp;L16&amp;","&amp;"'"&amp;M16&amp;"'"&amp;","&amp;N16&amp;","&amp;IF(O16="","''","'"&amp;O16&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C16&amp;"'"&amp;","&amp;"'"&amp;D16&amp;"'"&amp;","&amp;VLOOKUP(F16,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G16,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H16,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I16,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J16&amp;","&amp;K16&amp;","&amp;L16&amp;","&amp;"'"&amp;M16&amp;"'"&amp;","&amp;N16&amp;","&amp;IF(O16="","''","'"&amp;O16&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill013','薙ぎ払い',2,0,0,2,15,15,0.1,'effectskill013.gif',550,'');</v>
       </c>
     </row>
@@ -12321,7 +12356,7 @@
       <c r="O17" s="13"/>
       <c r="P17" s="40"/>
       <c r="Q17" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C17&amp;"'"&amp;","&amp;"'"&amp;D17&amp;"'"&amp;","&amp;VLOOKUP(F17,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G17,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H17,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I17,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J17&amp;","&amp;K17&amp;","&amp;L17&amp;","&amp;"'"&amp;M17&amp;"'"&amp;","&amp;N17&amp;","&amp;IF(O17="","''","'"&amp;O17&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C17&amp;"'"&amp;","&amp;"'"&amp;D17&amp;"'"&amp;","&amp;VLOOKUP(F17,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G17,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H17,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I17,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J17&amp;","&amp;K17&amp;","&amp;L17&amp;","&amp;"'"&amp;M17&amp;"'"&amp;","&amp;N17&amp;","&amp;IF(O17="","''","'"&amp;O17&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill014','疾走居合',2,0,0,2,25,25,0.1,'effectskill014.gif',800,'');</v>
       </c>
     </row>
@@ -12366,7 +12401,7 @@
       <c r="O18" s="13"/>
       <c r="P18" s="40"/>
       <c r="Q18" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C18&amp;"'"&amp;","&amp;"'"&amp;D18&amp;"'"&amp;","&amp;VLOOKUP(F18,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G18,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H18,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I18,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J18&amp;","&amp;K18&amp;","&amp;L18&amp;","&amp;"'"&amp;M18&amp;"'"&amp;","&amp;N18&amp;","&amp;IF(O18="","''","'"&amp;O18&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C18&amp;"'"&amp;","&amp;"'"&amp;D18&amp;"'"&amp;","&amp;VLOOKUP(F18,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G18,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H18,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I18,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J18&amp;","&amp;K18&amp;","&amp;L18&amp;","&amp;"'"&amp;M18&amp;"'"&amp;","&amp;N18&amp;","&amp;IF(O18="","''","'"&amp;O18&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill015','ギガスラッシュ',2,0,0,2,35,35,0.1,'effectskill015.gif',1500,'');</v>
       </c>
     </row>
@@ -12411,7 +12446,7 @@
       <c r="O19" s="13"/>
       <c r="P19" s="40"/>
       <c r="Q19" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C19&amp;"'"&amp;","&amp;"'"&amp;D19&amp;"'"&amp;","&amp;VLOOKUP(F19,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G19,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H19,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I19,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J19&amp;","&amp;K19&amp;","&amp;L19&amp;","&amp;"'"&amp;M19&amp;"'"&amp;","&amp;N19&amp;","&amp;IF(O19="","''","'"&amp;O19&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C19&amp;"'"&amp;","&amp;"'"&amp;D19&amp;"'"&amp;","&amp;VLOOKUP(F19,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G19,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H19,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I19,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J19&amp;","&amp;K19&amp;","&amp;L19&amp;","&amp;"'"&amp;M19&amp;"'"&amp;","&amp;N19&amp;","&amp;IF(O19="","''","'"&amp;O19&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill016','次元斬_絶',2,0,0,2,45,45,0.1,'effectskill016.gif',1200,'');</v>
       </c>
     </row>
@@ -12456,7 +12491,7 @@
       <c r="O20" s="13"/>
       <c r="P20" s="40"/>
       <c r="Q20" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C20&amp;"'"&amp;","&amp;"'"&amp;D20&amp;"'"&amp;","&amp;VLOOKUP(F20,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G20,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H20,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I20,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J20&amp;","&amp;K20&amp;","&amp;L20&amp;","&amp;"'"&amp;M20&amp;"'"&amp;","&amp;N20&amp;","&amp;IF(O20="","''","'"&amp;O20&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C20&amp;"'"&amp;","&amp;"'"&amp;D20&amp;"'"&amp;","&amp;VLOOKUP(F20,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G20,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H20,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I20,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J20&amp;","&amp;K20&amp;","&amp;L20&amp;","&amp;"'"&amp;M20&amp;"'"&amp;","&amp;N20&amp;","&amp;IF(O20="","''","'"&amp;O20&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill017','ファイアボール',3,1,0,3,10,10,0.0,'effectskill017.gif',1000,'');</v>
       </c>
     </row>
@@ -12501,7 +12536,7 @@
       <c r="O21" s="13"/>
       <c r="P21" s="40"/>
       <c r="Q21" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C21&amp;"'"&amp;","&amp;"'"&amp;D21&amp;"'"&amp;","&amp;VLOOKUP(F21,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G21,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H21,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I21,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J21&amp;","&amp;K21&amp;","&amp;L21&amp;","&amp;"'"&amp;M21&amp;"'"&amp;","&amp;N21&amp;","&amp;IF(O21="","''","'"&amp;O21&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C21&amp;"'"&amp;","&amp;"'"&amp;D21&amp;"'"&amp;","&amp;VLOOKUP(F21,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G21,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H21,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I21,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J21&amp;","&amp;K21&amp;","&amp;L21&amp;","&amp;"'"&amp;M21&amp;"'"&amp;","&amp;N21&amp;","&amp;IF(O21="","''","'"&amp;O21&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill018','エクスプロード',3,1,0,3,30,30,0.0,'effectskill018.gif',1000,'');</v>
       </c>
     </row>
@@ -12546,7 +12581,7 @@
       <c r="O22" s="13"/>
       <c r="P22" s="40"/>
       <c r="Q22" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C22&amp;"'"&amp;","&amp;"'"&amp;D22&amp;"'"&amp;","&amp;VLOOKUP(F22,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G22,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H22,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I22,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J22&amp;","&amp;K22&amp;","&amp;L22&amp;","&amp;"'"&amp;M22&amp;"'"&amp;","&amp;N22&amp;","&amp;IF(O22="","''","'"&amp;O22&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C22&amp;"'"&amp;","&amp;"'"&amp;D22&amp;"'"&amp;","&amp;VLOOKUP(F22,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G22,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H22,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I22,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J22&amp;","&amp;K22&amp;","&amp;L22&amp;","&amp;"'"&amp;M22&amp;"'"&amp;","&amp;N22&amp;","&amp;IF(O22="","''","'"&amp;O22&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill019','ブレイズウォール',3,1,0,3,50,50,0.0,'effectskill019.gif',1200,'');</v>
       </c>
     </row>
@@ -12591,7 +12626,7 @@
       <c r="O23" s="13"/>
       <c r="P23" s="40"/>
       <c r="Q23" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C23&amp;"'"&amp;","&amp;"'"&amp;D23&amp;"'"&amp;","&amp;VLOOKUP(F23,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G23,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H23,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I23,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J23&amp;","&amp;K23&amp;","&amp;L23&amp;","&amp;"'"&amp;M23&amp;"'"&amp;","&amp;N23&amp;","&amp;IF(O23="","''","'"&amp;O23&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C23&amp;"'"&amp;","&amp;"'"&amp;D23&amp;"'"&amp;","&amp;VLOOKUP(F23,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G23,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H23,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I23,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J23&amp;","&amp;K23&amp;","&amp;L23&amp;","&amp;"'"&amp;M23&amp;"'"&amp;","&amp;N23&amp;","&amp;IF(O23="","''","'"&amp;O23&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill020','アイススマッシュ',3,3,0,3,10,10,0.0,'effectskill020.gif',600,'');</v>
       </c>
     </row>
@@ -12636,7 +12671,7 @@
       <c r="O24" s="13"/>
       <c r="P24" s="40"/>
       <c r="Q24" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C24&amp;"'"&amp;","&amp;"'"&amp;D24&amp;"'"&amp;","&amp;VLOOKUP(F24,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G24,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H24,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I24,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J24&amp;","&amp;K24&amp;","&amp;L24&amp;","&amp;"'"&amp;M24&amp;"'"&amp;","&amp;N24&amp;","&amp;IF(O24="","''","'"&amp;O24&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C24&amp;"'"&amp;","&amp;"'"&amp;D24&amp;"'"&amp;","&amp;VLOOKUP(F24,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G24,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H24,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I24,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J24&amp;","&amp;K24&amp;","&amp;L24&amp;","&amp;"'"&amp;M24&amp;"'"&amp;","&amp;N24&amp;","&amp;IF(O24="","''","'"&amp;O24&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill021','メガスプラッシュ',3,3,0,3,30,30,0.0,'effectskill021.gif',1100,'');</v>
       </c>
     </row>
@@ -12681,7 +12716,7 @@
       <c r="O25" s="13"/>
       <c r="P25" s="40"/>
       <c r="Q25" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C25&amp;"'"&amp;","&amp;"'"&amp;D25&amp;"'"&amp;","&amp;VLOOKUP(F25,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G25,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H25,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I25,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J25&amp;","&amp;K25&amp;","&amp;L25&amp;","&amp;"'"&amp;M25&amp;"'"&amp;","&amp;N25&amp;","&amp;IF(O25="","''","'"&amp;O25&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C25&amp;"'"&amp;","&amp;"'"&amp;D25&amp;"'"&amp;","&amp;VLOOKUP(F25,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G25,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H25,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I25,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J25&amp;","&amp;K25&amp;","&amp;L25&amp;","&amp;"'"&amp;M25&amp;"'"&amp;","&amp;N25&amp;","&amp;IF(O25="","''","'"&amp;O25&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill022','コールドブレイズ',3,3,0,3,50,50,0.0,'effectskill022.gif',1000,'');</v>
       </c>
     </row>
@@ -12726,7 +12761,7 @@
       <c r="O26" s="13"/>
       <c r="P26" s="40"/>
       <c r="Q26" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C26&amp;"'"&amp;","&amp;"'"&amp;D26&amp;"'"&amp;","&amp;VLOOKUP(F26,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G26,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H26,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I26,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J26&amp;","&amp;K26&amp;","&amp;L26&amp;","&amp;"'"&amp;M26&amp;"'"&amp;","&amp;N26&amp;","&amp;IF(O26="","''","'"&amp;O26&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C26&amp;"'"&amp;","&amp;"'"&amp;D26&amp;"'"&amp;","&amp;VLOOKUP(F26,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G26,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H26,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I26,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J26&amp;","&amp;K26&amp;","&amp;L26&amp;","&amp;"'"&amp;M26&amp;"'"&amp;","&amp;N26&amp;","&amp;IF(O26="","''","'"&amp;O26&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill023','サンダー',3,2,0,3,10,10,0.0,'effectskill023.gif',1000,'');</v>
       </c>
     </row>
@@ -12771,7 +12806,7 @@
       <c r="O27" s="13"/>
       <c r="P27" s="40"/>
       <c r="Q27" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C27&amp;"'"&amp;","&amp;"'"&amp;D27&amp;"'"&amp;","&amp;VLOOKUP(F27,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G27,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H27,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I27,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J27&amp;","&amp;K27&amp;","&amp;L27&amp;","&amp;"'"&amp;M27&amp;"'"&amp;","&amp;N27&amp;","&amp;IF(O27="","''","'"&amp;O27&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C27&amp;"'"&amp;","&amp;"'"&amp;D27&amp;"'"&amp;","&amp;VLOOKUP(F27,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G27,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H27,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I27,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J27&amp;","&amp;K27&amp;","&amp;L27&amp;","&amp;"'"&amp;M27&amp;"'"&amp;","&amp;N27&amp;","&amp;IF(O27="","''","'"&amp;O27&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill024','サンダーボルト',3,2,0,3,30,30,0.0,'effectskill024.gif',1200,'');</v>
       </c>
     </row>
@@ -12816,7 +12851,7 @@
       <c r="O28" s="13"/>
       <c r="P28" s="40"/>
       <c r="Q28" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C28&amp;"'"&amp;","&amp;"'"&amp;D28&amp;"'"&amp;","&amp;VLOOKUP(F28,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G28,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H28,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I28,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J28&amp;","&amp;K28&amp;","&amp;L28&amp;","&amp;"'"&amp;M28&amp;"'"&amp;","&amp;N28&amp;","&amp;IF(O28="","''","'"&amp;O28&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C28&amp;"'"&amp;","&amp;"'"&amp;D28&amp;"'"&amp;","&amp;VLOOKUP(F28,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G28,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H28,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I28,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J28&amp;","&amp;K28&amp;","&amp;L28&amp;","&amp;"'"&amp;M28&amp;"'"&amp;","&amp;N28&amp;","&amp;IF(O28="","''","'"&amp;O28&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill025','サンダーストーム',3,2,0,3,50,50,0.0,'effectskill025.gif',1400,'');</v>
       </c>
     </row>
@@ -12861,7 +12896,7 @@
       <c r="O29" s="13"/>
       <c r="P29" s="40"/>
       <c r="Q29" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C29&amp;"'"&amp;","&amp;"'"&amp;D29&amp;"'"&amp;","&amp;VLOOKUP(F29,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G29,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H29,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I29,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J29&amp;","&amp;K29&amp;","&amp;L29&amp;","&amp;"'"&amp;M29&amp;"'"&amp;","&amp;N29&amp;","&amp;IF(O29="","''","'"&amp;O29&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C29&amp;"'"&amp;","&amp;"'"&amp;D29&amp;"'"&amp;","&amp;VLOOKUP(F29,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G29,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H29,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I29,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J29&amp;","&amp;K29&amp;","&amp;L29&amp;","&amp;"'"&amp;M29&amp;"'"&amp;","&amp;N29&amp;","&amp;IF(O29="","''","'"&amp;O29&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill026','ダイヤミサイル',3,4,0,3,10,10,0.0,'effectskill026.gif',800,'');</v>
       </c>
     </row>
@@ -12906,7 +12941,7 @@
       <c r="O30" s="13"/>
       <c r="P30" s="40"/>
       <c r="Q30" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C30&amp;"'"&amp;","&amp;"'"&amp;D30&amp;"'"&amp;","&amp;VLOOKUP(F30,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G30,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H30,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I30,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J30&amp;","&amp;K30&amp;","&amp;L30&amp;","&amp;"'"&amp;M30&amp;"'"&amp;","&amp;N30&amp;","&amp;IF(O30="","''","'"&amp;O30&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C30&amp;"'"&amp;","&amp;"'"&amp;D30&amp;"'"&amp;","&amp;VLOOKUP(F30,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G30,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H30,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I30,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J30&amp;","&amp;K30&amp;","&amp;L30&amp;","&amp;"'"&amp;M30&amp;"'"&amp;","&amp;N30&amp;","&amp;IF(O30="","''","'"&amp;O30&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill027','アースクエイク',3,4,0,3,30,30,0.0,'effectskill027.gif',1000,'');</v>
       </c>
     </row>
@@ -12951,7 +12986,7 @@
       <c r="O31" s="13"/>
       <c r="P31" s="40"/>
       <c r="Q31" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C31&amp;"'"&amp;","&amp;"'"&amp;D31&amp;"'"&amp;","&amp;VLOOKUP(F31,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G31,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H31,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I31,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J31&amp;","&amp;K31&amp;","&amp;L31&amp;","&amp;"'"&amp;M31&amp;"'"&amp;","&amp;N31&amp;","&amp;IF(O31="","''","'"&amp;O31&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C31&amp;"'"&amp;","&amp;"'"&amp;D31&amp;"'"&amp;","&amp;VLOOKUP(F31,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G31,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H31,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I31,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J31&amp;","&amp;K31&amp;","&amp;L31&amp;","&amp;"'"&amp;M31&amp;"'"&amp;","&amp;N31&amp;","&amp;IF(O31="","''","'"&amp;O31&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill028','ストーンクラウド',3,4,0,3,50,50,0.0,'effectskill028.gif',1200,'');</v>
       </c>
     </row>
@@ -12996,7 +13031,7 @@
       <c r="O32" s="13"/>
       <c r="P32" s="40"/>
       <c r="Q32" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C32&amp;"'"&amp;","&amp;"'"&amp;D32&amp;"'"&amp;","&amp;VLOOKUP(F32,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G32,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H32,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I32,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J32&amp;","&amp;K32&amp;","&amp;L32&amp;","&amp;"'"&amp;M32&amp;"'"&amp;","&amp;N32&amp;","&amp;IF(O32="","''","'"&amp;O32&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C32&amp;"'"&amp;","&amp;"'"&amp;D32&amp;"'"&amp;","&amp;VLOOKUP(F32,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G32,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H32,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I32,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J32&amp;","&amp;K32&amp;","&amp;L32&amp;","&amp;"'"&amp;M32&amp;"'"&amp;","&amp;N32&amp;","&amp;IF(O32="","''","'"&amp;O32&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill029','ホーリーボール',3,5,0,3,10,10,0.0,'effectskill029.gif',1000,'');</v>
       </c>
     </row>
@@ -13041,7 +13076,7 @@
       <c r="O33" s="13"/>
       <c r="P33" s="40"/>
       <c r="Q33" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C33&amp;"'"&amp;","&amp;"'"&amp;D33&amp;"'"&amp;","&amp;VLOOKUP(F33,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G33,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H33,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I33,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J33&amp;","&amp;K33&amp;","&amp;L33&amp;","&amp;"'"&amp;M33&amp;"'"&amp;","&amp;N33&amp;","&amp;IF(O33="","''","'"&amp;O33&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C33&amp;"'"&amp;","&amp;"'"&amp;D33&amp;"'"&amp;","&amp;VLOOKUP(F33,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G33,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H33,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I33,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J33&amp;","&amp;K33&amp;","&amp;L33&amp;","&amp;"'"&amp;M33&amp;"'"&amp;","&amp;N33&amp;","&amp;IF(O33="","''","'"&amp;O33&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill030','セイントビーム',3,5,0,3,30,30,0.0,'effectskill030.gif',1000,'');</v>
       </c>
     </row>
@@ -13086,7 +13121,7 @@
       <c r="O34" s="13"/>
       <c r="P34" s="40"/>
       <c r="Q34" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C34&amp;"'"&amp;","&amp;"'"&amp;D34&amp;"'"&amp;","&amp;VLOOKUP(F34,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G34,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H34,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I34,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J34&amp;","&amp;K34&amp;","&amp;L34&amp;","&amp;"'"&amp;M34&amp;"'"&amp;","&amp;N34&amp;","&amp;IF(O34="","''","'"&amp;O34&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C34&amp;"'"&amp;","&amp;"'"&amp;D34&amp;"'"&amp;","&amp;VLOOKUP(F34,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G34,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H34,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I34,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J34&amp;","&amp;K34&amp;","&amp;L34&amp;","&amp;"'"&amp;M34&amp;"'"&amp;","&amp;N34&amp;","&amp;IF(O34="","''","'"&amp;O34&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill031','ホーリーバースト',3,5,0,3,50,50,0.0,'effectskill031.gif',1500,'');</v>
       </c>
     </row>
@@ -13131,7 +13166,7 @@
       <c r="O35" s="13"/>
       <c r="P35" s="40"/>
       <c r="Q35" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C35&amp;"'"&amp;","&amp;"'"&amp;D35&amp;"'"&amp;","&amp;VLOOKUP(F35,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G35,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H35,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I35,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J35&amp;","&amp;K35&amp;","&amp;L35&amp;","&amp;"'"&amp;M35&amp;"'"&amp;","&amp;N35&amp;","&amp;IF(O35="","''","'"&amp;O35&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C35&amp;"'"&amp;","&amp;"'"&amp;D35&amp;"'"&amp;","&amp;VLOOKUP(F35,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G35,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H35,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I35,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J35&amp;","&amp;K35&amp;","&amp;L35&amp;","&amp;"'"&amp;M35&amp;"'"&amp;","&amp;N35&amp;","&amp;IF(O35="","''","'"&amp;O35&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill032','イビルゲート',3,6,0,3,10,10,0.0,'effectskill032.gif',1000,'');</v>
       </c>
     </row>
@@ -13176,7 +13211,7 @@
       <c r="O36" s="13"/>
       <c r="P36" s="40"/>
       <c r="Q36" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C36&amp;"'"&amp;","&amp;"'"&amp;D36&amp;"'"&amp;","&amp;VLOOKUP(F36,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G36,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H36,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I36,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J36&amp;","&amp;K36&amp;","&amp;L36&amp;","&amp;"'"&amp;M36&amp;"'"&amp;","&amp;N36&amp;","&amp;IF(O36="","''","'"&amp;O36&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C36&amp;"'"&amp;","&amp;"'"&amp;D36&amp;"'"&amp;","&amp;VLOOKUP(F36,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G36,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H36,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I36,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J36&amp;","&amp;K36&amp;","&amp;L36&amp;","&amp;"'"&amp;M36&amp;"'"&amp;","&amp;N36&amp;","&amp;IF(O36="","''","'"&amp;O36&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill033','ダークフォース',3,6,0,3,30,30,0.0,'effectskill033.gif',1400,'');</v>
       </c>
     </row>
@@ -13221,7 +13256,7 @@
       <c r="O37" s="13"/>
       <c r="P37" s="40"/>
       <c r="Q37" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C37&amp;"'"&amp;","&amp;"'"&amp;D37&amp;"'"&amp;","&amp;VLOOKUP(F37,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G37,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H37,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I37,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J37&amp;","&amp;K37&amp;","&amp;L37&amp;","&amp;"'"&amp;M37&amp;"'"&amp;","&amp;N37&amp;","&amp;IF(O37="","''","'"&amp;O37&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C37&amp;"'"&amp;","&amp;"'"&amp;D37&amp;"'"&amp;","&amp;VLOOKUP(F37,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G37,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H37,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I37,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J37&amp;","&amp;K37&amp;","&amp;L37&amp;","&amp;"'"&amp;M37&amp;"'"&amp;","&amp;N37&amp;","&amp;IF(O37="","''","'"&amp;O37&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill034','ブラックレイン',3,6,0,3,50,50,0.0,'effectskill034.gif',1300,'');</v>
       </c>
     </row>
@@ -13268,7 +13303,7 @@
       </c>
       <c r="P38" s="40"/>
       <c r="Q38" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C38&amp;"'"&amp;","&amp;"'"&amp;D38&amp;"'"&amp;","&amp;VLOOKUP(F38,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G38,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H38,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I38,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J38&amp;","&amp;K38&amp;","&amp;L38&amp;","&amp;"'"&amp;M38&amp;"'"&amp;","&amp;N38&amp;","&amp;IF(O38="","''","'"&amp;O38&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C38&amp;"'"&amp;","&amp;"'"&amp;D38&amp;"'"&amp;","&amp;VLOOKUP(F38,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G38,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H38,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I38,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J38&amp;","&amp;K38&amp;","&amp;L38&amp;","&amp;"'"&amp;M38&amp;"'"&amp;","&amp;N38&amp;","&amp;IF(O38="","''","'"&amp;O38&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill035','グラビデ',4,0,0,1,25,10,0.0,'effectskill035.gif',1000,'現HPの２５％ダメージ');</v>
       </c>
     </row>
@@ -13315,7 +13350,7 @@
       </c>
       <c r="P39" s="40"/>
       <c r="Q39" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C39&amp;"'"&amp;","&amp;"'"&amp;D39&amp;"'"&amp;","&amp;VLOOKUP(F39,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G39,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H39,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I39,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J39&amp;","&amp;K39&amp;","&amp;L39&amp;","&amp;"'"&amp;M39&amp;"'"&amp;","&amp;N39&amp;","&amp;IF(O39="","''","'"&amp;O39&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C39&amp;"'"&amp;","&amp;"'"&amp;D39&amp;"'"&amp;","&amp;VLOOKUP(F39,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G39,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H39,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I39,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J39&amp;","&amp;K39&amp;","&amp;L39&amp;","&amp;"'"&amp;M39&amp;"'"&amp;","&amp;N39&amp;","&amp;IF(O39="","''","'"&amp;O39&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill036','グラビガ',4,0,0,1,50,30,0.0,'effectskill036.gif',1000,'現HPの５０％ダメージ');</v>
       </c>
     </row>
@@ -13362,7 +13397,7 @@
       </c>
       <c r="P40" s="40"/>
       <c r="Q40" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C40&amp;"'"&amp;","&amp;"'"&amp;D40&amp;"'"&amp;","&amp;VLOOKUP(F40,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G40,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H40,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I40,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J40&amp;","&amp;K40&amp;","&amp;L40&amp;","&amp;"'"&amp;M40&amp;"'"&amp;","&amp;N40&amp;","&amp;IF(O40="","''","'"&amp;O40&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C40&amp;"'"&amp;","&amp;"'"&amp;D40&amp;"'"&amp;","&amp;VLOOKUP(F40,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G40,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H40,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I40,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J40&amp;","&amp;K40&amp;","&amp;L40&amp;","&amp;"'"&amp;M40&amp;"'"&amp;","&amp;N40&amp;","&amp;IF(O40="","''","'"&amp;O40&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill037','グラビジャ',4,0,0,1,75,50,0.0,'effectskill037.gif',1200,'現HPの７５％ダメージ');</v>
       </c>
     </row>
@@ -13409,7 +13444,7 @@
       </c>
       <c r="P41" s="41"/>
       <c r="Q41" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C41&amp;"'"&amp;","&amp;"'"&amp;D41&amp;"'"&amp;","&amp;VLOOKUP(F41,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G41,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H41,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I41,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J41&amp;","&amp;K41&amp;","&amp;L41&amp;","&amp;"'"&amp;M41&amp;"'"&amp;","&amp;N41&amp;","&amp;IF(O41="","''","'"&amp;O41&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C41&amp;"'"&amp;","&amp;"'"&amp;D41&amp;"'"&amp;","&amp;VLOOKUP(F41,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G41,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H41,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I41,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J41&amp;","&amp;K41&amp;","&amp;L41&amp;","&amp;"'"&amp;M41&amp;"'"&amp;","&amp;N41&amp;","&amp;IF(O41="","''","'"&amp;O41&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill038','デススペル',5,0,0,1,0,40,0.0,'effectskill038.gif',1800,'即死：単体での確立 = １００％ - (現HP /  MAXHP)、
 最低５％でヒット。');</v>
       </c>
@@ -13455,7 +13490,7 @@
       <c r="O42" s="9"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C42&amp;"'"&amp;","&amp;"'"&amp;D42&amp;"'"&amp;","&amp;VLOOKUP(F42,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G42,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H42,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I42,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J42&amp;","&amp;K42&amp;","&amp;L42&amp;","&amp;"'"&amp;M42&amp;"'"&amp;","&amp;N42&amp;","&amp;IF(O42="","''","'"&amp;O42&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C42&amp;"'"&amp;","&amp;"'"&amp;D42&amp;"'"&amp;","&amp;VLOOKUP(F42,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G42,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H42,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I42,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J42&amp;","&amp;K42&amp;","&amp;L42&amp;","&amp;"'"&amp;M42&amp;"'"&amp;","&amp;N42&amp;","&amp;IF(O42="","''","'"&amp;O42&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill039','ケアル',6,0,0,6,20,20,0.0,'effectskill039.gif',700,'');</v>
       </c>
     </row>
@@ -13500,7 +13535,7 @@
       <c r="O43" s="9"/>
       <c r="P43" s="42"/>
       <c r="Q43" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C43&amp;"'"&amp;","&amp;"'"&amp;D43&amp;"'"&amp;","&amp;VLOOKUP(F43,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G43,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H43,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I43,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J43&amp;","&amp;K43&amp;","&amp;L43&amp;","&amp;"'"&amp;M43&amp;"'"&amp;","&amp;N43&amp;","&amp;IF(O43="","''","'"&amp;O43&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C43&amp;"'"&amp;","&amp;"'"&amp;D43&amp;"'"&amp;","&amp;VLOOKUP(F43,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G43,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H43,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I43,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J43&amp;","&amp;K43&amp;","&amp;L43&amp;","&amp;"'"&amp;M43&amp;"'"&amp;","&amp;N43&amp;","&amp;IF(O43="","''","'"&amp;O43&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill040','ケアルラ',6,0,0,6,30,30,0.0,'effectskill040.gif',1200,'');</v>
       </c>
     </row>
@@ -13545,7 +13580,7 @@
       <c r="O44" s="9"/>
       <c r="P44" s="42"/>
       <c r="Q44" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C44&amp;"'"&amp;","&amp;"'"&amp;D44&amp;"'"&amp;","&amp;VLOOKUP(F44,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G44,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H44,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I44,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J44&amp;","&amp;K44&amp;","&amp;L44&amp;","&amp;"'"&amp;M44&amp;"'"&amp;","&amp;N44&amp;","&amp;IF(O44="","''","'"&amp;O44&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C44&amp;"'"&amp;","&amp;"'"&amp;D44&amp;"'"&amp;","&amp;VLOOKUP(F44,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G44,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H44,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I44,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J44&amp;","&amp;K44&amp;","&amp;L44&amp;","&amp;"'"&amp;M44&amp;"'"&amp;","&amp;N44&amp;","&amp;IF(O44="","''","'"&amp;O44&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill041','ケアルガ',6,0,0,6,40,40,0.0,'effectskill041.gif',1000,'');</v>
       </c>
     </row>
@@ -13590,7 +13625,7 @@
       <c r="O45" s="9"/>
       <c r="P45" s="42"/>
       <c r="Q45" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C45&amp;"'"&amp;","&amp;"'"&amp;D45&amp;"'"&amp;","&amp;VLOOKUP(F45,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G45,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H45,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I45,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J45&amp;","&amp;K45&amp;","&amp;L45&amp;","&amp;"'"&amp;M45&amp;"'"&amp;","&amp;N45&amp;","&amp;IF(O45="","''","'"&amp;O45&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C45&amp;"'"&amp;","&amp;"'"&amp;D45&amp;"'"&amp;","&amp;VLOOKUP(F45,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G45,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H45,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I45,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J45&amp;","&amp;K45&amp;","&amp;L45&amp;","&amp;"'"&amp;M45&amp;"'"&amp;","&amp;N45&amp;","&amp;IF(O45="","''","'"&amp;O45&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill042','ケアルジャ',6,0,0,6,60,50,0.0,'effectskill042.gif',1300,'');</v>
       </c>
     </row>
@@ -13635,7 +13670,7 @@
       <c r="O46" s="9"/>
       <c r="P46" s="42"/>
       <c r="Q46" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C46&amp;"'"&amp;","&amp;"'"&amp;D46&amp;"'"&amp;","&amp;VLOOKUP(F46,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G46,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H46,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I46,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J46&amp;","&amp;K46&amp;","&amp;L46&amp;","&amp;"'"&amp;M46&amp;"'"&amp;","&amp;N46&amp;","&amp;IF(O46="","''","'"&amp;O46&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C46&amp;"'"&amp;","&amp;"'"&amp;D46&amp;"'"&amp;","&amp;VLOOKUP(F46,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G46,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H46,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I46,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J46&amp;","&amp;K46&amp;","&amp;L46&amp;","&amp;"'"&amp;M46&amp;"'"&amp;","&amp;N46&amp;","&amp;IF(O46="","''","'"&amp;O46&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill043','リジェネ',7,0,8,6,0,20,0.0,'effectskill043.gif',1400,'');</v>
       </c>
     </row>
@@ -13680,7 +13715,7 @@
       <c r="O47" s="9"/>
       <c r="P47" s="42"/>
       <c r="Q47" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C47&amp;"'"&amp;","&amp;"'"&amp;D47&amp;"'"&amp;","&amp;VLOOKUP(F47,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G47,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H47,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I47,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J47&amp;","&amp;K47&amp;","&amp;L47&amp;","&amp;"'"&amp;M47&amp;"'"&amp;","&amp;N47&amp;","&amp;IF(O47="","''","'"&amp;O47&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C47&amp;"'"&amp;","&amp;"'"&amp;D47&amp;"'"&amp;","&amp;VLOOKUP(F47,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G47,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H47,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I47,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J47&amp;","&amp;K47&amp;","&amp;L47&amp;","&amp;"'"&amp;M47&amp;"'"&amp;","&amp;N47&amp;","&amp;IF(O47="","''","'"&amp;O47&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill044','ポイズン',7,0,1,1,0,20,0.0,'effectskill044.gif',1000,'');</v>
       </c>
     </row>
@@ -13725,7 +13760,7 @@
       <c r="O48" s="9"/>
       <c r="P48" s="42"/>
       <c r="Q48" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C48&amp;"'"&amp;","&amp;"'"&amp;D48&amp;"'"&amp;","&amp;VLOOKUP(F48,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G48,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H48,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I48,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J48&amp;","&amp;K48&amp;","&amp;L48&amp;","&amp;"'"&amp;M48&amp;"'"&amp;","&amp;N48&amp;","&amp;IF(O48="","''","'"&amp;O48&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C48&amp;"'"&amp;","&amp;"'"&amp;D48&amp;"'"&amp;","&amp;VLOOKUP(F48,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G48,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H48,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I48,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J48&amp;","&amp;K48&amp;","&amp;L48&amp;","&amp;"'"&amp;M48&amp;"'"&amp;","&amp;N48&amp;","&amp;IF(O48="","''","'"&amp;O48&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill045','ポイズンフラワー',7,0,1,2,0,30,0.0,'effectskill045.gif',1000,'');</v>
       </c>
     </row>
@@ -13746,7 +13781,7 @@
         <v>135</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>58</v>
+        <v>1145</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>27</v>
@@ -13772,8 +13807,8 @@
       </c>
       <c r="P49" s="42"/>
       <c r="Q49" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C49&amp;"'"&amp;","&amp;"'"&amp;D49&amp;"'"&amp;","&amp;VLOOKUP(F49,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G49,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H49,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I49,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J49&amp;","&amp;K49&amp;","&amp;L49&amp;","&amp;"'"&amp;M49&amp;"'"&amp;","&amp;N49&amp;","&amp;IF(O49="","''","'"&amp;O49&amp;"'")&amp;");"</f>
-        <v>INSERT INTO m_skill VALUES ('skill046','デッドリーポイズン',7,0,1,1,0,40,0.0,'effectskill046.gif',1000,'最大HPの２０％ダメージ');</v>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C49&amp;"'"&amp;","&amp;"'"&amp;D49&amp;"'"&amp;","&amp;VLOOKUP(F49,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G49,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H49,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I49,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J49&amp;","&amp;K49&amp;","&amp;L49&amp;","&amp;"'"&amp;M49&amp;"'"&amp;","&amp;N49&amp;","&amp;IF(O49="","''","'"&amp;O49&amp;"'")&amp;");"</f>
+        <v>INSERT INTO m_skill VALUES ('skill046','デッドリーポイズン',7,0,9,1,0,40,0.0,'effectskill046.gif',1000,'最大HPの２０％ダメージ');</v>
       </c>
     </row>
     <row r="50" spans="3:17">
@@ -13817,7 +13852,7 @@
       <c r="O50" s="9"/>
       <c r="P50" s="42"/>
       <c r="Q50" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C50&amp;"'"&amp;","&amp;"'"&amp;D50&amp;"'"&amp;","&amp;VLOOKUP(F50,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G50,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H50,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I50,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J50&amp;","&amp;K50&amp;","&amp;L50&amp;","&amp;"'"&amp;M50&amp;"'"&amp;","&amp;N50&amp;","&amp;IF(O50="","''","'"&amp;O50&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C50&amp;"'"&amp;","&amp;"'"&amp;D50&amp;"'"&amp;","&amp;VLOOKUP(F50,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G50,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H50,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I50,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J50&amp;","&amp;K50&amp;","&amp;L50&amp;","&amp;"'"&amp;M50&amp;"'"&amp;","&amp;N50&amp;","&amp;IF(O50="","''","'"&amp;O50&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill047','スリプル',7,0,2,1,0,20,0.0,'effectskill047.gif',1300,'');</v>
       </c>
     </row>
@@ -13862,7 +13897,7 @@
       <c r="O51" s="9"/>
       <c r="P51" s="42"/>
       <c r="Q51" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C51&amp;"'"&amp;","&amp;"'"&amp;D51&amp;"'"&amp;","&amp;VLOOKUP(F51,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G51,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H51,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I51,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J51&amp;","&amp;K51&amp;","&amp;L51&amp;","&amp;"'"&amp;M51&amp;"'"&amp;","&amp;N51&amp;","&amp;IF(O51="","''","'"&amp;O51&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C51&amp;"'"&amp;","&amp;"'"&amp;D51&amp;"'"&amp;","&amp;VLOOKUP(F51,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G51,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H51,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I51,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J51&amp;","&amp;K51&amp;","&amp;L51&amp;","&amp;"'"&amp;M51&amp;"'"&amp;","&amp;N51&amp;","&amp;IF(O51="","''","'"&amp;O51&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill048','スリープミスト',7,0,2,2,0,30,0.0,'effectskill048.gif',1000,'');</v>
       </c>
     </row>
@@ -13907,7 +13942,7 @@
       <c r="O52" s="9"/>
       <c r="P52" s="42"/>
       <c r="Q52" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C52&amp;"'"&amp;","&amp;"'"&amp;D52&amp;"'"&amp;","&amp;VLOOKUP(F52,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G52,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H52,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I52,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J52&amp;","&amp;K52&amp;","&amp;L52&amp;","&amp;"'"&amp;M52&amp;"'"&amp;","&amp;N52&amp;","&amp;IF(O52="","''","'"&amp;O52&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C52&amp;"'"&amp;","&amp;"'"&amp;D52&amp;"'"&amp;","&amp;VLOOKUP(F52,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G52,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H52,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I52,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J52&amp;","&amp;K52&amp;","&amp;L52&amp;","&amp;"'"&amp;M52&amp;"'"&amp;","&amp;N52&amp;","&amp;IF(O52="","''","'"&amp;O52&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill049','チャーム',7,0,3,1,0,30,0.0,'effectskill049.gif',1000,'');</v>
       </c>
     </row>
@@ -13952,7 +13987,7 @@
       <c r="O53" s="9"/>
       <c r="P53" s="42"/>
       <c r="Q53" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C53&amp;"'"&amp;","&amp;"'"&amp;D53&amp;"'"&amp;","&amp;VLOOKUP(F53,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G53,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H53,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I53,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J53&amp;","&amp;K53&amp;","&amp;L53&amp;","&amp;"'"&amp;M53&amp;"'"&amp;","&amp;N53&amp;","&amp;IF(O53="","''","'"&amp;O53&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C53&amp;"'"&amp;","&amp;"'"&amp;D53&amp;"'"&amp;","&amp;VLOOKUP(F53,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G53,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H53,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I53,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J53&amp;","&amp;K53&amp;","&amp;L53&amp;","&amp;"'"&amp;M53&amp;"'"&amp;","&amp;N53&amp;","&amp;IF(O53="","''","'"&amp;O53&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill050','スロウ',7,0,4,1,0,20,0.0,'effectskill050.gif',1000,'');</v>
       </c>
     </row>
@@ -13997,7 +14032,7 @@
       <c r="O54" s="9"/>
       <c r="P54" s="42"/>
       <c r="Q54" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C54&amp;"'"&amp;","&amp;"'"&amp;D54&amp;"'"&amp;","&amp;VLOOKUP(F54,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G54,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H54,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I54,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J54&amp;","&amp;K54&amp;","&amp;L54&amp;","&amp;"'"&amp;M54&amp;"'"&amp;","&amp;N54&amp;","&amp;IF(O54="","''","'"&amp;O54&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C54&amp;"'"&amp;","&amp;"'"&amp;D54&amp;"'"&amp;","&amp;VLOOKUP(F54,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G54,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H54,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I54,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J54&amp;","&amp;K54&amp;","&amp;L54&amp;","&amp;"'"&amp;M54&amp;"'"&amp;","&amp;N54&amp;","&amp;IF(O54="","''","'"&amp;O54&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill051','スロウガ',7,0,4,2,0,30,0.0,'effectskill051.gif',1000,'');</v>
       </c>
     </row>
@@ -14044,7 +14079,7 @@
       </c>
       <c r="P55" s="42"/>
       <c r="Q55" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C55&amp;"'"&amp;","&amp;"'"&amp;D55&amp;"'"&amp;","&amp;VLOOKUP(F55,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G55,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H55,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I55,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J55&amp;","&amp;K55&amp;","&amp;L55&amp;","&amp;"'"&amp;M55&amp;"'"&amp;","&amp;N55&amp;","&amp;IF(O55="","''","'"&amp;O55&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C55&amp;"'"&amp;","&amp;"'"&amp;D55&amp;"'"&amp;","&amp;VLOOKUP(F55,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G55,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H55,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I55,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J55&amp;","&amp;K55&amp;","&amp;L55&amp;","&amp;"'"&amp;M55&amp;"'"&amp;","&amp;N55&amp;","&amp;IF(O55="","''","'"&amp;O55&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill052','バーサク',7,0,5,6,0,30,0.0,'effectskill052.gif',1000,'攻撃力３０％UP');</v>
       </c>
     </row>
@@ -14091,7 +14126,7 @@
       </c>
       <c r="P56" s="42"/>
       <c r="Q56" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C56&amp;"'"&amp;","&amp;"'"&amp;D56&amp;"'"&amp;","&amp;VLOOKUP(F56,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G56,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H56,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I56,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J56&amp;","&amp;K56&amp;","&amp;L56&amp;","&amp;"'"&amp;M56&amp;"'"&amp;","&amp;N56&amp;","&amp;IF(O56="","''","'"&amp;O56&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C56&amp;"'"&amp;","&amp;"'"&amp;D56&amp;"'"&amp;","&amp;VLOOKUP(F56,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G56,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H56,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I56,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J56&amp;","&amp;K56&amp;","&amp;L56&amp;","&amp;"'"&amp;M56&amp;"'"&amp;","&amp;N56&amp;","&amp;IF(O56="","''","'"&amp;O56&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill053','ビジョン',7,0,6,6,0,30,0.0,'effectskill053.gif',1000,'３０％の確率で攻撃を回避');</v>
       </c>
     </row>
@@ -14138,7 +14173,7 @@
       </c>
       <c r="P57" s="42"/>
       <c r="Q57" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C57&amp;"'"&amp;","&amp;"'"&amp;D57&amp;"'"&amp;","&amp;VLOOKUP(F57,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G57,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H57,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I57,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J57&amp;","&amp;K57&amp;","&amp;L57&amp;","&amp;"'"&amp;M57&amp;"'"&amp;","&amp;N57&amp;","&amp;IF(O57="","''","'"&amp;O57&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C57&amp;"'"&amp;","&amp;"'"&amp;D57&amp;"'"&amp;","&amp;VLOOKUP(F57,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G57,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H57,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I57,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J57&amp;","&amp;K57&amp;","&amp;L57&amp;","&amp;"'"&amp;M57&amp;"'"&amp;","&amp;N57&amp;","&amp;IF(O57="","''","'"&amp;O57&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill054','エナジーボール',7,0,7,6,0,30,0.0,'effectskill054.gif',1000,'クリティカル率３０％UP');</v>
       </c>
     </row>
@@ -14185,7 +14220,7 @@
       </c>
       <c r="P58" s="42"/>
       <c r="Q58" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C58&amp;"'"&amp;","&amp;"'"&amp;D58&amp;"'"&amp;","&amp;VLOOKUP(F58,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G58,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H58,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I58,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J58&amp;","&amp;K58&amp;","&amp;L58&amp;","&amp;"'"&amp;M58&amp;"'"&amp;","&amp;N58&amp;","&amp;IF(O58="","''","'"&amp;O58&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C58&amp;"'"&amp;","&amp;"'"&amp;D58&amp;"'"&amp;","&amp;VLOOKUP(F58,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G58,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H58,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I58,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J58&amp;","&amp;K58&amp;","&amp;L58&amp;","&amp;"'"&amp;M58&amp;"'"&amp;","&amp;N58&amp;","&amp;IF(O58="","''","'"&amp;O58&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill055','ミスをした',8,0,0,0,0,0,0.0,'effectskill055.gif',1000,'そのターンは行動しない');</v>
       </c>
     </row>
@@ -14232,7 +14267,7 @@
       </c>
       <c r="P59" s="42"/>
       <c r="Q59" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C59&amp;"'"&amp;","&amp;"'"&amp;D59&amp;"'"&amp;","&amp;VLOOKUP(F59,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G59,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H59,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I59,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J59&amp;","&amp;K59&amp;","&amp;L59&amp;","&amp;"'"&amp;M59&amp;"'"&amp;","&amp;N59&amp;","&amp;IF(O59="","''","'"&amp;O59&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C59&amp;"'"&amp;","&amp;"'"&amp;D59&amp;"'"&amp;","&amp;VLOOKUP(F59,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G59,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H59,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I59,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J59&amp;","&amp;K59&amp;","&amp;L59&amp;","&amp;"'"&amp;M59&amp;"'"&amp;","&amp;N59&amp;","&amp;IF(O59="","''","'"&amp;O59&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill056','様子を見ている',8,0,0,0,0,0,0.0,'effectskill056.gif',1000,'そのターンは行動しない');</v>
       </c>
     </row>
@@ -14279,7 +14314,7 @@
       </c>
       <c r="P60" s="42"/>
       <c r="Q60" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C60&amp;"'"&amp;","&amp;"'"&amp;D60&amp;"'"&amp;","&amp;VLOOKUP(F60,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G60,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H60,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I60,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J60&amp;","&amp;K60&amp;","&amp;L60&amp;","&amp;"'"&amp;M60&amp;"'"&amp;","&amp;N60&amp;","&amp;IF(O60="","''","'"&amp;O60&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C60&amp;"'"&amp;","&amp;"'"&amp;D60&amp;"'"&amp;","&amp;VLOOKUP(F60,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G60,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H60,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I60,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J60&amp;","&amp;K60&amp;","&amp;L60&amp;","&amp;"'"&amp;M60&amp;"'"&amp;","&amp;N60&amp;","&amp;IF(O60="","''","'"&amp;O60&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill057','余裕に構えている',8,0,0,0,0,0,0.0,'effectskill057.gif',1000,'そのターンは行動しない');</v>
       </c>
     </row>
@@ -14320,7 +14355,7 @@
       </c>
       <c r="O61" s="8"/>
       <c r="Q61" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C61&amp;"'"&amp;","&amp;"'"&amp;D61&amp;"'"&amp;","&amp;VLOOKUP(F61,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G61,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H61,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I61,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J61&amp;","&amp;K61&amp;","&amp;L61&amp;","&amp;"'"&amp;M61&amp;"'"&amp;","&amp;N61&amp;","&amp;IF(O61="","''","'"&amp;O61&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C61&amp;"'"&amp;","&amp;"'"&amp;D61&amp;"'"&amp;","&amp;VLOOKUP(F61,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G61,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H61,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I61,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J61&amp;","&amp;K61&amp;","&amp;L61&amp;","&amp;"'"&amp;M61&amp;"'"&amp;","&amp;N61&amp;","&amp;IF(O61="","''","'"&amp;O61&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill058','噛みつき',2,0,0,1,15,15,0.1,'effectskill058.gif',700,'');</v>
       </c>
     </row>
@@ -14361,7 +14396,7 @@
       </c>
       <c r="O62" s="8"/>
       <c r="Q62" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C62&amp;"'"&amp;","&amp;"'"&amp;D62&amp;"'"&amp;","&amp;VLOOKUP(F62,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G62,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H62,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I62,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J62&amp;","&amp;K62&amp;","&amp;L62&amp;","&amp;"'"&amp;M62&amp;"'"&amp;","&amp;N62&amp;","&amp;IF(O62="","''","'"&amp;O62&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C62&amp;"'"&amp;","&amp;"'"&amp;D62&amp;"'"&amp;","&amp;VLOOKUP(F62,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G62,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H62,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I62,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J62&amp;","&amp;K62&amp;","&amp;L62&amp;","&amp;"'"&amp;M62&amp;"'"&amp;","&amp;N62&amp;","&amp;IF(O62="","''","'"&amp;O62&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill059','喰いちぎり',2,0,0,1,30,30,0.1,'effectskill059.gif',700,'');</v>
       </c>
     </row>
@@ -14402,7 +14437,7 @@
       </c>
       <c r="O63" s="8"/>
       <c r="Q63" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C63&amp;"'"&amp;","&amp;"'"&amp;D63&amp;"'"&amp;","&amp;VLOOKUP(F63,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G63,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H63,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I63,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J63&amp;","&amp;K63&amp;","&amp;L63&amp;","&amp;"'"&amp;M63&amp;"'"&amp;","&amp;N63&amp;","&amp;IF(O63="","''","'"&amp;O63&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C63&amp;"'"&amp;","&amp;"'"&amp;D63&amp;"'"&amp;","&amp;VLOOKUP(F63,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G63,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H63,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I63,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J63&amp;","&amp;K63&amp;","&amp;L63&amp;","&amp;"'"&amp;M63&amp;"'"&amp;","&amp;N63&amp;","&amp;IF(O63="","''","'"&amp;O63&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill060','タックル',1,0,0,1,15,15,0.1,'effectskill060.gif',700,'');</v>
       </c>
     </row>
@@ -14443,7 +14478,7 @@
       </c>
       <c r="O64" s="8"/>
       <c r="Q64" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C64&amp;"'"&amp;","&amp;"'"&amp;D64&amp;"'"&amp;","&amp;VLOOKUP(F64,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G64,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H64,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I64,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J64&amp;","&amp;K64&amp;","&amp;L64&amp;","&amp;"'"&amp;M64&amp;"'"&amp;","&amp;N64&amp;","&amp;IF(O64="","''","'"&amp;O64&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C64&amp;"'"&amp;","&amp;"'"&amp;D64&amp;"'"&amp;","&amp;VLOOKUP(F64,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G64,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H64,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I64,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J64&amp;","&amp;K64&amp;","&amp;L64&amp;","&amp;"'"&amp;M64&amp;"'"&amp;","&amp;N64&amp;","&amp;IF(O64="","''","'"&amp;O64&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill061','突撃',1,0,0,1,30,30,0.1,'effectskill061.gif',700,'');</v>
       </c>
     </row>
@@ -14487,7 +14522,7 @@
       </c>
       <c r="O65" s="8"/>
       <c r="Q65" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C65&amp;"'"&amp;","&amp;"'"&amp;D65&amp;"'"&amp;","&amp;VLOOKUP(F65,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G65,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H65,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I65,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J65&amp;","&amp;K65&amp;","&amp;L65&amp;","&amp;"'"&amp;M65&amp;"'"&amp;","&amp;N65&amp;","&amp;IF(O65="","''","'"&amp;O65&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C65&amp;"'"&amp;","&amp;"'"&amp;D65&amp;"'"&amp;","&amp;VLOOKUP(F65,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G65,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H65,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I65,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J65&amp;","&amp;K65&amp;","&amp;L65&amp;","&amp;"'"&amp;M65&amp;"'"&amp;","&amp;N65&amp;","&amp;IF(O65="","''","'"&amp;O65&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill062','振り回す',1,0,0,1,15,15,0.1,'effectskill062.gif',1000,'');</v>
       </c>
     </row>
@@ -14531,7 +14566,7 @@
       </c>
       <c r="O66" s="8"/>
       <c r="Q66" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C66&amp;"'"&amp;","&amp;"'"&amp;D66&amp;"'"&amp;","&amp;VLOOKUP(F66,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G66,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H66,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I66,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J66&amp;","&amp;K66&amp;","&amp;L66&amp;","&amp;"'"&amp;M66&amp;"'"&amp;","&amp;N66&amp;","&amp;IF(O66="","''","'"&amp;O66&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C66&amp;"'"&amp;","&amp;"'"&amp;D66&amp;"'"&amp;","&amp;VLOOKUP(F66,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G66,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H66,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I66,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J66&amp;","&amp;K66&amp;","&amp;L66&amp;","&amp;"'"&amp;M66&amp;"'"&amp;","&amp;N66&amp;","&amp;IF(O66="","''","'"&amp;O66&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill063','フルスイング',1,0,0,1,30,30,0.1,'effectskill063.gif',800,'');</v>
       </c>
     </row>
@@ -14575,7 +14610,7 @@
       </c>
       <c r="O67" s="8"/>
       <c r="Q67" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C67&amp;"'"&amp;","&amp;"'"&amp;D67&amp;"'"&amp;","&amp;VLOOKUP(F67,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G67,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H67,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I67,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J67&amp;","&amp;K67&amp;","&amp;L67&amp;","&amp;"'"&amp;M67&amp;"'"&amp;","&amp;N67&amp;","&amp;IF(O67="","''","'"&amp;O67&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C67&amp;"'"&amp;","&amp;"'"&amp;D67&amp;"'"&amp;","&amp;VLOOKUP(F67,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G67,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H67,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I67,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J67&amp;","&amp;K67&amp;","&amp;L67&amp;","&amp;"'"&amp;M67&amp;"'"&amp;","&amp;N67&amp;","&amp;IF(O67="","''","'"&amp;O67&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill064','突き',2,0,0,1,15,15,0.1,'effectskill064.gif',800,'');</v>
       </c>
     </row>
@@ -14619,7 +14654,7 @@
       </c>
       <c r="O68" s="8"/>
       <c r="Q68" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C68&amp;"'"&amp;","&amp;"'"&amp;D68&amp;"'"&amp;","&amp;VLOOKUP(F68,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G68,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H68,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I68,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J68&amp;","&amp;K68&amp;","&amp;L68&amp;","&amp;"'"&amp;M68&amp;"'"&amp;","&amp;N68&amp;","&amp;IF(O68="","''","'"&amp;O68&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C68&amp;"'"&amp;","&amp;"'"&amp;D68&amp;"'"&amp;","&amp;VLOOKUP(F68,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G68,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H68,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I68,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J68&amp;","&amp;K68&amp;","&amp;L68&amp;","&amp;"'"&amp;M68&amp;"'"&amp;","&amp;N68&amp;","&amp;IF(O68="","''","'"&amp;O68&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill065','串刺し',2,0,0,1,30,30,0.1,'effectskill065.gif',900,'');</v>
       </c>
     </row>
@@ -14660,7 +14695,7 @@
       </c>
       <c r="O69" s="8"/>
       <c r="Q69" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C69&amp;"'"&amp;","&amp;"'"&amp;D69&amp;"'"&amp;","&amp;VLOOKUP(F69,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G69,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H69,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I69,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J69&amp;","&amp;K69&amp;","&amp;L69&amp;","&amp;"'"&amp;M69&amp;"'"&amp;","&amp;N69&amp;","&amp;IF(O69="","''","'"&amp;O69&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C69&amp;"'"&amp;","&amp;"'"&amp;D69&amp;"'"&amp;","&amp;VLOOKUP(F69,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G69,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H69,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I69,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J69&amp;","&amp;K69&amp;","&amp;L69&amp;","&amp;"'"&amp;M69&amp;"'"&amp;","&amp;N69&amp;","&amp;IF(O69="","''","'"&amp;O69&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill066','叩きつけ',1,0,0,1,15,15,0.1,'effectskill066.gif',1000,'');</v>
       </c>
     </row>
@@ -14704,7 +14739,7 @@
       </c>
       <c r="O70" s="8"/>
       <c r="Q70" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C70&amp;"'"&amp;","&amp;"'"&amp;D70&amp;"'"&amp;","&amp;VLOOKUP(F70,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G70,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H70,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I70,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J70&amp;","&amp;K70&amp;","&amp;L70&amp;","&amp;"'"&amp;M70&amp;"'"&amp;","&amp;N70&amp;","&amp;IF(O70="","''","'"&amp;O70&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C70&amp;"'"&amp;","&amp;"'"&amp;D70&amp;"'"&amp;","&amp;VLOOKUP(F70,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G70,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H70,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I70,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J70&amp;","&amp;K70&amp;","&amp;L70&amp;","&amp;"'"&amp;M70&amp;"'"&amp;","&amp;N70&amp;","&amp;IF(O70="","''","'"&amp;O70&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill067','叩き潰し',1,0,0,1,30,30,0.1,'effectskill067.gif',1000,'');</v>
       </c>
     </row>
@@ -14745,7 +14780,7 @@
       </c>
       <c r="O71" s="8"/>
       <c r="Q71" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C71&amp;"'"&amp;","&amp;"'"&amp;D71&amp;"'"&amp;","&amp;VLOOKUP(F71,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G71,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H71,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I71,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J71&amp;","&amp;K71&amp;","&amp;L71&amp;","&amp;"'"&amp;M71&amp;"'"&amp;","&amp;N71&amp;","&amp;IF(O71="","''","'"&amp;O71&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C71&amp;"'"&amp;","&amp;"'"&amp;D71&amp;"'"&amp;","&amp;VLOOKUP(F71,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G71,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H71,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I71,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J71&amp;","&amp;K71&amp;","&amp;L71&amp;","&amp;"'"&amp;M71&amp;"'"&amp;","&amp;N71&amp;","&amp;IF(O71="","''","'"&amp;O71&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill068','引き裂く',2,0,0,1,15,15,0.1,'effectskill068.gif',700,'');</v>
       </c>
     </row>
@@ -14789,7 +14824,7 @@
       </c>
       <c r="O72" s="8"/>
       <c r="Q72" s="5" t="str">
-        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C72&amp;"'"&amp;","&amp;"'"&amp;D72&amp;"'"&amp;","&amp;VLOOKUP(F72,コード!$C$33:$H$41,2,FALSE)&amp;","&amp;VLOOKUP(G72,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H72,コード!$C$13:$H$21,2,FALSE)&amp;","&amp;VLOOKUP(I72,コード!$C$23:$H$31,2,FALSE)&amp;","&amp;J72&amp;","&amp;K72&amp;","&amp;L72&amp;","&amp;"'"&amp;M72&amp;"'"&amp;","&amp;N72&amp;","&amp;IF(O72="","''","'"&amp;O72&amp;"'")&amp;");"</f>
+        <f>"INSERT INTO m_skill VALUES ("&amp;"'"&amp;C72&amp;"'"&amp;","&amp;"'"&amp;D72&amp;"'"&amp;","&amp;VLOOKUP(F72,コード!$C$34:$H$42,2,FALSE)&amp;","&amp;VLOOKUP(G72,コード!$C$5:$H$11,2,FALSE)&amp;","&amp;VLOOKUP(H72,コード!$C$13:$H$22,2,FALSE)&amp;","&amp;VLOOKUP(I72,コード!$C$24:$H$32,2,FALSE)&amp;","&amp;J72&amp;","&amp;K72&amp;","&amp;L72&amp;","&amp;"'"&amp;M72&amp;"'"&amp;","&amp;N72&amp;","&amp;IF(O72="","''","'"&amp;O72&amp;"'")&amp;");"</f>
         <v>INSERT INTO m_skill VALUES ('skill069','首狩り',2,0,0,1,30,30,0.1,'effectskill069.gif',1000,'');</v>
       </c>
     </row>
@@ -15062,7 +15097,7 @@
         <v>160</v>
       </c>
       <c r="K6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;VLOOKUP(H6,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;VLOOKUP(H6,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,1);</v>
       </c>
     </row>
@@ -15092,7 +15127,7 @@
         <v>160</v>
       </c>
       <c r="K7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;VLOOKUP(H7,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;VLOOKUP(H7,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,1);</v>
       </c>
     </row>
@@ -15122,7 +15157,7 @@
         <v>160</v>
       </c>
       <c r="K8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;VLOOKUP(H8,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;VLOOKUP(H8,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,1);</v>
       </c>
     </row>
@@ -15149,7 +15184,7 @@
         <v>34</v>
       </c>
       <c r="K9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;VLOOKUP(H9,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;VLOOKUP(H9,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,2);</v>
       </c>
     </row>
@@ -15179,7 +15214,7 @@
         <v>34</v>
       </c>
       <c r="K10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;VLOOKUP(H10,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;VLOOKUP(H10,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,2);</v>
       </c>
     </row>
@@ -15206,7 +15241,7 @@
         <v>36</v>
       </c>
       <c r="K11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;VLOOKUP(H11,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;VLOOKUP(H11,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,5);</v>
       </c>
     </row>
@@ -15236,7 +15271,7 @@
         <v>36</v>
       </c>
       <c r="K12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;VLOOKUP(H12,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;VLOOKUP(H12,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,5);</v>
       </c>
     </row>
@@ -15263,7 +15298,7 @@
         <v>35</v>
       </c>
       <c r="K13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;VLOOKUP(H13,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;VLOOKUP(H13,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,4);</v>
       </c>
     </row>
@@ -15293,7 +15328,7 @@
         <v>35</v>
       </c>
       <c r="K14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;VLOOKUP(H14,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;VLOOKUP(H14,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,4);</v>
       </c>
     </row>
@@ -15323,7 +15358,7 @@
         <v>35</v>
       </c>
       <c r="K15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;VLOOKUP(H15,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;VLOOKUP(H15,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,4);</v>
       </c>
     </row>
@@ -15350,7 +15385,7 @@
         <v>161</v>
       </c>
       <c r="K16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;VLOOKUP(H16,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;VLOOKUP(H16,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,3);</v>
       </c>
     </row>
@@ -15380,7 +15415,7 @@
         <v>161</v>
       </c>
       <c r="K17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;VLOOKUP(H17,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;VLOOKUP(H17,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,3);</v>
       </c>
     </row>
@@ -15410,7 +15445,7 @@
         <v>161</v>
       </c>
       <c r="K18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;VLOOKUP(H18,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;VLOOKUP(H18,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,3);</v>
       </c>
     </row>
@@ -15437,7 +15472,7 @@
         <v>35</v>
       </c>
       <c r="K19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;VLOOKUP(H19,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;VLOOKUP(H19,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,4);</v>
       </c>
     </row>
@@ -15467,7 +15502,7 @@
         <v>35</v>
       </c>
       <c r="K20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;VLOOKUP(H20,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;VLOOKUP(H20,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,4);</v>
       </c>
     </row>
@@ -15494,7 +15529,7 @@
         <v>34</v>
       </c>
       <c r="K21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;VLOOKUP(H21,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;VLOOKUP(H21,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,2);</v>
       </c>
     </row>
@@ -15524,7 +15559,7 @@
         <v>34</v>
       </c>
       <c r="K22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;VLOOKUP(H22,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;VLOOKUP(H22,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,2);</v>
       </c>
     </row>
@@ -15554,7 +15589,7 @@
         <v>34</v>
       </c>
       <c r="K23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;VLOOKUP(H23,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;VLOOKUP(H23,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,2);</v>
       </c>
     </row>
@@ -15581,7 +15616,7 @@
         <v>35</v>
       </c>
       <c r="K24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;VLOOKUP(H24,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;VLOOKUP(H24,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,4);</v>
       </c>
     </row>
@@ -15611,7 +15646,7 @@
         <v>35</v>
       </c>
       <c r="K25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;VLOOKUP(H25,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;VLOOKUP(H25,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,4);</v>
       </c>
     </row>
@@ -15641,7 +15676,7 @@
         <v>35</v>
       </c>
       <c r="K26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;VLOOKUP(H26,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;VLOOKUP(H26,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,4);</v>
       </c>
     </row>
@@ -15668,7 +15703,7 @@
         <v>160</v>
       </c>
       <c r="K27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;VLOOKUP(H27,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;VLOOKUP(H27,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,1);</v>
       </c>
     </row>
@@ -15698,7 +15733,7 @@
         <v>160</v>
       </c>
       <c r="K28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;VLOOKUP(H28,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;VLOOKUP(H28,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,1);</v>
       </c>
     </row>
@@ -15725,7 +15760,7 @@
         <v>161</v>
       </c>
       <c r="K29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;VLOOKUP(H29,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;VLOOKUP(H29,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,3);</v>
       </c>
     </row>
@@ -15755,7 +15790,7 @@
         <v>161</v>
       </c>
       <c r="K30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;VLOOKUP(H30,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;VLOOKUP(H30,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,3);</v>
       </c>
     </row>
@@ -15782,7 +15817,7 @@
         <v>161</v>
       </c>
       <c r="K31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;VLOOKUP(H31,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;VLOOKUP(H31,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,3);</v>
       </c>
     </row>
@@ -15812,7 +15847,7 @@
         <v>36</v>
       </c>
       <c r="K32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;VLOOKUP(H32,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;VLOOKUP(H32,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,5);</v>
       </c>
     </row>
@@ -15842,7 +15877,7 @@
         <v>160</v>
       </c>
       <c r="K33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;VLOOKUP(H33,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;VLOOKUP(H33,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,1);</v>
       </c>
     </row>
@@ -15872,7 +15907,7 @@
         <v>37</v>
       </c>
       <c r="K34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;VLOOKUP(H34,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;VLOOKUP(H34,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,6);</v>
       </c>
     </row>
@@ -15899,7 +15934,7 @@
         <v>37</v>
       </c>
       <c r="K35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;VLOOKUP(H35,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;VLOOKUP(H35,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,6);</v>
       </c>
     </row>
@@ -15929,7 +15964,7 @@
         <v>37</v>
       </c>
       <c r="K36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;VLOOKUP(H36,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;VLOOKUP(H36,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,6);</v>
       </c>
     </row>
@@ -15959,7 +15994,7 @@
         <v>37</v>
       </c>
       <c r="K37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;VLOOKUP(H37,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;VLOOKUP(H37,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,6);</v>
       </c>
     </row>
@@ -15986,7 +16021,7 @@
         <v>37</v>
       </c>
       <c r="K38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;VLOOKUP(H38,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;VLOOKUP(H38,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,6);</v>
       </c>
     </row>
@@ -16016,7 +16051,7 @@
         <v>36</v>
       </c>
       <c r="K39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;VLOOKUP(H39,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;VLOOKUP(H39,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,5);</v>
       </c>
     </row>
@@ -16046,7 +16081,7 @@
         <v>36</v>
       </c>
       <c r="K40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;VLOOKUP(H40,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;VLOOKUP(H40,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,5);</v>
       </c>
     </row>
@@ -16074,7 +16109,7 @@
         <v>37</v>
       </c>
       <c r="K41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;VLOOKUP(H41,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;VLOOKUP(H41,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,6);</v>
       </c>
     </row>
@@ -16104,7 +16139,7 @@
         <v>37</v>
       </c>
       <c r="K42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;VLOOKUP(H42,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;VLOOKUP(H42,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,6);</v>
       </c>
     </row>
@@ -16134,7 +16169,7 @@
         <v>37</v>
       </c>
       <c r="K43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;VLOOKUP(H43,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;VLOOKUP(H43,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,6);</v>
       </c>
     </row>
@@ -16164,7 +16199,7 @@
         <v>37</v>
       </c>
       <c r="K44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;VLOOKUP(H44,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;VLOOKUP(H44,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,6);</v>
       </c>
     </row>
@@ -16191,7 +16226,7 @@
         <v>34</v>
       </c>
       <c r="K45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;VLOOKUP(H45,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;VLOOKUP(H45,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,2);</v>
       </c>
     </row>
@@ -16221,7 +16256,7 @@
         <v>160</v>
       </c>
       <c r="K46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;VLOOKUP(H46,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;VLOOKUP(H46,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,1);</v>
       </c>
     </row>
@@ -16251,7 +16286,7 @@
         <v>161</v>
       </c>
       <c r="K47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;VLOOKUP(H47,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;VLOOKUP(H47,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,3);</v>
       </c>
     </row>
@@ -16278,7 +16313,7 @@
         <v>36</v>
       </c>
       <c r="K48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;VLOOKUP(H48,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;VLOOKUP(H48,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,5);</v>
       </c>
     </row>
@@ -16308,7 +16343,7 @@
         <v>36</v>
       </c>
       <c r="K49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;VLOOKUP(H49,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;VLOOKUP(H49,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,5);</v>
       </c>
     </row>
@@ -16338,7 +16373,7 @@
         <v>37</v>
       </c>
       <c r="K50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;VLOOKUP(H50,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;VLOOKUP(H50,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,6);</v>
       </c>
     </row>
@@ -16365,7 +16400,7 @@
         <v>160</v>
       </c>
       <c r="K51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;VLOOKUP(H51,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;VLOOKUP(H51,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,1);</v>
       </c>
     </row>
@@ -16395,7 +16430,7 @@
         <v>160</v>
       </c>
       <c r="K52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;VLOOKUP(H52,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;VLOOKUP(H52,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,1);</v>
       </c>
     </row>
@@ -16425,7 +16460,7 @@
         <v>160</v>
       </c>
       <c r="K53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;VLOOKUP(H53,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;VLOOKUP(H53,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,1);</v>
       </c>
     </row>
@@ -16452,7 +16487,7 @@
         <v>161</v>
       </c>
       <c r="K54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;VLOOKUP(H54,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;VLOOKUP(H54,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,3);</v>
       </c>
     </row>
@@ -16479,7 +16514,7 @@
         <v>161</v>
       </c>
       <c r="K55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;VLOOKUP(H55,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;VLOOKUP(H55,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,3);</v>
       </c>
     </row>
@@ -16506,7 +16541,7 @@
         <v>34</v>
       </c>
       <c r="K56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;VLOOKUP(H56,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;VLOOKUP(H56,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,2);</v>
       </c>
     </row>
@@ -16533,7 +16568,7 @@
         <v>34</v>
       </c>
       <c r="K57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;VLOOKUP(H57,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;VLOOKUP(H57,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,2);</v>
       </c>
     </row>
@@ -16560,7 +16595,7 @@
         <v>35</v>
       </c>
       <c r="K58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;VLOOKUP(H58,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;VLOOKUP(H58,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,4);</v>
       </c>
     </row>
@@ -16590,7 +16625,7 @@
         <v>35</v>
       </c>
       <c r="K59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;VLOOKUP(H59,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;VLOOKUP(H59,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,4);</v>
       </c>
     </row>
@@ -16620,7 +16655,7 @@
         <v>35</v>
       </c>
       <c r="K60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;VLOOKUP(H60,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;VLOOKUP(H60,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,4);</v>
       </c>
     </row>
@@ -16647,7 +16682,7 @@
         <v>160</v>
       </c>
       <c r="K61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;VLOOKUP(H61,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;VLOOKUP(H61,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,1);</v>
       </c>
     </row>
@@ -16674,7 +16709,7 @@
         <v>160</v>
       </c>
       <c r="K62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;VLOOKUP(H62,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;VLOOKUP(H62,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,1);</v>
       </c>
     </row>
@@ -16701,7 +16736,7 @@
         <v>310</v>
       </c>
       <c r="K63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;VLOOKUP(H63,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;VLOOKUP(H63,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,2);</v>
       </c>
     </row>
@@ -16731,7 +16766,7 @@
         <v>34</v>
       </c>
       <c r="K64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;VLOOKUP(H64,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;VLOOKUP(H64,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,2);</v>
       </c>
     </row>
@@ -16761,7 +16796,7 @@
         <v>34</v>
       </c>
       <c r="K65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;VLOOKUP(H65,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;VLOOKUP(H65,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,2);</v>
       </c>
     </row>
@@ -16788,7 +16823,7 @@
         <v>34</v>
       </c>
       <c r="K66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;VLOOKUP(H66,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;VLOOKUP(H66,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,2);</v>
       </c>
     </row>
@@ -16818,7 +16853,7 @@
         <v>34</v>
       </c>
       <c r="K67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;VLOOKUP(H67,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;VLOOKUP(H67,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,2);</v>
       </c>
     </row>
@@ -16848,7 +16883,7 @@
         <v>161</v>
       </c>
       <c r="K68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;VLOOKUP(H68,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;VLOOKUP(H68,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,3);</v>
       </c>
     </row>
@@ -16878,7 +16913,7 @@
         <v>161</v>
       </c>
       <c r="K69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;VLOOKUP(H69,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;VLOOKUP(H69,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,3);</v>
       </c>
     </row>
@@ -16905,7 +16940,7 @@
         <v>36</v>
       </c>
       <c r="K70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;VLOOKUP(H70,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;VLOOKUP(H70,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,5);</v>
       </c>
     </row>
@@ -16932,7 +16967,7 @@
         <v>36</v>
       </c>
       <c r="K71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;VLOOKUP(H71,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;VLOOKUP(H71,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,5);</v>
       </c>
     </row>
@@ -16959,7 +16994,7 @@
         <v>36</v>
       </c>
       <c r="K72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;VLOOKUP(H72,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;VLOOKUP(H72,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,5);</v>
       </c>
     </row>
@@ -16986,7 +17021,7 @@
         <v>36</v>
       </c>
       <c r="K73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;VLOOKUP(H73,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;VLOOKUP(H73,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,5);</v>
       </c>
     </row>
@@ -17013,7 +17048,7 @@
         <v>161</v>
       </c>
       <c r="K74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;VLOOKUP(H74,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;VLOOKUP(H74,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,3);</v>
       </c>
     </row>
@@ -17040,7 +17075,7 @@
         <v>161</v>
       </c>
       <c r="K75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;VLOOKUP(H75,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;VLOOKUP(H75,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,3);</v>
       </c>
     </row>
@@ -17067,7 +17102,7 @@
         <v>34</v>
       </c>
       <c r="K76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;VLOOKUP(H76,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;VLOOKUP(H76,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,2);</v>
       </c>
     </row>
@@ -17094,7 +17129,7 @@
         <v>161</v>
       </c>
       <c r="K77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;VLOOKUP(H77,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;VLOOKUP(H77,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,3);</v>
       </c>
     </row>
@@ -17121,7 +17156,7 @@
         <v>36</v>
       </c>
       <c r="K78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;VLOOKUP(H78,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;VLOOKUP(H78,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,5);</v>
       </c>
     </row>
@@ -17148,7 +17183,7 @@
         <v>36</v>
       </c>
       <c r="K79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;VLOOKUP(H79,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;VLOOKUP(H79,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,5);</v>
       </c>
     </row>
@@ -17175,7 +17210,7 @@
         <v>37</v>
       </c>
       <c r="K80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;VLOOKUP(H80,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;VLOOKUP(H80,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,6);</v>
       </c>
     </row>
@@ -17202,7 +17237,7 @@
         <v>37</v>
       </c>
       <c r="K81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;VLOOKUP(H81,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;VLOOKUP(H81,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,6);</v>
       </c>
     </row>
@@ -17229,7 +17264,7 @@
         <v>36</v>
       </c>
       <c r="K82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;VLOOKUP(H82,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;VLOOKUP(H82,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,5);</v>
       </c>
     </row>
@@ -17258,7 +17293,7 @@
         <v>36</v>
       </c>
       <c r="K83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;VLOOKUP(H83,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;VLOOKUP(H83,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,5);</v>
       </c>
     </row>
@@ -17287,7 +17322,7 @@
         <v>36</v>
       </c>
       <c r="K84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;VLOOKUP(H84,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;VLOOKUP(H84,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,5);</v>
       </c>
     </row>
@@ -17314,7 +17349,7 @@
         <v>36</v>
       </c>
       <c r="K85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;VLOOKUP(H85,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;VLOOKUP(H85,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,5);</v>
       </c>
     </row>
@@ -17344,7 +17379,7 @@
         <v>36</v>
       </c>
       <c r="K86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;VLOOKUP(H86,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;VLOOKUP(H86,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,5);</v>
       </c>
     </row>
@@ -17374,7 +17409,7 @@
         <v>36</v>
       </c>
       <c r="K87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;VLOOKUP(H87,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;VLOOKUP(H87,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,5);</v>
       </c>
     </row>
@@ -17401,7 +17436,7 @@
         <v>161</v>
       </c>
       <c r="K88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;VLOOKUP(H88,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;VLOOKUP(H88,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,3);</v>
       </c>
     </row>
@@ -17428,7 +17463,7 @@
         <v>161</v>
       </c>
       <c r="K89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$47:$H$100,2,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;VLOOKUP(H89,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;$L$5&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$H$101,2,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;VLOOKUP(H89,コード!$C$5:$H$11,2,FALSE)&amp;");"</f>
         <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,3);</v>
       </c>
     </row>

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5A7A2E-7F06-40FD-89FE-7160D83A33C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96B0014-5BA2-4440-80DD-F578DDBAD990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="1172">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -5322,10 +5322,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>0.3</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>0.2</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -5455,6 +5451,14 @@
     <rPh sb="0" eb="3">
       <t>メイチュウリツ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill052</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.25</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9434,7 +9438,7 @@
         <v>153</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>1127</v>
@@ -9477,7 +9481,7 @@
       <c r="I5" s="19"/>
       <c r="J5" s="18"/>
       <c r="K5" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B5&amp;"'"&amp;","&amp;E5&amp;","&amp;"'"&amp;C5&amp;"'"&amp;","&amp;"'"&amp;D5&amp;"'"&amp;","&amp;"'"&amp;F5&amp;"'"&amp;","&amp;G5&amp;","&amp;H5&amp;","&amp;"'"&amp;I5&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K5:K11" si="0">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B5&amp;"'"&amp;","&amp;E5&amp;","&amp;"'"&amp;C5&amp;"'"&amp;","&amp;"'"&amp;D5&amp;"'"&amp;","&amp;"'"&amp;F5&amp;"'"&amp;","&amp;G5&amp;","&amp;H5&amp;","&amp;"'"&amp;I5&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code001',0,'無','','',0,0.0,'');</v>
       </c>
     </row>
@@ -9490,7 +9494,7 @@
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="8">
-        <f t="shared" ref="E6:E11" si="0">E5+1</f>
+        <f t="shared" ref="E6:E11" si="1">E5+1</f>
         <v>1</v>
       </c>
       <c r="F6" s="19"/>
@@ -9503,7 +9507,7 @@
       <c r="I6" s="19"/>
       <c r="J6" s="18"/>
       <c r="K6" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;E6&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;"'"&amp;D6&amp;"'"&amp;","&amp;"'"&amp;F6&amp;"'"&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;"'"&amp;I6&amp;"'"&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO m_code VALUES ('code001',1,'火','','',0,0.0,'');</v>
       </c>
     </row>
@@ -9516,7 +9520,7 @@
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F7" s="19"/>
@@ -9529,7 +9533,7 @@
       <c r="I7" s="19"/>
       <c r="J7" s="18"/>
       <c r="K7" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;E7&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;"'"&amp;D7&amp;"'"&amp;","&amp;"'"&amp;F7&amp;"'"&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;"'"&amp;I7&amp;"'"&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO m_code VALUES ('code001',2,'雷','','',0,0.0,'');</v>
       </c>
     </row>
@@ -9542,7 +9546,7 @@
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="F8" s="19"/>
@@ -9555,7 +9559,7 @@
       <c r="I8" s="19"/>
       <c r="J8" s="18"/>
       <c r="K8" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;E8&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;"'"&amp;D8&amp;"'"&amp;","&amp;"'"&amp;F8&amp;"'"&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;"'"&amp;I8&amp;"'"&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO m_code VALUES ('code001',3,'水','','',0,0.0,'');</v>
       </c>
     </row>
@@ -9568,7 +9572,7 @@
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="F9" s="19"/>
@@ -9581,7 +9585,7 @@
       <c r="I9" s="19"/>
       <c r="J9" s="18"/>
       <c r="K9" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;E9&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;"'"&amp;D9&amp;"'"&amp;","&amp;"'"&amp;F9&amp;"'"&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;"'"&amp;I9&amp;"'"&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO m_code VALUES ('code001',4,'土','','',0,0.0,'');</v>
       </c>
     </row>
@@ -9594,7 +9598,7 @@
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="F10" s="19"/>
@@ -9607,7 +9611,7 @@
       <c r="I10" s="19"/>
       <c r="J10" s="18"/>
       <c r="K10" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;E10&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;"'"&amp;D10&amp;"'"&amp;","&amp;"'"&amp;F10&amp;"'"&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;"'"&amp;I10&amp;"'"&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO m_code VALUES ('code001',5,'光','','',0,0.0,'');</v>
       </c>
     </row>
@@ -9620,7 +9624,7 @@
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="F11" s="19"/>
@@ -9633,7 +9637,7 @@
       <c r="I11" s="19"/>
       <c r="J11" s="18"/>
       <c r="K11" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;E11&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;"'"&amp;D11&amp;"'"&amp;","&amp;"'"&amp;F11&amp;"'"&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;"'"&amp;I11&amp;"'"&amp;");"</f>
+        <f t="shared" si="0"/>
         <v>INSERT INTO m_code VALUES ('code001',6,'闇','','',0,0.0,'');</v>
       </c>
     </row>
@@ -9642,7 +9646,7 @@
         <v>153</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>1127</v>
@@ -9685,10 +9689,10 @@
         <v>125</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K13" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;E13&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;"'"&amp;D13&amp;"'"&amp;","&amp;"'"&amp;F13&amp;"'"&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;"'"&amp;I13&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K13:K22" si="2">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;E13&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;"'"&amp;D13&amp;"'"&amp;","&amp;"'"&amp;F13&amp;"'"&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;"'"&amp;I13&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code002',0,'無','無','',0,0.0,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
@@ -9711,14 +9715,14 @@
         <v>132</v>
       </c>
       <c r="H14" s="9" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I14" s="19" t="s">
         <v>1153</v>
       </c>
-      <c r="I14" s="19" t="s">
-        <v>1154</v>
-      </c>
       <c r="K14" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;E14&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;"'"&amp;D14&amp;"'"&amp;","&amp;"'"&amp;F14&amp;"'"&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;"'"&amp;I14&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code002',1,'毒','毒','',0,0.2,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO m_code VALUES ('code002',1,'毒','毒','',0,0.25,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -9732,7 +9736,7 @@
         <v>1128</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" ref="E15:E20" si="1">E14+1</f>
+        <f t="shared" ref="E15:E20" si="3">E14+1</f>
         <v>2</v>
       </c>
       <c r="F15" s="19"/>
@@ -9743,10 +9747,10 @@
         <v>1149</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K15" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;E15&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;"'"&amp;D15&amp;"'"&amp;","&amp;"'"&amp;F15&amp;"'"&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;"'"&amp;I15&amp;"'"&amp;");"</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO m_code VALUES ('code002',2,'睡眠','眠','',0,0.8,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
@@ -9761,7 +9765,7 @@
         <v>1129</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="F16" s="19"/>
@@ -9772,10 +9776,10 @@
         <v>1150</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K16" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;E16&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;"'"&amp;D16&amp;"'"&amp;","&amp;"'"&amp;F16&amp;"'"&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;"'"&amp;I16&amp;"'"&amp;");"</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO m_code VALUES ('code002',3,'魅了','魅','',0,1.0,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
@@ -9790,7 +9794,7 @@
         <v>1130</v>
       </c>
       <c r="E17" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="F17" s="19"/>
@@ -9801,10 +9805,10 @@
         <v>1151</v>
       </c>
       <c r="I17" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K17" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;E17&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;"'"&amp;D17&amp;"'"&amp;","&amp;"'"&amp;F17&amp;"'"&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;"'"&amp;I17&amp;"'"&amp;");"</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO m_code VALUES ('code002',4,'スロー','遅','',0,0.5,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
@@ -9819,7 +9823,7 @@
         <v>1131</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F18" s="19"/>
@@ -9827,14 +9831,14 @@
         <v>132</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K18" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;E18&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;"'"&amp;D18&amp;"'"&amp;","&amp;"'"&amp;F18&amp;"'"&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;"'"&amp;I18&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code002',5,'攻撃力UP','攻↑','',0,0.5,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO m_code VALUES ('code002',5,'攻撃力UP','攻↑','',0,0.2,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
     <row r="19" spans="2:11">
@@ -9848,7 +9852,7 @@
         <v>1132</v>
       </c>
       <c r="E19" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="F19" s="19"/>
@@ -9856,14 +9860,14 @@
         <v>132</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I19" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K19" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;E19&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;"'"&amp;D19&amp;"'"&amp;","&amp;"'"&amp;F19&amp;"'"&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;"'"&amp;I19&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code002',6,'回避力UP','回↑','',0,0.5,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO m_code VALUES ('code002',6,'回避力UP','回↑','',0,0.2,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -9877,7 +9881,7 @@
         <v>1135</v>
       </c>
       <c r="E20" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="F20" s="19"/>
@@ -9885,14 +9889,14 @@
         <v>132</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K20" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;E20&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;"'"&amp;D20&amp;"'"&amp;","&amp;"'"&amp;F20&amp;"'"&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;"'"&amp;I20&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code002',7,'会心UP','会UP','',0,0.5,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO m_code VALUES ('code002',7,'会心UP','会UP','',0,0.2,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
     <row r="21" spans="2:11">
@@ -9917,11 +9921,11 @@
         <v>1152</v>
       </c>
       <c r="I21" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K21" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;E21&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;"'"&amp;D21&amp;"'"&amp;","&amp;"'"&amp;F21&amp;"'"&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;"'"&amp;I21&amp;"'"&amp;");"</f>
-        <v>INSERT INTO m_code VALUES ('code002',8,'自動回復','癒','',0,0.3,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
+        <f t="shared" si="2"/>
+        <v>INSERT INTO m_code VALUES ('code002',8,'自動回復','癒','',0,0.2,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
     <row r="22" spans="2:11">
@@ -9946,10 +9950,10 @@
         <v>1151</v>
       </c>
       <c r="I22" s="19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K22" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;E22&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;"'"&amp;D22&amp;"'"&amp;","&amp;"'"&amp;F22&amp;"'"&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;"'"&amp;I22&amp;"'"&amp;");"</f>
+        <f t="shared" si="2"/>
         <v>INSERT INTO m_code VALUES ('code002',9,'猛毒','猛','',0,0.5,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
@@ -9958,7 +9962,7 @@
         <v>153</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>1127</v>
@@ -10001,7 +10005,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="18"/>
       <c r="K24" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;E24&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;"'"&amp;D24&amp;"'"&amp;","&amp;"'"&amp;F24&amp;"'"&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;"'"&amp;I24&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K24:K32" si="4">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;E24&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;"'"&amp;D24&amp;"'"&amp;","&amp;"'"&amp;F24&amp;"'"&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;"'"&amp;I24&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code003',0,'無','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10027,7 +10031,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="18"/>
       <c r="K25" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;E25&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;"'"&amp;D25&amp;"'"&amp;","&amp;"'"&amp;F25&amp;"'"&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;"'"&amp;I25&amp;"'"&amp;");"</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO m_code VALUES ('code003',1,'敵ランダム','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10040,7 +10044,7 @@
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="8">
-        <f t="shared" ref="E26:E32" si="2">E25+1</f>
+        <f t="shared" ref="E26:E32" si="5">E25+1</f>
         <v>2</v>
       </c>
       <c r="F26" s="19"/>
@@ -10053,7 +10057,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="18"/>
       <c r="K26" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;E26&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;"'"&amp;D26&amp;"'"&amp;","&amp;"'"&amp;F26&amp;"'"&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;"'"&amp;I26&amp;"'"&amp;");"</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO m_code VALUES ('code003',2,'敵全体','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10066,7 +10070,7 @@
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="F27" s="19"/>
@@ -10079,7 +10083,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="18"/>
       <c r="K27" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;E27&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;"'"&amp;D27&amp;"'"&amp;","&amp;"'"&amp;F27&amp;"'"&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;"'"&amp;I27&amp;"'"&amp;");"</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO m_code VALUES ('code003',3,'敵ランダム・敵全体','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10092,7 +10096,7 @@
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="F28" s="19"/>
@@ -10105,7 +10109,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="18"/>
       <c r="K28" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;E28&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;"'"&amp;D28&amp;"'"&amp;","&amp;"'"&amp;F28&amp;"'"&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;"'"&amp;I28&amp;"'"&amp;");"</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO m_code VALUES ('code003',4,'敵ランダム・複数回','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10118,7 +10122,7 @@
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="F29" s="19"/>
@@ -10131,7 +10135,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="18"/>
       <c r="K29" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;E29&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;"'"&amp;D29&amp;"'"&amp;","&amp;"'"&amp;F29&amp;"'"&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;"'"&amp;I29&amp;"'"&amp;");"</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO m_code VALUES ('code003',5,'自身','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10144,7 +10148,7 @@
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="F30" s="19"/>
@@ -10157,7 +10161,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="18"/>
       <c r="K30" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;E30&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;"'"&amp;D30&amp;"'"&amp;","&amp;"'"&amp;F30&amp;"'"&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;"'"&amp;I30&amp;"'"&amp;");"</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO m_code VALUES ('code003',6,'味方ランダム','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10170,7 +10174,7 @@
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="F31" s="19"/>
@@ -10183,7 +10187,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="18"/>
       <c r="K31" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;E31&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;"'"&amp;D31&amp;"'"&amp;","&amp;"'"&amp;F31&amp;"'"&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;"'"&amp;I31&amp;"'"&amp;");"</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO m_code VALUES ('code003',7,'味方全体','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10196,7 +10200,7 @@
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="F32" s="19"/>
@@ -10209,7 +10213,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="18"/>
       <c r="K32" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;E32&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;"'"&amp;D32&amp;"'"&amp;","&amp;"'"&amp;F32&amp;"'"&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;"'"&amp;I32&amp;"'"&amp;");"</f>
+        <f t="shared" si="4"/>
         <v>INSERT INTO m_code VALUES ('code003',8,'味方ランダム・味方全体','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10218,7 +10222,7 @@
         <v>153</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>1127</v>
@@ -10263,7 +10267,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="18"/>
       <c r="K34" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;E34&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;"'"&amp;D34&amp;"'"&amp;","&amp;"'"&amp;F34&amp;"'"&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;"'"&amp;I34&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K34:K42" si="6">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;E34&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;"'"&amp;D34&amp;"'"&amp;","&amp;"'"&amp;F34&amp;"'"&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;"'"&amp;I34&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code004',0,'無','無','',0,0.0,'');</v>
       </c>
     </row>
@@ -10291,7 +10295,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="18"/>
       <c r="K35" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;E35&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;"'"&amp;D35&amp;"'"&amp;","&amp;"'"&amp;F35&amp;"'"&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;"'"&amp;I35&amp;"'"&amp;");"</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO m_code VALUES ('code004',1,'打撃攻撃','打','',0,0.0,'');</v>
       </c>
     </row>
@@ -10306,7 +10310,7 @@
         <v>1137</v>
       </c>
       <c r="E36" s="8">
-        <f t="shared" ref="E36:E42" si="3">E35+1</f>
+        <f t="shared" ref="E36:E42" si="7">E35+1</f>
         <v>2</v>
       </c>
       <c r="F36" s="19"/>
@@ -10319,7 +10323,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="18"/>
       <c r="K36" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;E36&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;"'"&amp;D36&amp;"'"&amp;","&amp;"'"&amp;F36&amp;"'"&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;"'"&amp;I36&amp;"'"&amp;");"</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO m_code VALUES ('code004',2,'斬撃攻撃','斬','',0,0.0,'');</v>
       </c>
     </row>
@@ -10334,7 +10338,7 @@
         <v>1138</v>
       </c>
       <c r="E37" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="F37" s="19"/>
@@ -10347,7 +10351,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="18"/>
       <c r="K37" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;E37&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;"'"&amp;D37&amp;"'"&amp;","&amp;"'"&amp;F37&amp;"'"&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;"'"&amp;I37&amp;"'"&amp;");"</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO m_code VALUES ('code004',3,'攻撃魔法','攻魔','',0,0.0,'');</v>
       </c>
     </row>
@@ -10362,7 +10366,7 @@
         <v>1139</v>
       </c>
       <c r="E38" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="F38" s="19"/>
@@ -10375,7 +10379,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="18"/>
       <c r="K38" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;E38&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;"'"&amp;D38&amp;"'"&amp;","&amp;"'"&amp;F38&amp;"'"&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;"'"&amp;I38&amp;"'"&amp;");"</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO m_code VALUES ('code004',4,'割合攻撃','割合','',0,0.0,'');</v>
       </c>
     </row>
@@ -10390,7 +10394,7 @@
         <v>1140</v>
       </c>
       <c r="E39" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="F39" s="19"/>
@@ -10403,7 +10407,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="18"/>
       <c r="K39" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;E39&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;"'"&amp;D39&amp;"'"&amp;","&amp;"'"&amp;F39&amp;"'"&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;"'"&amp;I39&amp;"'"&amp;");"</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO m_code VALUES ('code004',5,'即死攻撃','即死','',0,0.0,'');</v>
       </c>
     </row>
@@ -10418,7 +10422,7 @@
         <v>69</v>
       </c>
       <c r="E40" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="F40" s="19"/>
@@ -10431,7 +10435,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="18"/>
       <c r="K40" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;E40&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;"'"&amp;D40&amp;"'"&amp;","&amp;"'"&amp;F40&amp;"'"&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;"'"&amp;I40&amp;"'"&amp;");"</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO m_code VALUES ('code004',6,'回復','回復','',0,0.0,'');</v>
       </c>
     </row>
@@ -10446,7 +10450,7 @@
         <v>57</v>
       </c>
       <c r="E41" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="F41" s="19"/>
@@ -10459,7 +10463,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="18"/>
       <c r="K41" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;E41&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;"'"&amp;D41&amp;"'"&amp;","&amp;"'"&amp;F41&amp;"'"&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;"'"&amp;I41&amp;"'"&amp;");"</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO m_code VALUES ('code004',7,'状態','状態','',0,0.0,'');</v>
       </c>
     </row>
@@ -10474,7 +10478,7 @@
         <v>1141</v>
       </c>
       <c r="E42" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="F42" s="19"/>
@@ -10487,7 +10491,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="18"/>
       <c r="K42" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;E42&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;"'"&amp;D42&amp;"'"&amp;","&amp;"'"&amp;F42&amp;"'"&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;"'"&amp;I42&amp;"'"&amp;");"</f>
+        <f t="shared" si="6"/>
         <v>INSERT INTO m_code VALUES ('code004',8,'休み','休','',0,0.0,'');</v>
       </c>
     </row>
@@ -10496,7 +10500,7 @@
         <v>153</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>1127</v>
@@ -10600,7 +10604,7 @@
         <v>153</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>1127</v>
@@ -10643,7 +10647,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="18"/>
       <c r="K48" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;E48&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;"'"&amp;D48&amp;"'"&amp;","&amp;"'"&amp;F48&amp;"'"&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;"'"&amp;I48&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K48:K79" si="8">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;E48&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;"'"&amp;D48&amp;"'"&amp;","&amp;"'"&amp;F48&amp;"'"&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;"'"&amp;I48&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code006',1,'キラービー','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10669,7 +10673,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="18"/>
       <c r="K49" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;E49&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;"'"&amp;D49&amp;"'"&amp;","&amp;"'"&amp;F49&amp;"'"&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;"'"&amp;I49&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',2,'カーミラ','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10682,7 +10686,7 @@
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="8">
-        <f t="shared" ref="E50:E79" si="4">E49+1</f>
+        <f t="shared" ref="E50:E79" si="9">E49+1</f>
         <v>3</v>
       </c>
       <c r="F50" s="19"/>
@@ -10695,7 +10699,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="18"/>
       <c r="K50" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;E50&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;"'"&amp;D50&amp;"'"&amp;","&amp;"'"&amp;F50&amp;"'"&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;"'"&amp;I50&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',3,'デーモン','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10708,7 +10712,7 @@
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="F51" s="19"/>
@@ -10721,7 +10725,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="18"/>
       <c r="K51" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;E51&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;"'"&amp;D51&amp;"'"&amp;","&amp;"'"&amp;F51&amp;"'"&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;"'"&amp;I51&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',4,'ゴブリン','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10734,7 +10738,7 @@
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="F52" s="19"/>
@@ -10747,7 +10751,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="18"/>
       <c r="K52" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;E52&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;"'"&amp;D52&amp;"'"&amp;","&amp;"'"&amp;F52&amp;"'"&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;"'"&amp;I52&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',5,'マシンゴーレム','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10760,7 +10764,7 @@
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="F53" s="19"/>
@@ -10773,7 +10777,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="18"/>
       <c r="K53" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;E53&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;"'"&amp;D53&amp;"'"&amp;","&amp;"'"&amp;F53&amp;"'"&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;"'"&amp;I53&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',6,'ハーピー','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10786,7 +10790,7 @@
       </c>
       <c r="D54" s="19"/>
       <c r="E54" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="F54" s="19"/>
@@ -10799,7 +10803,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="18"/>
       <c r="K54" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;E54&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;"'"&amp;D54&amp;"'"&amp;","&amp;"'"&amp;F54&amp;"'"&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;"'"&amp;I54&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',7,'アーマーナイト','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10812,7 +10816,7 @@
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="F55" s="19"/>
@@ -10825,7 +10829,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="18"/>
       <c r="K55" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;E55&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;"'"&amp;D55&amp;"'"&amp;","&amp;"'"&amp;F55&amp;"'"&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;"'"&amp;I55&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',8,'マジシャン','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10838,7 +10842,7 @@
       </c>
       <c r="D56" s="19"/>
       <c r="E56" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="F56" s="19"/>
@@ -10851,7 +10855,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="18"/>
       <c r="K56" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;E56&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;"'"&amp;D56&amp;"'"&amp;","&amp;"'"&amp;F56&amp;"'"&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;"'"&amp;I56&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',9,'マイコニド','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10864,7 +10868,7 @@
       </c>
       <c r="D57" s="19"/>
       <c r="E57" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="F57" s="19"/>
@@ -10877,7 +10881,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="18"/>
       <c r="K57" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;E57&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;"'"&amp;D57&amp;"'"&amp;","&amp;"'"&amp;F57&amp;"'"&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;"'"&amp;I57&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',10,'ニードルバード','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10890,7 +10894,7 @@
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="F58" s="19"/>
@@ -10903,7 +10907,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="18"/>
       <c r="K58" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;E58&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;"'"&amp;D58&amp;"'"&amp;","&amp;"'"&amp;F58&amp;"'"&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;"'"&amp;I58&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',11,'プチドラゴン','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10916,7 +10920,7 @@
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="F59" s="19"/>
@@ -10929,7 +10933,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="18"/>
       <c r="K59" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;E59&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;"'"&amp;D59&amp;"'"&amp;","&amp;"'"&amp;F59&amp;"'"&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;"'"&amp;I59&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',12,'ポト','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10942,7 +10946,7 @@
       </c>
       <c r="D60" s="19"/>
       <c r="E60" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="F60" s="19"/>
@@ -10955,7 +10959,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="18"/>
       <c r="K60" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;E60&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;"'"&amp;D60&amp;"'"&amp;","&amp;"'"&amp;F60&amp;"'"&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;"'"&amp;I60&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',13,'プリースト','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10968,7 +10972,7 @@
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="F61" s="19"/>
@@ -10981,7 +10985,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="18"/>
       <c r="K61" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;E61&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;"'"&amp;D61&amp;"'"&amp;","&amp;"'"&amp;F61&amp;"'"&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;"'"&amp;I61&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',14,'ラビ','','',0,0.0,'');</v>
       </c>
     </row>
@@ -10994,7 +10998,7 @@
       </c>
       <c r="D62" s="19"/>
       <c r="E62" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="F62" s="19"/>
@@ -11007,7 +11011,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="18"/>
       <c r="K62" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;E62&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;"'"&amp;D62&amp;"'"&amp;","&amp;"'"&amp;F62&amp;"'"&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;"'"&amp;I62&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',15,'グリーンスライム','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11020,7 +11024,7 @@
       </c>
       <c r="D63" s="19"/>
       <c r="E63" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="F63" s="19"/>
@@ -11033,7 +11037,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="18"/>
       <c r="K63" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;E63&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;"'"&amp;D63&amp;"'"&amp;","&amp;"'"&amp;F63&amp;"'"&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;"'"&amp;I63&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',16,'イビルソード','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11046,7 +11050,7 @@
       </c>
       <c r="D64" s="19"/>
       <c r="E64" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="F64" s="19"/>
@@ -11058,7 +11062,7 @@
       </c>
       <c r="I64" s="19"/>
       <c r="K64" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;E64&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;"'"&amp;D64&amp;"'"&amp;","&amp;"'"&amp;F64&amp;"'"&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;"'"&amp;I64&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',17,'ウルフ','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11071,7 +11075,7 @@
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="F65" s="19"/>
@@ -11083,7 +11087,7 @@
       </c>
       <c r="I65" s="19"/>
       <c r="K65" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;E65&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;"'"&amp;D65&amp;"'"&amp;","&amp;"'"&amp;F65&amp;"'"&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;"'"&amp;I65&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',18,'ダック','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11096,7 +11100,7 @@
       </c>
       <c r="D66" s="19"/>
       <c r="E66" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="F66" s="19"/>
@@ -11108,7 +11112,7 @@
       </c>
       <c r="I66" s="19"/>
       <c r="K66" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;E66&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;"'"&amp;D66&amp;"'"&amp;","&amp;"'"&amp;F66&amp;"'"&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;"'"&amp;I66&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',19,'モールベア','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11121,7 +11125,7 @@
       </c>
       <c r="D67" s="19"/>
       <c r="E67" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="F67" s="19"/>
@@ -11133,7 +11137,7 @@
       </c>
       <c r="I67" s="19"/>
       <c r="K67" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;E67&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;"'"&amp;D67&amp;"'"&amp;","&amp;"'"&amp;F67&amp;"'"&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;"'"&amp;I67&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',20,'ギャルビー','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11146,7 +11150,7 @@
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="F68" s="19"/>
@@ -11158,7 +11162,7 @@
       </c>
       <c r="I68" s="19"/>
       <c r="K68" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;E68&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;"'"&amp;D68&amp;"'"&amp;","&amp;"'"&amp;F68&amp;"'"&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;"'"&amp;I68&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',21,'サハギン','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11171,7 +11175,7 @@
       </c>
       <c r="D69" s="19"/>
       <c r="E69" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
       <c r="F69" s="19"/>
@@ -11183,7 +11187,7 @@
       </c>
       <c r="I69" s="19"/>
       <c r="K69" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;E69&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;"'"&amp;D69&amp;"'"&amp;","&amp;"'"&amp;F69&amp;"'"&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;"'"&amp;I69&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',22,'クロウラー','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11196,7 +11200,7 @@
       </c>
       <c r="D70" s="19"/>
       <c r="E70" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
       <c r="F70" s="19"/>
@@ -11208,7 +11212,7 @@
       </c>
       <c r="I70" s="19"/>
       <c r="K70" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;E70&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;"'"&amp;D70&amp;"'"&amp;","&amp;"'"&amp;F70&amp;"'"&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;"'"&amp;I70&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',23,'パックン','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11221,7 +11225,7 @@
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="F71" s="19"/>
@@ -11233,7 +11237,7 @@
       </c>
       <c r="I71" s="19"/>
       <c r="K71" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;E71&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;"'"&amp;D71&amp;"'"&amp;","&amp;"'"&amp;F71&amp;"'"&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;"'"&amp;I71&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',24,'チビデビル','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11246,7 +11250,7 @@
       </c>
       <c r="D72" s="19"/>
       <c r="E72" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="F72" s="19"/>
@@ -11258,7 +11262,7 @@
       </c>
       <c r="I72" s="19"/>
       <c r="K72" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;E72&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;"'"&amp;D72&amp;"'"&amp;","&amp;"'"&amp;F72&amp;"'"&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;"'"&amp;I72&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',25,'オーガボックス','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11271,7 +11275,7 @@
       </c>
       <c r="D73" s="19"/>
       <c r="E73" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="F73" s="19"/>
@@ -11283,7 +11287,7 @@
       </c>
       <c r="I73" s="19"/>
       <c r="K73" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;E73&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;"'"&amp;D73&amp;"'"&amp;","&amp;"'"&amp;F73&amp;"'"&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;"'"&amp;I73&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',26,'バレッテ','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11296,7 +11300,7 @@
       </c>
       <c r="D74" s="19"/>
       <c r="E74" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="F74" s="19"/>
@@ -11308,7 +11312,7 @@
       </c>
       <c r="I74" s="19"/>
       <c r="K74" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;E74&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;"'"&amp;D74&amp;"'"&amp;","&amp;"'"&amp;F74&amp;"'"&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;"'"&amp;I74&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',27,'バシリスク','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11321,7 +11325,7 @@
       </c>
       <c r="D75" s="19"/>
       <c r="E75" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="F75" s="19"/>
@@ -11333,7 +11337,7 @@
       </c>
       <c r="I75" s="19"/>
       <c r="K75" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;E75&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;"'"&amp;D75&amp;"'"&amp;","&amp;"'"&amp;F75&amp;"'"&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;"'"&amp;I75&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',28,'スペクター','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11346,7 +11350,7 @@
       </c>
       <c r="D76" s="19"/>
       <c r="E76" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="F76" s="19"/>
@@ -11358,7 +11362,7 @@
       </c>
       <c r="I76" s="19"/>
       <c r="K76" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;E76&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;"'"&amp;D76&amp;"'"&amp;","&amp;"'"&amp;F76&amp;"'"&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;"'"&amp;I76&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',29,'ユニコーンヘッド','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11371,7 +11375,7 @@
       </c>
       <c r="D77" s="19"/>
       <c r="E77" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="F77" s="19"/>
@@ -11383,7 +11387,7 @@
       </c>
       <c r="I77" s="19"/>
       <c r="K77" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;E77&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;"'"&amp;D77&amp;"'"&amp;","&amp;"'"&amp;F77&amp;"'"&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;"'"&amp;I77&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',30,'シェイプシフター','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11396,7 +11400,7 @@
       </c>
       <c r="D78" s="19"/>
       <c r="E78" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>31</v>
       </c>
       <c r="F78" s="19"/>
@@ -11408,7 +11412,7 @@
       </c>
       <c r="I78" s="19"/>
       <c r="K78" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;E78&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;"'"&amp;D78&amp;"'"&amp;","&amp;"'"&amp;F78&amp;"'"&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;"'"&amp;I78&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',31,'ボルダー','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11421,7 +11425,7 @@
       </c>
       <c r="D79" s="19"/>
       <c r="E79" s="8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="F79" s="19"/>
@@ -11433,7 +11437,7 @@
       </c>
       <c r="I79" s="19"/>
       <c r="K79" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;E79&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;"'"&amp;D79&amp;"'"&amp;","&amp;"'"&amp;F79&amp;"'"&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;"'"&amp;I79&amp;"'"&amp;");"</f>
+        <f t="shared" si="8"/>
         <v>INSERT INTO m_code VALUES ('code006',32,'パンプキンボム','','',0,0.0,'');</v>
       </c>
     </row>
@@ -11442,7 +11446,7 @@
         <v>153</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>1127</v>
@@ -11485,7 +11489,7 @@
       </c>
       <c r="I81" s="19"/>
       <c r="K81" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;E81&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;"'"&amp;D81&amp;"'"&amp;","&amp;"'"&amp;F81&amp;"'"&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;"'"&amp;I81&amp;"'"&amp;");"</f>
+        <f t="shared" ref="K81:K87" si="10">"INSERT INTO m_code VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;E81&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;"'"&amp;D81&amp;"'"&amp;","&amp;"'"&amp;F81&amp;"'"&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;"'"&amp;I81&amp;"'"&amp;");"</f>
         <v>INSERT INTO m_code VALUES ('code007',1,'一般','一','',0,0.0,'');</v>
       </c>
     </row>
@@ -11511,7 +11515,7 @@
       </c>
       <c r="I82" s="19"/>
       <c r="K82" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;E82&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;"'"&amp;D82&amp;"'"&amp;","&amp;"'"&amp;F82&amp;"'"&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;"'"&amp;I82&amp;"'"&amp;");"</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO m_code VALUES ('code007',2,'優良','優','',0,0.0,'');</v>
       </c>
     </row>
@@ -11537,7 +11541,7 @@
       </c>
       <c r="I83" s="19"/>
       <c r="K83" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;E83&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;"'"&amp;D83&amp;"'"&amp;","&amp;"'"&amp;F83&amp;"'"&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;"'"&amp;I83&amp;"'"&amp;");"</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO m_code VALUES ('code007',3,'カモ','カ','',0,0.0,'');</v>
       </c>
     </row>
@@ -11563,7 +11567,7 @@
       </c>
       <c r="I84" s="19"/>
       <c r="K84" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;E84&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;"'"&amp;D84&amp;"'"&amp;","&amp;"'"&amp;F84&amp;"'"&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;"'"&amp;I84&amp;"'"&amp;");"</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO m_code VALUES ('code007',4,'要注意','要','',0,0.0,'');</v>
       </c>
     </row>
@@ -11589,7 +11593,7 @@
       </c>
       <c r="I85" s="19"/>
       <c r="K85" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;E85&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;"'"&amp;D85&amp;"'"&amp;","&amp;"'"&amp;F85&amp;"'"&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;"'"&amp;I85&amp;"'"&amp;");"</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO m_code VALUES ('code007',5,'ブラックリスト','ブ','',0,0.0,'');</v>
       </c>
     </row>
@@ -11615,7 +11619,7 @@
       </c>
       <c r="I86" s="19"/>
       <c r="K86" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;E86&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;"'"&amp;D86&amp;"'"&amp;","&amp;"'"&amp;F86&amp;"'"&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;"'"&amp;I86&amp;"'"&amp;");"</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO m_code VALUES ('code007',90,'管理者','管','',0,0.0,'');</v>
       </c>
     </row>
@@ -11641,7 +11645,7 @@
       </c>
       <c r="I87" s="19"/>
       <c r="K87" s="5" t="str">
-        <f>"INSERT INTO m_code VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;E87&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;"'"&amp;D87&amp;"'"&amp;","&amp;"'"&amp;F87&amp;"'"&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;"'"&amp;I87&amp;"'"&amp;");"</f>
+        <f t="shared" si="10"/>
         <v>INSERT INTO m_code VALUES ('code007',91,'統括管理者','統','',0,0.0,'');</v>
       </c>
     </row>
@@ -11650,7 +11654,7 @@
         <v>153</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>1127</v>
@@ -11808,7 +11812,7 @@
         <v>124</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="N3" s="12" t="s">
         <v>191</v>
@@ -14887,13 +14891,13 @@
         <v>89</v>
       </c>
       <c r="G75" s="8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="I75" s="8" t="s">
         <v>1168</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>1168</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>1169</v>
       </c>
       <c r="J75" s="26">
         <v>100</v>
@@ -14936,7 +14940,7 @@
         <v>128</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J76" s="26">
         <v>15</v>
@@ -14973,13 +14977,13 @@
         <v>91</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H77" s="13" t="s">
         <v>128</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J77" s="26">
         <v>15</v>
@@ -15016,13 +15020,13 @@
         <v>91</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="H78" s="13" t="s">
         <v>128</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J78" s="26">
         <v>15</v>
@@ -15059,13 +15063,13 @@
         <v>91</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="H79" s="13" t="s">
         <v>128</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J79" s="26">
         <v>15</v>
@@ -15102,13 +15106,13 @@
         <v>91</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H80" s="13" t="s">
         <v>128</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J80" s="26">
         <v>15</v>
@@ -15145,13 +15149,13 @@
         <v>91</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="H81" s="13" t="s">
         <v>128</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="J81" s="26">
         <v>15</v>
@@ -18162,7 +18166,7 @@
       </c>
       <c r="M13" s="21">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N13" s="45"/>
       <c r="O13" s="1" t="str">
@@ -18204,7 +18208,7 @@
       </c>
       <c r="M14" s="21">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N14" s="45"/>
       <c r="O14" s="1" t="str">
@@ -18330,7 +18334,7 @@
       </c>
       <c r="M17" s="21">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N17" s="45"/>
       <c r="O17" s="1" t="str">
@@ -19564,7 +19568,7 @@
         <v>428</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>1017</v>
+        <v>1170</v>
       </c>
       <c r="E47" s="21" t="b">
         <v>0</v>
@@ -19575,11 +19579,11 @@
       </c>
       <c r="H47" s="24">
         <f>VLOOKUP(D47,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I47" s="25" t="str">
         <f>VLOOKUP(D47,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>斬撃</v>
+        <v>バーサク</v>
       </c>
       <c r="K47" s="43" t="s">
         <v>1029</v>
@@ -19595,7 +19599,7 @@
       <c r="N47" s="45"/>
       <c r="O47" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0043','monster008','skill009',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0043','monster008','skill052',FALSE);</v>
       </c>
     </row>
     <row r="48" spans="2:15">
@@ -19968,7 +19972,7 @@
       </c>
       <c r="M56" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N56" s="45"/>
       <c r="O56" s="1" t="str">
@@ -19984,7 +19988,7 @@
         <v>429</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>1026</v>
+        <v>1170</v>
       </c>
       <c r="E57" s="21" t="b">
         <v>0</v>
@@ -19993,13 +19997,13 @@
         <f>VLOOKUP(C57,モンスター!$B$6:$H$100,2,FALSE)</f>
         <v>ゴブリンガード</v>
       </c>
-      <c r="H57" s="24" t="str">
+      <c r="H57" s="24">
         <f>VLOOKUP(D57,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I57" s="25" t="str">
         <f>VLOOKUP(D57,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>薙ぎ払い</v>
+        <v>バーサク</v>
       </c>
       <c r="K57" s="43" t="s">
         <v>1084</v>
@@ -20015,7 +20019,7 @@
       <c r="N57" s="45"/>
       <c r="O57" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0053','monster009','skill013',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0053','monster009','skill052',FALSE);</v>
       </c>
     </row>
     <row r="58" spans="2:15">
@@ -20236,7 +20240,7 @@
         <v>430</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>1025</v>
+        <v>1170</v>
       </c>
       <c r="E63" s="21" t="b">
         <v>0</v>
@@ -20247,11 +20251,11 @@
       </c>
       <c r="H63" s="24">
         <f>VLOOKUP(D63,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I63" s="25" t="str">
         <f>VLOOKUP(D63,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>剣の舞</v>
+        <v>バーサク</v>
       </c>
       <c r="K63" s="43" t="s">
         <v>1070</v>
@@ -20267,7 +20271,7 @@
       <c r="N63" s="45"/>
       <c r="O63" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0059','monster010','skill010',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0059','monster010','skill052',FALSE);</v>
       </c>
     </row>
     <row r="64" spans="2:15">

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96B0014-5BA2-4440-80DD-F578DDBAD990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D62524D-34DD-4EC7-88C4-1C95DB93EBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3062" uniqueCount="1174">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -5459,6 +5459,14 @@
   </si>
   <si>
     <t>0.25</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill054</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill026</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -17830,7 +17838,7 @@
       </c>
       <c r="M5" s="21">
         <f>COUNTIF($D$5:$D$1000,K5)</f>
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N5" s="45"/>
       <c r="O5" s="1" t="str">
@@ -17888,7 +17896,7 @@
         <v>419</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>1017</v>
+        <v>1172</v>
       </c>
       <c r="E7" s="21" t="b">
         <v>0</v>
@@ -17899,11 +17907,11 @@
       </c>
       <c r="H7" s="24">
         <f>VLOOKUP(D7,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I7" s="25" t="str">
         <f>VLOOKUP(D7,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>斬撃</v>
+        <v>エナジーボール</v>
       </c>
       <c r="K7" s="43" t="s">
         <v>1065</v>
@@ -17918,8 +17926,8 @@
       </c>
       <c r="N7" s="45"/>
       <c r="O7" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0003','monster001','skill009',FALSE);</v>
+        <f>"INSERT INTO m_my_skills VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;"'"&amp;D7&amp;"'"&amp;","&amp;E7&amp;");"</f>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0003','monster001','skill054',FALSE);</v>
       </c>
     </row>
     <row r="8" spans="2:15">
@@ -17998,7 +18006,7 @@
       </c>
       <c r="M9" s="21">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N9" s="45"/>
       <c r="O9" s="1" t="str">
@@ -18166,7 +18174,7 @@
       </c>
       <c r="M13" s="21">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N13" s="45"/>
       <c r="O13" s="1" t="str">
@@ -18182,7 +18190,7 @@
         <v>421</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>1021</v>
+        <v>1172</v>
       </c>
       <c r="E14" s="21" t="b">
         <v>0</v>
@@ -18191,13 +18199,13 @@
         <f>VLOOKUP(C14,モンスター!$B$6:$H$100,2,FALSE)</f>
         <v>アサシンバグ</v>
       </c>
-      <c r="H14" s="24" t="str">
+      <c r="H14" s="24">
         <f>VLOOKUP(D14,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I14" s="25" t="str">
         <f>VLOOKUP(D14,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>回し蹴り</v>
+        <v>エナジーボール</v>
       </c>
       <c r="K14" s="43" t="s">
         <v>1025</v>
@@ -18213,7 +18221,7 @@
       <c r="N14" s="45"/>
       <c r="O14" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0010','monster002','skill005',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0010','monster002','skill054',FALSE);</v>
       </c>
     </row>
     <row r="15" spans="2:15">
@@ -18350,7 +18358,7 @@
         <v>423</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>1017</v>
+        <v>1172</v>
       </c>
       <c r="E18" s="21" t="b">
         <v>0</v>
@@ -18361,11 +18369,11 @@
       </c>
       <c r="H18" s="24">
         <f>VLOOKUP(D18,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I18" s="25" t="str">
         <f>VLOOKUP(D18,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>斬撃</v>
+        <v>エナジーボール</v>
       </c>
       <c r="K18" s="43" t="s">
         <v>1048</v>
@@ -18381,7 +18389,7 @@
       <c r="N18" s="45"/>
       <c r="O18" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0014','monster003','skill009',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0014','monster003','skill054',FALSE);</v>
       </c>
     </row>
     <row r="19" spans="2:15">
@@ -18628,7 +18636,7 @@
       </c>
       <c r="M24" s="21">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N24" s="45"/>
       <c r="O24" s="1" t="str">
@@ -18880,7 +18888,7 @@
       </c>
       <c r="M30" s="21">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N30" s="45"/>
       <c r="O30" s="1" t="str">
@@ -19972,7 +19980,7 @@
       </c>
       <c r="M56" s="21">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N56" s="45"/>
       <c r="O56" s="1" t="str">
@@ -20056,7 +20064,7 @@
       </c>
       <c r="M58" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N58" s="45"/>
       <c r="O58" s="1" t="str">
@@ -20266,7 +20274,7 @@
       </c>
       <c r="M63" s="21">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N63" s="45"/>
       <c r="O63" s="1" t="str">
@@ -20308,7 +20316,7 @@
       </c>
       <c r="M64" s="21">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N64" s="45"/>
       <c r="O64" s="1" t="str">
@@ -20686,7 +20694,7 @@
       </c>
       <c r="M73" s="21">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73" s="45"/>
       <c r="O73" s="1" t="str">
@@ -27293,7 +27301,7 @@
         <v>467</v>
       </c>
       <c r="D282" s="21" t="s">
-        <v>1070</v>
+        <v>1172</v>
       </c>
       <c r="E282" s="21" t="b">
         <v>0</v>
@@ -27304,16 +27312,16 @@
       </c>
       <c r="H282" s="24">
         <f>VLOOKUP(D282,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I282" s="25" t="str">
         <f>VLOOKUP(D282,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>喰いちぎり</v>
+        <v>エナジーボール</v>
       </c>
       <c r="N282" s="45"/>
       <c r="O282" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0278','monster047','skill059',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0278','monster047','skill054',FALSE);</v>
       </c>
     </row>
     <row r="283" spans="2:15">
@@ -27541,7 +27549,7 @@
         <v>468</v>
       </c>
       <c r="D290" s="21" t="s">
-        <v>1073</v>
+        <v>1172</v>
       </c>
       <c r="E290" s="21" t="b">
         <v>0</v>
@@ -27552,16 +27560,16 @@
       </c>
       <c r="H290" s="24">
         <f>VLOOKUP(D290,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I290" s="25" t="str">
         <f>VLOOKUP(D290,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>首狩り</v>
+        <v>エナジーボール</v>
       </c>
       <c r="N290" s="45"/>
       <c r="O290" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0286','monster048','skill069',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0286','monster048','skill054',FALSE);</v>
       </c>
     </row>
     <row r="291" spans="2:15">
@@ -28130,7 +28138,7 @@
         <v>471</v>
       </c>
       <c r="D309" s="21" t="s">
-        <v>1017</v>
+        <v>1170</v>
       </c>
       <c r="E309" s="21" t="b">
         <v>0</v>
@@ -28141,16 +28149,16 @@
       </c>
       <c r="H309" s="24">
         <f>VLOOKUP(D309,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I309" s="25" t="str">
         <f>VLOOKUP(D309,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>斬撃</v>
+        <v>バーサク</v>
       </c>
       <c r="N309" s="45"/>
       <c r="O309" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0305','monster051','skill009',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0305','monster051','skill052',FALSE);</v>
       </c>
     </row>
     <row r="310" spans="2:15">
@@ -28223,7 +28231,7 @@
         <v>472</v>
       </c>
       <c r="D312" s="21" t="s">
-        <v>1072</v>
+        <v>1170</v>
       </c>
       <c r="E312" s="21" t="b">
         <v>0</v>
@@ -28234,16 +28242,16 @@
       </c>
       <c r="H312" s="24">
         <f>VLOOKUP(D312,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I312" s="25" t="str">
         <f>VLOOKUP(D312,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>タックル</v>
+        <v>バーサク</v>
       </c>
       <c r="N312" s="45"/>
       <c r="O312" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0308','monster052','skill060',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0308','monster052','skill052',FALSE);</v>
       </c>
     </row>
     <row r="313" spans="2:15">
@@ -31447,7 +31455,7 @@
         <v>489</v>
       </c>
       <c r="D416" s="21" t="s">
-        <v>1041</v>
+        <v>1172</v>
       </c>
       <c r="E416" s="21" t="b">
         <v>0</v>
@@ -31458,16 +31466,16 @@
       </c>
       <c r="H416" s="24">
         <f>VLOOKUP(D416,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I416" s="25" t="str">
         <f>VLOOKUP(D416,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>打撃</v>
+        <v>エナジーボール</v>
       </c>
       <c r="N416" s="45"/>
       <c r="O416" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0412','monster069','skill001',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0412','monster069','skill054',FALSE);</v>
       </c>
     </row>
     <row r="417" spans="2:15">
@@ -31540,7 +31548,7 @@
         <v>489</v>
       </c>
       <c r="D419" s="21" t="s">
-        <v>1028</v>
+        <v>1173</v>
       </c>
       <c r="E419" s="21" t="b">
         <v>0</v>
@@ -31555,12 +31563,12 @@
       </c>
       <c r="I419" s="25" t="str">
         <f>VLOOKUP(D419,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>アイススマッシュ</v>
+        <v>ダイヤミサイル</v>
       </c>
       <c r="N419" s="45"/>
       <c r="O419" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0415','monster069','skill020',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0415','monster069','skill026',FALSE);</v>
       </c>
     </row>
     <row r="420" spans="2:15">
@@ -31602,7 +31610,7 @@
         <v>490</v>
       </c>
       <c r="D421" s="21" t="s">
-        <v>1072</v>
+        <v>1172</v>
       </c>
       <c r="E421" s="21" t="b">
         <v>0</v>
@@ -31613,16 +31621,16 @@
       </c>
       <c r="H421" s="24">
         <f>VLOOKUP(D421,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I421" s="25" t="str">
         <f>VLOOKUP(D421,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>タックル</v>
+        <v>エナジーボール</v>
       </c>
       <c r="N421" s="45"/>
       <c r="O421" s="1" t="str">
         <f t="shared" si="8"/>
-        <v>INSERT INTO m_my_skills VALUES ('myskill0417','monster070','skill060',FALSE);</v>
+        <v>INSERT INTO m_my_skills VALUES ('myskill0417','monster070','skill054',FALSE);</v>
       </c>
     </row>
     <row r="422" spans="2:15">

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E90D75-69F3-4FF5-8A41-A9D362D9512E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC50D5E5-EABF-470A-98CD-1399AB41B761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
@@ -5638,7 +5638,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5744,6 +5744,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15323,13 +15329,15 @@
       <c r="G6" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="10"/>
+      <c r="H6" s="56">
+        <v>0.3</v>
+      </c>
       <c r="I6" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L6" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B6&amp;"'"&amp;","&amp;"'"&amp;C6&amp;"'"&amp;","&amp;VLOOKUP(D6,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E6&amp;","&amp;F6&amp;","&amp;G6&amp;","&amp;H6&amp;","&amp;VLOOKUP(I6,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster001','キラービー',1,110,12,16,0.3,1);</v>
       </c>
     </row>
     <row r="7" spans="2:17">
@@ -15354,13 +15362,15 @@
         <f>ROUNDDOWN(G6*1.3,0)</f>
         <v>20</v>
       </c>
-      <c r="H7" s="10"/>
+      <c r="H7" s="56">
+        <v>0.3</v>
+      </c>
       <c r="I7" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L7" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B7&amp;"'"&amp;","&amp;"'"&amp;C7&amp;"'"&amp;","&amp;VLOOKUP(D7,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E7&amp;","&amp;F7&amp;","&amp;G7&amp;","&amp;H7&amp;","&amp;VLOOKUP(I7,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster002','アサシンバグ',1,132,15,20,0.3,1);</v>
       </c>
     </row>
     <row r="8" spans="2:17">
@@ -15385,13 +15395,15 @@
         <f>ROUNDDOWN(G7*1.3,0)</f>
         <v>26</v>
       </c>
-      <c r="H8" s="10"/>
+      <c r="H8" s="56">
+        <v>0.3</v>
+      </c>
       <c r="I8" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L8" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B8&amp;"'"&amp;","&amp;"'"&amp;C8&amp;"'"&amp;","&amp;VLOOKUP(D8,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E8&amp;","&amp;F8&amp;","&amp;G8&amp;","&amp;H8&amp;","&amp;VLOOKUP(I8,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster003','ラスターバグ',1,158,19,26,0.3,1);</v>
       </c>
     </row>
     <row r="9" spans="2:17">
@@ -15413,13 +15425,15 @@
       <c r="G9" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="H9" s="10"/>
+      <c r="H9" s="56">
+        <v>0.13</v>
+      </c>
       <c r="I9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B9&amp;"'"&amp;","&amp;"'"&amp;C9&amp;"'"&amp;","&amp;VLOOKUP(D9,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E9&amp;","&amp;F9&amp;","&amp;G9&amp;","&amp;H9&amp;","&amp;VLOOKUP(I9,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster004','カーミラ',2,100,10,13,0.13,2);</v>
       </c>
     </row>
     <row r="10" spans="2:17">
@@ -15444,13 +15458,15 @@
         <f>ROUNDDOWN(G9*1.3,0)</f>
         <v>16</v>
       </c>
-      <c r="H10" s="10"/>
+      <c r="H10" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I10" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L10" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B10&amp;"'"&amp;","&amp;"'"&amp;C10&amp;"'"&amp;","&amp;VLOOKUP(D10,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E10&amp;","&amp;F10&amp;","&amp;G10&amp;","&amp;H10&amp;","&amp;VLOOKUP(I10,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster005','カーミラクイーン',2,120,13,16,0.15,2);</v>
       </c>
     </row>
     <row r="11" spans="2:17">
@@ -15472,13 +15488,15 @@
       <c r="G11" s="10">
         <v>7</v>
       </c>
-      <c r="H11" s="10"/>
+      <c r="H11" s="56">
+        <v>0.08</v>
+      </c>
       <c r="I11" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L11" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B11&amp;"'"&amp;","&amp;"'"&amp;C11&amp;"'"&amp;","&amp;VLOOKUP(D11,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E11&amp;","&amp;F11&amp;","&amp;G11&amp;","&amp;H11&amp;","&amp;VLOOKUP(I11,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster006','デーモン',3,130,15,7,0.08,5);</v>
       </c>
     </row>
     <row r="12" spans="2:17">
@@ -15503,13 +15521,15 @@
         <f>ROUNDDOWN(G11*1.3,0)</f>
         <v>9</v>
       </c>
-      <c r="H12" s="10"/>
+      <c r="H12" s="56">
+        <v>0.1</v>
+      </c>
       <c r="I12" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L12" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B12&amp;"'"&amp;","&amp;"'"&amp;C12&amp;"'"&amp;","&amp;VLOOKUP(D12,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E12&amp;","&amp;F12&amp;","&amp;G12&amp;","&amp;H12&amp;","&amp;VLOOKUP(I12,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster007','グレートデーモン',3,156,19,9,0.1,5);</v>
       </c>
     </row>
     <row r="13" spans="2:17">
@@ -15531,13 +15551,15 @@
       <c r="G13" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="10"/>
+      <c r="H13" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I13" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B13&amp;"'"&amp;","&amp;"'"&amp;C13&amp;"'"&amp;","&amp;VLOOKUP(D13,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E13&amp;","&amp;F13&amp;","&amp;G13&amp;","&amp;H13&amp;","&amp;VLOOKUP(I13,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster008','ゴブリン',4,120,11,10,0.15,4);</v>
       </c>
     </row>
     <row r="14" spans="2:17">
@@ -15562,13 +15584,15 @@
         <f>ROUNDDOWN(G13*1.3,0)</f>
         <v>13</v>
       </c>
-      <c r="H14" s="10"/>
+      <c r="H14" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I14" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L14" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B14&amp;"'"&amp;","&amp;"'"&amp;C14&amp;"'"&amp;","&amp;VLOOKUP(D14,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E14&amp;","&amp;F14&amp;","&amp;G14&amp;","&amp;H14&amp;","&amp;VLOOKUP(I14,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster009','ゴブリンガード',4,144,14,13,0.15,4);</v>
       </c>
     </row>
     <row r="15" spans="2:17">
@@ -15593,13 +15617,15 @@
         <f>ROUNDDOWN(G14*1.3,0)</f>
         <v>16</v>
       </c>
-      <c r="H15" s="10"/>
+      <c r="H15" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I15" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L15" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B15&amp;"'"&amp;","&amp;"'"&amp;C15&amp;"'"&amp;","&amp;VLOOKUP(D15,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E15&amp;","&amp;F15&amp;","&amp;G15&amp;","&amp;H15&amp;","&amp;VLOOKUP(I15,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster010','ゴブリンロード',4,172,18,16,0.15,4);</v>
       </c>
     </row>
     <row r="16" spans="2:17">
@@ -15621,13 +15647,15 @@
       <c r="G16" s="10">
         <v>5</v>
       </c>
-      <c r="H16" s="10"/>
+      <c r="H16" s="56">
+        <v>0.02</v>
+      </c>
       <c r="I16" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L16" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B16&amp;"'"&amp;","&amp;"'"&amp;C16&amp;"'"&amp;","&amp;VLOOKUP(D16,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E16&amp;","&amp;F16&amp;","&amp;G16&amp;","&amp;H16&amp;","&amp;VLOOKUP(I16,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster011','マシンゴーレム',5,140,17,5,0.02,3);</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -15652,13 +15680,15 @@
         <f>ROUNDDOWN(G16*1.3,0)</f>
         <v>6</v>
       </c>
-      <c r="H17" s="10"/>
+      <c r="H17" s="56">
+        <v>0.04</v>
+      </c>
       <c r="I17" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L17" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B17&amp;"'"&amp;","&amp;"'"&amp;C17&amp;"'"&amp;","&amp;VLOOKUP(D17,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E17&amp;","&amp;F17&amp;","&amp;G17&amp;","&amp;H17&amp;","&amp;VLOOKUP(I17,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster012','ガーディアン',5,168,22,6,0.04,3);</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -15683,13 +15713,15 @@
         <f>ROUNDDOWN(G17*1.3,0)</f>
         <v>7</v>
       </c>
-      <c r="H18" s="10"/>
+      <c r="H18" s="56">
+        <v>0.05</v>
+      </c>
       <c r="I18" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L18" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B18&amp;"'"&amp;","&amp;"'"&amp;C18&amp;"'"&amp;","&amp;VLOOKUP(D18,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E18&amp;","&amp;F18&amp;","&amp;G18&amp;","&amp;H18&amp;","&amp;VLOOKUP(I18,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster013','デスマシン',5,201,28,7,0.05,3);</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -15711,13 +15743,15 @@
       <c r="G19" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="H19" s="10"/>
+      <c r="H19" s="56">
+        <v>0.2</v>
+      </c>
       <c r="I19" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L19" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B19&amp;"'"&amp;","&amp;"'"&amp;C19&amp;"'"&amp;","&amp;VLOOKUP(D19,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E19&amp;","&amp;F19&amp;","&amp;G19&amp;","&amp;H19&amp;","&amp;VLOOKUP(I19,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster014','ハーピー',6,100,8,14,0.2,4);</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -15742,13 +15776,15 @@
         <f>ROUNDDOWN(G19*1.3,0)</f>
         <v>18</v>
       </c>
-      <c r="H20" s="10"/>
+      <c r="H20" s="56">
+        <v>0.23</v>
+      </c>
       <c r="I20" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L20" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B20&amp;"'"&amp;","&amp;"'"&amp;C20&amp;"'"&amp;","&amp;VLOOKUP(D20,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E20&amp;","&amp;F20&amp;","&amp;G20&amp;","&amp;H20&amp;","&amp;VLOOKUP(I20,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster015','セイレーン',6,120,10,18,0.23,4);</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -15770,13 +15806,15 @@
       <c r="G21" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="H21" s="10"/>
+      <c r="H21" s="56">
+        <v>0.05</v>
+      </c>
       <c r="I21" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L21" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B21&amp;"'"&amp;","&amp;"'"&amp;C21&amp;"'"&amp;","&amp;VLOOKUP(D21,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E21&amp;","&amp;F21&amp;","&amp;G21&amp;","&amp;H21&amp;","&amp;VLOOKUP(I21,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster016','アーマーナイト',7,120,13,8,0.05,2);</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -15801,13 +15839,15 @@
         <f>ROUNDDOWN(G21*1.3,0)</f>
         <v>10</v>
       </c>
-      <c r="H22" s="10"/>
+      <c r="H22" s="56">
+        <v>0.05</v>
+      </c>
       <c r="I22" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L22" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B22&amp;"'"&amp;","&amp;"'"&amp;C22&amp;"'"&amp;","&amp;VLOOKUP(D22,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E22&amp;","&amp;F22&amp;","&amp;G22&amp;","&amp;H22&amp;","&amp;VLOOKUP(I22,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster017','ダークナイト',7,144,16,10,0.05,2);</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -15832,13 +15872,15 @@
         <f>ROUNDDOWN(G22*1.3,0)</f>
         <v>13</v>
       </c>
-      <c r="H23" s="10"/>
+      <c r="H23" s="56">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="I23" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L23" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B23&amp;"'"&amp;","&amp;"'"&amp;C23&amp;"'"&amp;","&amp;VLOOKUP(D23,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E23&amp;","&amp;F23&amp;","&amp;G23&amp;","&amp;H23&amp;","&amp;VLOOKUP(I23,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster018','ターミネータ',7,172,20,13,0.07,2);</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -15860,13 +15902,15 @@
       <c r="G24" s="10">
         <v>12</v>
       </c>
-      <c r="H24" s="10"/>
+      <c r="H24" s="56">
+        <v>0.1</v>
+      </c>
       <c r="I24" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L24" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B24&amp;"'"&amp;","&amp;"'"&amp;C24&amp;"'"&amp;","&amp;VLOOKUP(D24,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E24&amp;","&amp;F24&amp;","&amp;G24&amp;","&amp;H24&amp;","&amp;VLOOKUP(I24,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster019','マジシャン',8,100,9,12,0.1,4);</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -15891,13 +15935,15 @@
         <f>ROUNDDOWN(G24*1.3,0)</f>
         <v>15</v>
       </c>
-      <c r="H25" s="10"/>
+      <c r="H25" s="56">
+        <v>0.11</v>
+      </c>
       <c r="I25" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L25" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B25&amp;"'"&amp;","&amp;"'"&amp;C25&amp;"'"&amp;","&amp;VLOOKUP(D25,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E25&amp;","&amp;F25&amp;","&amp;G25&amp;","&amp;H25&amp;","&amp;VLOOKUP(I25,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster020','ウィザード',8,120,11,15,0.11,4);</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -15922,13 +15968,15 @@
         <f>ROUNDDOWN(G25*1.3,0)</f>
         <v>19</v>
       </c>
-      <c r="H26" s="10"/>
+      <c r="H26" s="56">
+        <v>0.12</v>
+      </c>
       <c r="I26" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L26" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B26&amp;"'"&amp;","&amp;"'"&amp;C26&amp;"'"&amp;","&amp;VLOOKUP(D26,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E26&amp;","&amp;F26&amp;","&amp;G26&amp;","&amp;H26&amp;","&amp;VLOOKUP(I26,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster021','ハイウィザード',8,144,14,19,0.12,4);</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -15950,13 +15998,15 @@
       <c r="G27" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="H27" s="10"/>
+      <c r="H27" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I27" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L27" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B27&amp;"'"&amp;","&amp;"'"&amp;C27&amp;"'"&amp;","&amp;VLOOKUP(D27,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E27&amp;","&amp;F27&amp;","&amp;G27&amp;","&amp;H27&amp;","&amp;VLOOKUP(I27,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster022','マイコニド',9,120,10,12,0.15,1);</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -15981,13 +16031,15 @@
         <f>ROUNDDOWN(G27*1.3,0)</f>
         <v>15</v>
       </c>
-      <c r="H28" s="10"/>
+      <c r="H28" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I28" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L28" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B28&amp;"'"&amp;","&amp;"'"&amp;C28&amp;"'"&amp;","&amp;VLOOKUP(D28,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E28&amp;","&amp;F28&amp;","&amp;G28&amp;","&amp;H28&amp;","&amp;VLOOKUP(I28,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster023','ダースマタンゴ',9,144,13,15,0.15,1);</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -16009,13 +16061,15 @@
       <c r="G29" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="H29" s="10"/>
+      <c r="H29" s="56">
+        <v>0.25</v>
+      </c>
       <c r="I29" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L29" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B29&amp;"'"&amp;","&amp;"'"&amp;C29&amp;"'"&amp;","&amp;VLOOKUP(D29,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E29&amp;","&amp;F29&amp;","&amp;G29&amp;","&amp;H29&amp;","&amp;VLOOKUP(I29,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster024','ニードルバード',10,100,13,16,0.25,3);</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -16040,13 +16094,15 @@
         <f>ROUNDDOWN(G29*1.3,0)</f>
         <v>20</v>
       </c>
-      <c r="H30" s="10"/>
+      <c r="H30" s="56">
+        <v>0.27</v>
+      </c>
       <c r="I30" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L30" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B30&amp;"'"&amp;","&amp;"'"&amp;C30&amp;"'"&amp;","&amp;VLOOKUP(D30,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E30&amp;","&amp;F30&amp;","&amp;G30&amp;","&amp;H30&amp;","&amp;VLOOKUP(I30,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster025','コカトバード',10,120,16,20,0.27,3);</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -16068,13 +16124,15 @@
       <c r="G31" s="10">
         <v>8</v>
       </c>
-      <c r="H31" s="10"/>
+      <c r="H31" s="56">
+        <v>0.08</v>
+      </c>
       <c r="I31" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L31" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B31&amp;"'"&amp;","&amp;"'"&amp;C31&amp;"'"&amp;","&amp;VLOOKUP(D31,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E31&amp;","&amp;F31&amp;","&amp;G31&amp;","&amp;H31&amp;","&amp;VLOOKUP(I31,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster026','プチドラゴン',11,130,13,8,0.08,3);</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -16099,13 +16157,15 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H32" s="10"/>
+      <c r="H32" s="56">
+        <v>0.1</v>
+      </c>
       <c r="I32" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L32" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B32&amp;"'"&amp;","&amp;"'"&amp;C32&amp;"'"&amp;","&amp;VLOOKUP(D32,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E32&amp;","&amp;F32&amp;","&amp;G32&amp;","&amp;H32&amp;","&amp;VLOOKUP(I32,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster027','プチドラゾンビ',11,156,16,10,0.1,5);</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -16130,13 +16190,15 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="H33" s="10"/>
+      <c r="H33" s="56">
+        <v>0.12</v>
+      </c>
       <c r="I33" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L33" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B33&amp;"'"&amp;","&amp;"'"&amp;C33&amp;"'"&amp;","&amp;VLOOKUP(D33,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E33&amp;","&amp;F33&amp;","&amp;G33&amp;","&amp;H33&amp;","&amp;VLOOKUP(I33,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster028','フロストドラゴン',11,187,20,13,0.12,1);</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -16161,13 +16223,15 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="H34" s="10"/>
+      <c r="H34" s="56">
+        <v>0.13</v>
+      </c>
       <c r="I34" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L34" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B34&amp;"'"&amp;","&amp;"'"&amp;C34&amp;"'"&amp;","&amp;VLOOKUP(D34,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E34&amp;","&amp;F34&amp;","&amp;G34&amp;","&amp;H34&amp;","&amp;VLOOKUP(I34,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster029','プチティアマット',11,224,26,16,0.13,6);</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -16189,13 +16253,15 @@
       <c r="G35" s="10">
         <v>16</v>
       </c>
-      <c r="H35" s="10"/>
+      <c r="H35" s="56">
+        <v>0.18</v>
+      </c>
       <c r="I35" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L35" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B35&amp;"'"&amp;","&amp;"'"&amp;C35&amp;"'"&amp;","&amp;VLOOKUP(D35,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E35&amp;","&amp;F35&amp;","&amp;G35&amp;","&amp;H35&amp;","&amp;VLOOKUP(I35,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster030','ポト',12,100,10,16,0.18,6);</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -16220,13 +16286,15 @@
         <f>ROUNDDOWN(G35*1.3,0)</f>
         <v>20</v>
       </c>
-      <c r="H36" s="10"/>
+      <c r="H36" s="56">
+        <v>0.2</v>
+      </c>
       <c r="I36" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L36" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B36&amp;"'"&amp;","&amp;"'"&amp;C36&amp;"'"&amp;","&amp;VLOOKUP(D36,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E36&amp;","&amp;F36&amp;","&amp;G36&amp;","&amp;H36&amp;","&amp;VLOOKUP(I36,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster031','マーマポト',12,120,13,20,0.2,6);</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -16251,13 +16319,15 @@
         <f>ROUNDDOWN(G36*1.3,0)</f>
         <v>26</v>
       </c>
-      <c r="H37" s="10"/>
+      <c r="H37" s="56">
+        <v>0.22</v>
+      </c>
       <c r="I37" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L37" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B37&amp;"'"&amp;","&amp;"'"&amp;C37&amp;"'"&amp;","&amp;VLOOKUP(D37,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E37&amp;","&amp;F37&amp;","&amp;G37&amp;","&amp;H37&amp;","&amp;VLOOKUP(I37,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster032','パーパポト',12,141,16,26,0.22,6);</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -16279,13 +16349,15 @@
       <c r="G38" s="10">
         <v>13</v>
       </c>
-      <c r="H38" s="10"/>
+      <c r="H38" s="56">
+        <v>0.1</v>
+      </c>
       <c r="I38" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L38" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B38&amp;"'"&amp;","&amp;"'"&amp;C38&amp;"'"&amp;","&amp;VLOOKUP(D38,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E38&amp;","&amp;F38&amp;","&amp;G38&amp;","&amp;H38&amp;","&amp;VLOOKUP(I38,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster033','プリースト',13,100,9,13,0.1,6);</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -16310,13 +16382,15 @@
         <f>ROUNDDOWN(G38*1.3,0)</f>
         <v>16</v>
       </c>
-      <c r="H39" s="10"/>
+      <c r="H39" s="56">
+        <v>0.11</v>
+      </c>
       <c r="I39" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L39" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B39&amp;"'"&amp;","&amp;"'"&amp;C39&amp;"'"&amp;","&amp;VLOOKUP(D39,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E39&amp;","&amp;F39&amp;","&amp;G39&amp;","&amp;H39&amp;","&amp;VLOOKUP(I39,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster034','カオスソーサラー',13,120,11,16,0.11,5);</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -16341,13 +16415,15 @@
         <f>ROUNDDOWN(G39*1.3,0)</f>
         <v>20</v>
       </c>
-      <c r="H40" s="10"/>
+      <c r="H40" s="56">
+        <v>0.13</v>
+      </c>
       <c r="I40" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L40" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B40&amp;"'"&amp;","&amp;"'"&amp;C40&amp;"'"&amp;","&amp;VLOOKUP(D40,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E40&amp;","&amp;F40&amp;","&amp;G40&amp;","&amp;H40&amp;","&amp;VLOOKUP(I40,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster035','イビルシャーマン',13,144,14,20,0.13,5);</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -16370,13 +16446,15 @@
       <c r="G41" s="10">
         <v>16</v>
       </c>
-      <c r="H41" s="10"/>
+      <c r="H41" s="56">
+        <v>0.16</v>
+      </c>
       <c r="I41" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L41" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B41&amp;"'"&amp;","&amp;"'"&amp;C41&amp;"'"&amp;","&amp;VLOOKUP(D41,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E41&amp;","&amp;F41&amp;","&amp;G41&amp;","&amp;H41&amp;","&amp;VLOOKUP(I41,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster036','ラビ',14,100,11,16,0.16,6);</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -16401,13 +16479,15 @@
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="H42" s="10"/>
+      <c r="H42" s="56">
+        <v>0.17</v>
+      </c>
       <c r="I42" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L42" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B42&amp;"'"&amp;","&amp;"'"&amp;C42&amp;"'"&amp;","&amp;VLOOKUP(D42,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E42&amp;","&amp;F42&amp;","&amp;G42&amp;","&amp;H42&amp;","&amp;VLOOKUP(I42,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster037','ラビリオン',14,120,14,20,0.17,6);</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -16432,13 +16512,15 @@
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="H43" s="10"/>
+      <c r="H43" s="56">
+        <v>0.18</v>
+      </c>
       <c r="I43" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L43" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B43&amp;"'"&amp;","&amp;"'"&amp;C43&amp;"'"&amp;","&amp;VLOOKUP(D43,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E43&amp;","&amp;F43&amp;","&amp;G43&amp;","&amp;H43&amp;","&amp;VLOOKUP(I43,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster038','キングラビ',14,144,18,26,0.18,6);</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -16463,13 +16545,15 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="H44" s="10"/>
+      <c r="H44" s="56">
+        <v>0.2</v>
+      </c>
       <c r="I44" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L44" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B44&amp;"'"&amp;","&amp;"'"&amp;C44&amp;"'"&amp;","&amp;VLOOKUP(D44,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E44&amp;","&amp;F44&amp;","&amp;G44&amp;","&amp;H44&amp;","&amp;VLOOKUP(I44,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster039','グレートラビ',14,172,23,33,0.2,6);</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -16491,13 +16575,15 @@
       <c r="G45" s="10">
         <v>18</v>
       </c>
-      <c r="H45" s="10"/>
+      <c r="H45" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I45" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L45" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B45&amp;"'"&amp;","&amp;"'"&amp;C45&amp;"'"&amp;","&amp;VLOOKUP(D45,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E45&amp;","&amp;F45&amp;","&amp;G45&amp;","&amp;H45&amp;","&amp;VLOOKUP(I45,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster040','スライム',15,100,10,18,0.15,2);</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -16522,13 +16608,15 @@
         <f>ROUNDDOWN(G45*1.3,0)</f>
         <v>23</v>
       </c>
-      <c r="H46" s="10"/>
+      <c r="H46" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I46" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L46" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B46&amp;"'"&amp;","&amp;"'"&amp;C46&amp;"'"&amp;","&amp;VLOOKUP(D46,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E46&amp;","&amp;F46&amp;","&amp;G46&amp;","&amp;H46&amp;","&amp;VLOOKUP(I46,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster041','ブルーババロア',15,120,13,23,0.15,1);</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -16553,13 +16641,15 @@
         <f>ROUNDDOWN(G46*1.3,0)</f>
         <v>29</v>
       </c>
-      <c r="H47" s="10"/>
+      <c r="H47" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I47" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L47" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B47&amp;"'"&amp;","&amp;"'"&amp;C47&amp;"'"&amp;","&amp;VLOOKUP(D47,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E47&amp;","&amp;F47&amp;","&amp;G47&amp;","&amp;H47&amp;","&amp;VLOOKUP(I47,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster042','レッドマシュマロ',15,141,16,29,0.15,3);</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -16581,13 +16671,15 @@
       <c r="G48" s="10">
         <v>13</v>
       </c>
-      <c r="H48" s="10"/>
+      <c r="H48" s="56">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="I48" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L48" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B48&amp;"'"&amp;","&amp;"'"&amp;C48&amp;"'"&amp;","&amp;VLOOKUP(D48,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E48&amp;","&amp;F48&amp;","&amp;G48&amp;","&amp;H48&amp;","&amp;VLOOKUP(I48,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster043','イビルソード',16,110,15,13,0.14,5);</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -16612,13 +16704,15 @@
         <f>ROUNDDOWN(G48*1.3,0)</f>
         <v>16</v>
       </c>
-      <c r="H49" s="10"/>
+      <c r="H49" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I49" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B49&amp;"'"&amp;","&amp;"'"&amp;C49&amp;"'"&amp;","&amp;VLOOKUP(D49,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E49&amp;","&amp;F49&amp;","&amp;G49&amp;","&amp;H49&amp;","&amp;VLOOKUP(I49,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster044','イビルウェポン',16,132,19,16,0.15,5);</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -16643,13 +16737,15 @@
         <f>ROUNDDOWN(G49*1.3,0)</f>
         <v>20</v>
       </c>
-      <c r="H50" s="10"/>
+      <c r="H50" s="56">
+        <v>0.16</v>
+      </c>
       <c r="I50" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L50" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B50&amp;"'"&amp;","&amp;"'"&amp;C50&amp;"'"&amp;","&amp;VLOOKUP(D50,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E50&amp;","&amp;F50&amp;","&amp;G50&amp;","&amp;H50&amp;","&amp;VLOOKUP(I50,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster045','エレメントソード',16,158,24,20,0.16,6);</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -16671,13 +16767,15 @@
       <c r="G51" s="10">
         <v>19</v>
       </c>
-      <c r="H51" s="10"/>
+      <c r="H51" s="56">
+        <v>0.18</v>
+      </c>
       <c r="I51" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B51&amp;"'"&amp;","&amp;"'"&amp;C51&amp;"'"&amp;","&amp;VLOOKUP(D51,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E51&amp;","&amp;F51&amp;","&amp;G51&amp;","&amp;H51&amp;","&amp;VLOOKUP(I51,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster046','ケルベロス',17,110,11,19,0.18,1);</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -16702,13 +16800,15 @@
         <f>ROUNDDOWN(G51*1.3,0)</f>
         <v>24</v>
       </c>
-      <c r="H52" s="10"/>
+      <c r="H52" s="56">
+        <v>0.2</v>
+      </c>
       <c r="I52" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B52&amp;"'"&amp;","&amp;"'"&amp;C52&amp;"'"&amp;","&amp;VLOOKUP(D52,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E52&amp;","&amp;F52&amp;","&amp;G52&amp;","&amp;H52&amp;","&amp;VLOOKUP(I52,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster047','バウンドウルフ',17,132,14,24,0.2,1);</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -16733,13 +16833,15 @@
         <f>ROUNDDOWN(G52*1.3,0)</f>
         <v>31</v>
       </c>
-      <c r="H53" s="10"/>
+      <c r="H53" s="56">
+        <v>0.21</v>
+      </c>
       <c r="I53" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B53&amp;"'"&amp;","&amp;"'"&amp;C53&amp;"'"&amp;","&amp;VLOOKUP(D53,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E53&amp;","&amp;F53&amp;","&amp;G53&amp;","&amp;H53&amp;","&amp;VLOOKUP(I53,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster048','ジャッカル',17,158,18,31,0.21,1);</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -16761,13 +16863,15 @@
       <c r="G54" s="10">
         <v>14</v>
       </c>
-      <c r="H54" s="10"/>
+      <c r="H54" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I54" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B54&amp;"'"&amp;","&amp;"'"&amp;C54&amp;"'"&amp;","&amp;VLOOKUP(D54,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E54&amp;","&amp;F54&amp;","&amp;G54&amp;","&amp;H54&amp;","&amp;VLOOKUP(I54,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster049','ダックソルジャー',18,120,16,14,0.15,3);</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -16789,13 +16893,15 @@
       <c r="G55" s="10">
         <v>20</v>
       </c>
-      <c r="H55" s="10"/>
+      <c r="H55" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I55" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B55&amp;"'"&amp;","&amp;"'"&amp;C55&amp;"'"&amp;","&amp;VLOOKUP(D55,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E55&amp;","&amp;F55&amp;","&amp;G55&amp;","&amp;H55&amp;","&amp;VLOOKUP(I55,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster050','ダックジェネラル',18,160,24,20,0.15,3);</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -16817,13 +16923,15 @@
       <c r="G56" s="10">
         <v>18</v>
       </c>
-      <c r="H56" s="10"/>
+      <c r="H56" s="56">
+        <v>0.18</v>
+      </c>
       <c r="I56" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B56&amp;"'"&amp;","&amp;"'"&amp;C56&amp;"'"&amp;","&amp;VLOOKUP(D56,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E56&amp;","&amp;F56&amp;","&amp;G56&amp;","&amp;H56&amp;","&amp;VLOOKUP(I56,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster051','モールベア',19,130,14,18,0.18,2);</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -16845,13 +16953,15 @@
       <c r="G57" s="10">
         <v>26</v>
       </c>
-      <c r="H57" s="10"/>
+      <c r="H57" s="56">
+        <v>0.2</v>
+      </c>
       <c r="I57" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B57&amp;"'"&amp;","&amp;"'"&amp;C57&amp;"'"&amp;","&amp;VLOOKUP(D57,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E57&amp;","&amp;F57&amp;","&amp;G57&amp;","&amp;H57&amp;","&amp;VLOOKUP(I57,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster052','ニードリオン',19,170,18,26,0.2,2);</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -16873,13 +16983,15 @@
       <c r="G58" s="10">
         <v>16</v>
       </c>
-      <c r="H58" s="10"/>
+      <c r="H58" s="56">
+        <v>0.2</v>
+      </c>
       <c r="I58" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B58&amp;"'"&amp;","&amp;"'"&amp;C58&amp;"'"&amp;","&amp;VLOOKUP(D58,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E58&amp;","&amp;F58&amp;","&amp;G58&amp;","&amp;H58&amp;","&amp;VLOOKUP(I58,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster053','ギャルビー',20,120,13,16,0.2,4);</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -16904,13 +17016,15 @@
         <f>ROUNDDOWN(G58*1.3,0)</f>
         <v>20</v>
       </c>
-      <c r="H59" s="10"/>
+      <c r="H59" s="56">
+        <v>0.22</v>
+      </c>
       <c r="I59" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B59&amp;"'"&amp;","&amp;"'"&amp;C59&amp;"'"&amp;","&amp;VLOOKUP(D59,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E59&amp;","&amp;F59&amp;","&amp;G59&amp;","&amp;H59&amp;","&amp;VLOOKUP(I59,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster054','レディビー',20,144,16,20,0.22,4);</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -16935,13 +17049,15 @@
         <f>ROUNDDOWN(G59*1.3,0)</f>
         <v>26</v>
       </c>
-      <c r="H60" s="10"/>
+      <c r="H60" s="56">
+        <v>0.23</v>
+      </c>
       <c r="I60" s="10" t="s">
         <v>35</v>
       </c>
       <c r="L60" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,4);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B60&amp;"'"&amp;","&amp;"'"&amp;C60&amp;"'"&amp;","&amp;VLOOKUP(D60,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E60&amp;","&amp;F60&amp;","&amp;G60&amp;","&amp;H60&amp;","&amp;VLOOKUP(I60,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster055','クインビー',20,172,20,26,0.23,4);</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -16963,13 +17079,15 @@
       <c r="G61" s="10">
         <v>16</v>
       </c>
-      <c r="H61" s="10"/>
+      <c r="H61" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I61" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L61" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B61&amp;"'"&amp;","&amp;"'"&amp;C61&amp;"'"&amp;","&amp;VLOOKUP(D61,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E61&amp;","&amp;F61&amp;","&amp;G61&amp;","&amp;H61&amp;","&amp;VLOOKUP(I61,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster056','サハギン',21,130,16,16,0.15,1);</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -16991,13 +17109,15 @@
       <c r="G62" s="10">
         <v>19</v>
       </c>
-      <c r="H62" s="10"/>
+      <c r="H62" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I62" s="10" t="s">
         <v>150</v>
       </c>
       <c r="L62" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,1);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B62&amp;"'"&amp;","&amp;"'"&amp;C62&amp;"'"&amp;","&amp;VLOOKUP(D62,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E62&amp;","&amp;F62&amp;","&amp;G62&amp;","&amp;H62&amp;","&amp;VLOOKUP(I62,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster057','プチポセイドン',21,150,22,19,0.15,1);</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -17019,13 +17139,15 @@
       <c r="G63" s="10">
         <v>11</v>
       </c>
-      <c r="H63" s="10"/>
+      <c r="H63" s="56">
+        <v>0.08</v>
+      </c>
       <c r="I63" s="10" t="s">
         <v>299</v>
       </c>
       <c r="L63" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B63&amp;"'"&amp;","&amp;"'"&amp;C63&amp;"'"&amp;","&amp;VLOOKUP(D63,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E63&amp;","&amp;F63&amp;","&amp;G63&amp;","&amp;H63&amp;","&amp;VLOOKUP(I63,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster058','クロウラー',22,130,15,11,0.08,2);</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -17050,13 +17172,15 @@
         <f>ROUNDDOWN(G63*1.3,0)</f>
         <v>14</v>
       </c>
-      <c r="H64" s="10"/>
+      <c r="H64" s="56">
+        <v>0.09</v>
+      </c>
       <c r="I64" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L64" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B64&amp;"'"&amp;","&amp;"'"&amp;C64&amp;"'"&amp;","&amp;VLOOKUP(D64,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E64&amp;","&amp;F64&amp;","&amp;G64&amp;","&amp;H64&amp;","&amp;VLOOKUP(I64,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster059','メガクロウラー',22,156,19,14,0.09,2);</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -17081,13 +17205,15 @@
         <f>ROUNDDOWN(G64*1.3,0)</f>
         <v>18</v>
       </c>
-      <c r="H65" s="10"/>
+      <c r="H65" s="56">
+        <v>0.1</v>
+      </c>
       <c r="I65" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L65" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B65&amp;"'"&amp;","&amp;"'"&amp;C65&amp;"'"&amp;","&amp;VLOOKUP(D65,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E65&amp;","&amp;F65&amp;","&amp;G65&amp;","&amp;H65&amp;","&amp;VLOOKUP(I65,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster060','ギガクロウラー',22,187,24,18,0.1,2);</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -17109,13 +17235,15 @@
       <c r="G66" s="10">
         <v>10</v>
       </c>
-      <c r="H66" s="10"/>
+      <c r="H66" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I66" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L66" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B66&amp;"'"&amp;","&amp;"'"&amp;C66&amp;"'"&amp;","&amp;VLOOKUP(D66,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E66&amp;","&amp;F66&amp;","&amp;G66&amp;","&amp;H66&amp;","&amp;VLOOKUP(I66,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster061','ぱっくんオタマ',23,110,12,10,0.15,2);</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -17140,13 +17268,15 @@
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
-      <c r="H67" s="10"/>
+      <c r="H67" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I67" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L67" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B67&amp;"'"&amp;","&amp;"'"&amp;C67&amp;"'"&amp;","&amp;VLOOKUP(D67,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E67&amp;","&amp;F67&amp;","&amp;G67&amp;","&amp;H67&amp;","&amp;VLOOKUP(I67,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster062','ぱっくりオタマ',23,132,15,13,0.15,2);</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -17171,13 +17301,15 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="H68" s="10"/>
+      <c r="H68" s="56">
+        <v>0.1</v>
+      </c>
       <c r="I68" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L68" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B68&amp;"'"&amp;","&amp;"'"&amp;C68&amp;"'"&amp;","&amp;VLOOKUP(D68,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E68&amp;","&amp;F68&amp;","&amp;G68&amp;","&amp;H68&amp;","&amp;VLOOKUP(I68,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster063','ぱっくんトカゲ',23,158,19,16,0.1,3);</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -17202,13 +17334,15 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="H69" s="10"/>
+      <c r="H69" s="56">
+        <v>0.11</v>
+      </c>
       <c r="I69" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L69" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B69&amp;"'"&amp;","&amp;"'"&amp;C69&amp;"'"&amp;","&amp;VLOOKUP(D69,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E69&amp;","&amp;F69&amp;","&amp;G69&amp;","&amp;H69&amp;","&amp;VLOOKUP(I69,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster064','ぱっくんドラゴン',23,189,24,20,0.11,3);</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -17230,13 +17364,15 @@
       <c r="G70" s="10">
         <v>17</v>
       </c>
-      <c r="H70" s="10"/>
+      <c r="H70" s="56">
+        <v>0.22</v>
+      </c>
       <c r="I70" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L70" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B70&amp;"'"&amp;","&amp;"'"&amp;C70&amp;"'"&amp;","&amp;VLOOKUP(D70,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E70&amp;","&amp;F70&amp;","&amp;G70&amp;","&amp;H70&amp;","&amp;VLOOKUP(I70,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster065','チビデビル',24,120,13,17,0.22,5);</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -17258,13 +17394,15 @@
       <c r="G71" s="10">
         <v>20</v>
       </c>
-      <c r="H71" s="10"/>
+      <c r="H71" s="56">
+        <v>0.24</v>
+      </c>
       <c r="I71" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L71" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B71&amp;"'"&amp;","&amp;"'"&amp;C71&amp;"'"&amp;","&amp;VLOOKUP(D71,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E71&amp;","&amp;F71&amp;","&amp;G71&amp;","&amp;H71&amp;","&amp;VLOOKUP(I71,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster066','グレムリン',24,160,18,20,0.24,5);</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -17286,13 +17424,15 @@
       <c r="G72" s="10">
         <v>17</v>
       </c>
-      <c r="H72" s="10"/>
+      <c r="H72" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I72" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L72" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B72&amp;"'"&amp;","&amp;"'"&amp;C72&amp;"'"&amp;","&amp;VLOOKUP(D72,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E72&amp;","&amp;F72&amp;","&amp;G72&amp;","&amp;H72&amp;","&amp;VLOOKUP(I72,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster067','オーガボックス',25,140,18,17,0.15,5);</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -17314,13 +17454,15 @@
       <c r="G73" s="10">
         <v>20</v>
       </c>
-      <c r="H73" s="10"/>
+      <c r="H73" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I73" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L73" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B73&amp;"'"&amp;","&amp;"'"&amp;C73&amp;"'"&amp;","&amp;VLOOKUP(D73,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E73&amp;","&amp;F73&amp;","&amp;G73&amp;","&amp;H73&amp;","&amp;VLOOKUP(I73,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster068','カイザーミミック',25,170,23,20,0.15,5);</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -17342,13 +17484,15 @@
       <c r="G74" s="10">
         <v>12</v>
       </c>
-      <c r="H74" s="10"/>
+      <c r="H74" s="56">
+        <v>0.05</v>
+      </c>
       <c r="I74" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L74" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B74&amp;"'"&amp;","&amp;"'"&amp;C74&amp;"'"&amp;","&amp;VLOOKUP(D74,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E74&amp;","&amp;F74&amp;","&amp;G74&amp;","&amp;H74&amp;","&amp;VLOOKUP(I74,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster069','バレッテ',26,140,15,12,0.05,3);</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -17370,13 +17514,15 @@
       <c r="G75" s="10">
         <v>14</v>
       </c>
-      <c r="H75" s="10"/>
+      <c r="H75" s="56">
+        <v>0.05</v>
+      </c>
       <c r="I75" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L75" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B75&amp;"'"&amp;","&amp;"'"&amp;C75&amp;"'"&amp;","&amp;VLOOKUP(D75,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E75&amp;","&amp;F75&amp;","&amp;G75&amp;","&amp;H75&amp;","&amp;VLOOKUP(I75,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster070','ゴールドバレッテ',26,180,19,14,0.05,3);</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -17398,13 +17544,15 @@
       <c r="G76" s="10">
         <v>15</v>
       </c>
-      <c r="H76" s="10"/>
+      <c r="H76" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I76" s="10" t="s">
         <v>34</v>
       </c>
       <c r="L76" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,2);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B76&amp;"'"&amp;","&amp;"'"&amp;C76&amp;"'"&amp;","&amp;VLOOKUP(D76,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E76&amp;","&amp;F76&amp;","&amp;G76&amp;","&amp;H76&amp;","&amp;VLOOKUP(I76,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster071','バシリスク',27,110,12,15,0.15,2);</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -17426,13 +17574,15 @@
       <c r="G77" s="10">
         <v>22</v>
       </c>
-      <c r="H77" s="10"/>
+      <c r="H77" s="56">
+        <v>0.18</v>
+      </c>
       <c r="I77" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L77" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B77&amp;"'"&amp;","&amp;"'"&amp;C77&amp;"'"&amp;","&amp;VLOOKUP(D77,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E77&amp;","&amp;F77&amp;","&amp;G77&amp;","&amp;H77&amp;","&amp;VLOOKUP(I77,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster072','ファイアドレイク',27,150,18,22,0.18,3);</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -17454,13 +17604,15 @@
       <c r="G78" s="10">
         <v>17</v>
       </c>
-      <c r="H78" s="10"/>
+      <c r="H78" s="56">
+        <v>0.2</v>
+      </c>
       <c r="I78" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L78" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B78&amp;"'"&amp;","&amp;"'"&amp;C78&amp;"'"&amp;","&amp;VLOOKUP(D78,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E78&amp;","&amp;F78&amp;","&amp;G78&amp;","&amp;H78&amp;","&amp;VLOOKUP(I78,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster073','スペクター',28,130,13,17,0.2,5);</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -17482,13 +17634,15 @@
       <c r="G79" s="10">
         <v>20</v>
       </c>
-      <c r="H79" s="10"/>
+      <c r="H79" s="56">
+        <v>0.21</v>
+      </c>
       <c r="I79" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L79" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B79&amp;"'"&amp;","&amp;"'"&amp;C79&amp;"'"&amp;","&amp;VLOOKUP(D79,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E79&amp;","&amp;F79&amp;","&amp;G79&amp;","&amp;H79&amp;","&amp;VLOOKUP(I79,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster074','ゴースト',28,160,17,20,0.21,5);</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -17510,13 +17664,15 @@
       <c r="G80" s="10">
         <v>14</v>
       </c>
-      <c r="H80" s="10"/>
+      <c r="H80" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I80" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L80" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B80&amp;"'"&amp;","&amp;"'"&amp;C80&amp;"'"&amp;","&amp;VLOOKUP(D80,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E80&amp;","&amp;F80&amp;","&amp;G80&amp;","&amp;H80&amp;","&amp;VLOOKUP(I80,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster075','ユニコーンヘッド',29,120,15,14,0.15,6);</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -17538,13 +17694,15 @@
       <c r="G81" s="10">
         <v>25</v>
       </c>
-      <c r="H81" s="10"/>
+      <c r="H81" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I81" s="10" t="s">
         <v>37</v>
       </c>
       <c r="L81" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,6);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B81&amp;"'"&amp;","&amp;"'"&amp;C81&amp;"'"&amp;","&amp;VLOOKUP(D81,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E81&amp;","&amp;F81&amp;","&amp;G81&amp;","&amp;H81&amp;","&amp;VLOOKUP(I81,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster076','ゴールドユニコ',29,170,22,25,0.15,6);</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -17566,13 +17724,15 @@
       <c r="G82" s="10">
         <v>14</v>
       </c>
-      <c r="H82" s="10"/>
+      <c r="H82" s="56">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="I82" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L82" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B82&amp;"'"&amp;","&amp;"'"&amp;C82&amp;"'"&amp;","&amp;VLOOKUP(D82,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E82&amp;","&amp;F82&amp;","&amp;G82&amp;","&amp;H82&amp;","&amp;VLOOKUP(I82,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster077','シェイプシフター',30,130,12,14,0.14,5);</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -17596,13 +17756,15 @@
         <f>ROUNDDOWN(G82*1.3,0)</f>
         <v>18</v>
       </c>
-      <c r="H83" s="10"/>
+      <c r="H83" s="56">
+        <v>0.15</v>
+      </c>
       <c r="I83" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L83" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B83&amp;"'"&amp;","&amp;"'"&amp;C83&amp;"'"&amp;","&amp;VLOOKUP(D83,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E83&amp;","&amp;F83&amp;","&amp;G83&amp;","&amp;H83&amp;","&amp;VLOOKUP(I83,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster078','シャドウゼロ',30,170,15,18,0.15,5);</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -17626,13 +17788,15 @@
         <f>ROUNDDOWN(G83*1.3,0)</f>
         <v>23</v>
       </c>
-      <c r="H84" s="10"/>
+      <c r="H84" s="56">
+        <v>0.16</v>
+      </c>
       <c r="I84" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L84" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B84&amp;"'"&amp;","&amp;"'"&amp;C84&amp;"'"&amp;","&amp;VLOOKUP(D84,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E84&amp;","&amp;F84&amp;","&amp;G84&amp;","&amp;H84&amp;","&amp;VLOOKUP(I84,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster079','シャドウゼロワン',30,190,19,23,0.16,5);</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -17654,13 +17818,15 @@
       <c r="G85" s="10">
         <v>14</v>
       </c>
-      <c r="H85" s="10"/>
+      <c r="H85" s="56">
+        <v>0.25</v>
+      </c>
       <c r="I85" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L85" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B85&amp;"'"&amp;","&amp;"'"&amp;C85&amp;"'"&amp;","&amp;VLOOKUP(D85,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E85&amp;","&amp;F85&amp;","&amp;G85&amp;","&amp;H85&amp;","&amp;VLOOKUP(I85,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster080','ボルダー',31,120,13,14,0.25,5);</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -17685,13 +17851,15 @@
         <f>ROUNDDOWN(G85*1.3,0)</f>
         <v>18</v>
       </c>
-      <c r="H86" s="10"/>
+      <c r="H86" s="56">
+        <v>0.25</v>
+      </c>
       <c r="I86" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L86" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B86&amp;"'"&amp;","&amp;"'"&amp;C86&amp;"'"&amp;","&amp;VLOOKUP(D86,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E86&amp;","&amp;F86&amp;","&amp;G86&amp;","&amp;H86&amp;","&amp;VLOOKUP(I86,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster081','パワーボルダー',31,144,16,18,0.25,5);</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -17716,13 +17884,15 @@
         <f>ROUNDDOWN(G86*1.3,0)</f>
         <v>23</v>
       </c>
-      <c r="H87" s="10"/>
+      <c r="H87" s="56">
+        <v>0.25</v>
+      </c>
       <c r="I87" s="10" t="s">
         <v>36</v>
       </c>
       <c r="L87" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,5);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B87&amp;"'"&amp;","&amp;"'"&amp;C87&amp;"'"&amp;","&amp;VLOOKUP(D87,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E87&amp;","&amp;F87&amp;","&amp;G87&amp;","&amp;H87&amp;","&amp;VLOOKUP(I87,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster082','デスボルダー',31,172,20,23,0.25,5);</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -17744,13 +17914,15 @@
       <c r="G88" s="10">
         <v>12</v>
       </c>
-      <c r="H88" s="10"/>
+      <c r="H88" s="56">
+        <v>0.18</v>
+      </c>
       <c r="I88" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L88" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B88&amp;"'"&amp;","&amp;"'"&amp;C88&amp;"'"&amp;","&amp;VLOOKUP(D88,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E88&amp;","&amp;F88&amp;","&amp;G88&amp;","&amp;H88&amp;","&amp;VLOOKUP(I88,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster083','パンプキンボム',32,130,17,12,0.18,3);</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -17772,20 +17944,22 @@
       <c r="G89" s="10">
         <v>15</v>
       </c>
-      <c r="H89" s="10"/>
+      <c r="H89" s="56">
+        <v>0.2</v>
+      </c>
       <c r="I89" s="10" t="s">
         <v>151</v>
       </c>
       <c r="L89" s="5" t="str">
-        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
-        <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,3);</v>
+        <f>"INSERT INTO m_monster VALUES ("&amp;"'"&amp;B89&amp;"'"&amp;","&amp;"'"&amp;C89&amp;"'"&amp;","&amp;VLOOKUP(D89,コード!$C$48:$I$101,3,FALSE)&amp;","&amp;E89&amp;","&amp;F89&amp;","&amp;G89&amp;","&amp;H89&amp;","&amp;VLOOKUP(I89,コード!$C$5:$I$11,3,FALSE)&amp;");"</f>
+        <v>INSERT INTO m_monster VALUES ('monster084','グレネードボム',32,160,24,15,0.2,3);</v>
       </c>
     </row>
     <row r="90" spans="2:12">
       <c r="E90" s="27"/>
       <c r="F90" s="27"/>
       <c r="G90" s="27"/>
-      <c r="H90" s="27"/>
+      <c r="H90" s="57"/>
       <c r="I90" s="27"/>
     </row>
     <row r="91" spans="2:12">

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC50D5E5-EABF-470A-98CD-1399AB41B761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C062C0-70C7-42AD-94F5-E3E527D16843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="1184">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -5483,6 +5483,30 @@
   </si>
   <si>
     <t>dodge</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill050</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill051</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>0.35</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill053</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>skill043</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9832,14 +9856,14 @@
         <v>132</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>1151</v>
+        <v>1178</v>
       </c>
       <c r="I17" s="19" t="s">
         <v>1153</v>
       </c>
       <c r="K17" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>INSERT INTO m_code VALUES ('code002',4,'スロー','遅','',0,0.5,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
+        <v>INSERT INTO m_code VALUES ('code002',4,'スロー','遅','',0,0.3,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
     <row r="18" spans="2:11">
@@ -9890,14 +9914,14 @@
         <v>132</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>1152</v>
+        <v>1181</v>
       </c>
       <c r="I19" s="19" t="s">
         <v>1153</v>
       </c>
       <c r="K19" s="5" t="str">
         <f t="shared" si="2"/>
-        <v>INSERT INTO m_code VALUES ('code002',6,'回避力UP','回↑','',0,0.2,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
+        <v>INSERT INTO m_code VALUES ('code002',6,'回避力UP','回↑','',0,0.35,'param3: 解除確立　0.0 → 0%, 1.0 → 100%');</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -18126,7 +18150,7 @@
       </c>
       <c r="M5" s="21">
         <f>COUNTIF($D$5:$D$1000,K5)</f>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N5" s="45"/>
       <c r="O5" s="1" t="str">
@@ -18168,7 +18192,7 @@
       </c>
       <c r="M6" s="21">
         <f t="shared" ref="M6:M69" si="0">COUNTIF($D$5:$D$1000,K6)</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N6" s="45"/>
       <c r="O6" s="1" t="str">
@@ -18462,7 +18486,7 @@
       </c>
       <c r="M13" s="21">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N13" s="45"/>
       <c r="O13" s="1" t="str">
@@ -18924,7 +18948,7 @@
       </c>
       <c r="M24" s="21">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N24" s="45"/>
       <c r="O24" s="1" t="str">
@@ -19428,7 +19452,7 @@
       </c>
       <c r="M36" s="21">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N36" s="45"/>
       <c r="O36" s="1" t="str">
@@ -19890,7 +19914,7 @@
       </c>
       <c r="M47" s="21">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N47" s="45"/>
       <c r="O47" s="1" t="str">
@@ -20184,7 +20208,7 @@
       </c>
       <c r="M54" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N54" s="45"/>
       <c r="O54" s="1" t="str">
@@ -20226,7 +20250,7 @@
       </c>
       <c r="M55" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N55" s="45"/>
       <c r="O55" s="1" t="str">
@@ -20310,7 +20334,7 @@
       </c>
       <c r="M57" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N57" s="45"/>
       <c r="O57" s="1" t="str">
@@ -20352,7 +20376,7 @@
       </c>
       <c r="M58" s="21">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N58" s="45"/>
       <c r="O58" s="1" t="str">
@@ -20394,7 +20418,7 @@
       </c>
       <c r="M59" s="21">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N59" s="45"/>
       <c r="O59" s="1" t="str">
@@ -20436,7 +20460,7 @@
       </c>
       <c r="M60" s="21">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N60" s="45"/>
       <c r="O60" s="1" t="str">
@@ -20520,7 +20544,7 @@
       </c>
       <c r="M62" s="21">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N62" s="45"/>
       <c r="O62" s="1" t="str">
@@ -20856,7 +20880,7 @@
       </c>
       <c r="M70" s="21">
         <f t="shared" ref="M70:M86" si="2">COUNTIF($D$5:$D$1000,K70)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70" s="45"/>
       <c r="O70" s="1" t="str">
@@ -21823,7 +21847,7 @@
         <v>436</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>1017</v>
+        <v>1179</v>
       </c>
       <c r="E96" s="21" t="b">
         <v>0</v>
@@ -21834,16 +21858,16 @@
       </c>
       <c r="H96" s="24">
         <f>VLOOKUP(D96,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I96" s="25" t="str">
         <f>VLOOKUP(D96,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>斬撃</v>
+        <v>スロウ</v>
       </c>
       <c r="N96" s="45"/>
       <c r="O96" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0092','monster016','skill009',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0092','monster016','skill050',FALSE);</v>
       </c>
     </row>
     <row r="97" spans="2:15">
@@ -22691,7 +22715,7 @@
         <v>440</v>
       </c>
       <c r="D124" s="21" t="s">
-        <v>1023</v>
+        <v>1179</v>
       </c>
       <c r="E124" s="21" t="b">
         <v>0</v>
@@ -22706,12 +22730,12 @@
       </c>
       <c r="I124" s="25" t="str">
         <f>VLOOKUP(D124,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>様子を見ている</v>
+        <v>スロウ</v>
       </c>
       <c r="N124" s="45"/>
       <c r="O124" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0120','monster020','skill056',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0120','monster020','skill050',FALSE);</v>
       </c>
     </row>
     <row r="125" spans="2:15">
@@ -22846,7 +22870,7 @@
         <v>441</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>1023</v>
+        <v>1180</v>
       </c>
       <c r="E129" s="21" t="b">
         <v>0</v>
@@ -22861,12 +22885,12 @@
       </c>
       <c r="I129" s="25" t="str">
         <f>VLOOKUP(D129,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>様子を見ている</v>
+        <v>スロウガ</v>
       </c>
       <c r="N129" s="45"/>
       <c r="O129" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0125','monster021','skill056',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0125','monster021','skill051',FALSE);</v>
       </c>
     </row>
     <row r="130" spans="2:15">
@@ -24055,7 +24079,7 @@
         <v>448</v>
       </c>
       <c r="D168" s="21" t="s">
-        <v>1042</v>
+        <v>1180</v>
       </c>
       <c r="E168" s="21" t="b">
         <v>0</v>
@@ -24066,16 +24090,16 @@
       </c>
       <c r="H168" s="24">
         <f>VLOOKUP(D168,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I168" s="25" t="str">
         <f>VLOOKUP(D168,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>正拳突き</v>
+        <v>スロウガ</v>
       </c>
       <c r="N168" s="45"/>
       <c r="O168" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0164','monster028','skill002',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0164','monster028','skill051',FALSE);</v>
       </c>
     </row>
     <row r="169" spans="2:15">
@@ -25016,7 +25040,7 @@
         <v>453</v>
       </c>
       <c r="D199" s="21" t="s">
-        <v>1033</v>
+        <v>1183</v>
       </c>
       <c r="E199" s="21" t="b">
         <v>0</v>
@@ -25027,16 +25051,16 @@
       </c>
       <c r="H199" s="24" t="str">
         <f>VLOOKUP(D199,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I199" s="25" t="str">
         <f>VLOOKUP(D199,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>イビルゲート</v>
+        <v>リジェネ</v>
       </c>
       <c r="N199" s="45"/>
       <c r="O199" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0195','monster033','skill032',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0195','monster033','skill043',FALSE);</v>
       </c>
     </row>
     <row r="200" spans="2:15">
@@ -25791,7 +25815,7 @@
         <v>457</v>
       </c>
       <c r="D224" s="21" t="s">
-        <v>1041</v>
+        <v>1183</v>
       </c>
       <c r="E224" s="21" t="b">
         <v>0</v>
@@ -25800,18 +25824,18 @@
         <f>VLOOKUP(C224,モンスター!$B$6:$I$100,2,FALSE)</f>
         <v>ラビリオン</v>
       </c>
-      <c r="H224" s="24">
+      <c r="H224" s="24" t="str">
         <f>VLOOKUP(D224,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I224" s="25" t="str">
         <f>VLOOKUP(D224,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>打撃</v>
+        <v>リジェネ</v>
       </c>
       <c r="N224" s="45"/>
       <c r="O224" s="1" t="str">
         <f t="shared" si="5"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0220','monster037','skill001',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0220','monster037','skill043',FALSE);</v>
       </c>
     </row>
     <row r="225" spans="2:15">
@@ -27527,7 +27551,7 @@
         <v>466</v>
       </c>
       <c r="D280" s="21" t="s">
-        <v>1069</v>
+        <v>1182</v>
       </c>
       <c r="E280" s="21" t="b">
         <v>0</v>
@@ -27538,16 +27562,16 @@
       </c>
       <c r="H280" s="24">
         <f>VLOOKUP(D280,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I280" s="25" t="str">
         <f>VLOOKUP(D280,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>噛みつき</v>
+        <v>ビジョン</v>
       </c>
       <c r="N280" s="45"/>
       <c r="O280" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0276','monster046','skill058',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0276','monster046','skill053',FALSE);</v>
       </c>
     </row>
     <row r="281" spans="2:15">
@@ -27620,7 +27644,7 @@
         <v>467</v>
       </c>
       <c r="D283" s="21" t="s">
-        <v>1071</v>
+        <v>1182</v>
       </c>
       <c r="E283" s="21" t="b">
         <v>0</v>
@@ -27631,16 +27655,16 @@
       </c>
       <c r="H283" s="24">
         <f>VLOOKUP(D283,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I283" s="25" t="str">
         <f>VLOOKUP(D283,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>叩きつけ</v>
+        <v>ビジョン</v>
       </c>
       <c r="N283" s="45"/>
       <c r="O283" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0279','monster047','skill066',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0279','monster047','skill053',FALSE);</v>
       </c>
     </row>
     <row r="284" spans="2:15">
@@ -27837,7 +27861,7 @@
         <v>468</v>
       </c>
       <c r="D290" s="21" t="s">
-        <v>1172</v>
+        <v>1182</v>
       </c>
       <c r="E290" s="21" t="b">
         <v>0</v>
@@ -27852,12 +27876,12 @@
       </c>
       <c r="I290" s="25" t="str">
         <f>VLOOKUP(D290,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>エナジーボール</v>
+        <v>ビジョン</v>
       </c>
       <c r="N290" s="45"/>
       <c r="O290" s="1" t="str">
         <f t="shared" si="6"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0286','monster048','skill054',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0286','monster048','skill053',FALSE);</v>
       </c>
     </row>
     <row r="291" spans="2:15">
@@ -29263,7 +29287,7 @@
         <v>476</v>
       </c>
       <c r="D336" s="21" t="s">
-        <v>1028</v>
+        <v>1179</v>
       </c>
       <c r="E336" s="21" t="b">
         <v>0</v>
@@ -29272,18 +29296,18 @@
         <f>VLOOKUP(C336,モンスター!$B$6:$I$100,2,FALSE)</f>
         <v>サハギン</v>
       </c>
-      <c r="H336" s="24" t="str">
+      <c r="H336" s="24">
         <f>VLOOKUP(D336,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I336" s="25" t="str">
         <f>VLOOKUP(D336,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>アイススマッシュ</v>
+        <v>スロウ</v>
       </c>
       <c r="N336" s="45"/>
       <c r="O336" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0332','monster056','skill020',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0332','monster056','skill050',FALSE);</v>
       </c>
     </row>
     <row r="337" spans="2:15">
@@ -29542,7 +29566,7 @@
         <v>477</v>
       </c>
       <c r="D345" s="21" t="s">
-        <v>1017</v>
+        <v>1180</v>
       </c>
       <c r="E345" s="21" t="b">
         <v>0</v>
@@ -29553,16 +29577,16 @@
       </c>
       <c r="H345" s="24">
         <f>VLOOKUP(D345,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I345" s="25" t="str">
         <f>VLOOKUP(D345,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>斬撃</v>
+        <v>スロウガ</v>
       </c>
       <c r="N345" s="45"/>
       <c r="O345" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0341','monster057','skill009',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0341','monster057','skill051',FALSE);</v>
       </c>
     </row>
     <row r="346" spans="2:15">
@@ -33200,7 +33224,7 @@
         <v>497</v>
       </c>
       <c r="D463" s="21" t="s">
-        <v>1042</v>
+        <v>1182</v>
       </c>
       <c r="E463" s="21" t="b">
         <v>0</v>
@@ -33211,16 +33235,16 @@
       </c>
       <c r="H463" s="24">
         <f>VLOOKUP(D463,スキル!$C$4:$O$96,8,FALSE)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I463" s="25" t="str">
         <f>VLOOKUP(D463,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>正拳突き</v>
+        <v>ビジョン</v>
       </c>
       <c r="N463" s="45"/>
       <c r="O463" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0459','monster077','skill002',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0459','monster077','skill053',FALSE);</v>
       </c>
     </row>
     <row r="464" spans="2:15">
@@ -33479,7 +33503,7 @@
         <v>498</v>
       </c>
       <c r="D472" s="21" t="s">
-        <v>1023</v>
+        <v>1182</v>
       </c>
       <c r="E472" s="21" t="b">
         <v>0</v>
@@ -33494,12 +33518,12 @@
       </c>
       <c r="I472" s="25" t="str">
         <f>VLOOKUP(D472,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>様子を見ている</v>
+        <v>ビジョン</v>
       </c>
       <c r="N472" s="45"/>
       <c r="O472" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0468','monster078','skill056',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0468','monster078','skill053',FALSE);</v>
       </c>
     </row>
     <row r="473" spans="2:15">
@@ -33696,7 +33720,7 @@
         <v>499</v>
       </c>
       <c r="D479" s="21" t="s">
-        <v>1023</v>
+        <v>1182</v>
       </c>
       <c r="E479" s="21" t="b">
         <v>0</v>
@@ -33711,12 +33735,12 @@
       </c>
       <c r="I479" s="25" t="str">
         <f>VLOOKUP(D479,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>様子を見ている</v>
+        <v>ビジョン</v>
       </c>
       <c r="N479" s="45"/>
       <c r="O479" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0475','monster079','skill056',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0475','monster079','skill053',FALSE);</v>
       </c>
     </row>
     <row r="480" spans="2:15">
@@ -34440,7 +34464,7 @@
         <v>503</v>
       </c>
       <c r="D503" s="21" t="s">
-        <v>1018</v>
+        <v>1179</v>
       </c>
       <c r="E503" s="21" t="b">
         <v>0</v>
@@ -34455,12 +34479,12 @@
       </c>
       <c r="I503" s="25" t="str">
         <f>VLOOKUP(D503,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>ミスをした</v>
+        <v>スロウ</v>
       </c>
       <c r="N503" s="45"/>
       <c r="O503" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0499','monster083','skill055',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0499','monster083','skill050',FALSE);</v>
       </c>
     </row>
     <row r="504" spans="1:21">
@@ -34626,7 +34650,7 @@
         <v>504</v>
       </c>
       <c r="D509" s="21" t="s">
-        <v>1018</v>
+        <v>1180</v>
       </c>
       <c r="E509" s="21" t="b">
         <v>0</v>
@@ -34641,12 +34665,12 @@
       </c>
       <c r="I509" s="25" t="str">
         <f>VLOOKUP(D509,スキル!$C$4:$O$96,2,FALSE)</f>
-        <v>ミスをした</v>
+        <v>スロウガ</v>
       </c>
       <c r="N509" s="45"/>
       <c r="O509" s="1" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill055',FALSE);</v>
+        <v>INSERT INTO m_monster_skills VALUES ('myskill0505','monster084','skill051',FALSE);</v>
       </c>
     </row>
     <row r="510" spans="1:21" ht="18.75">

--- a/KazApp_document/設計書.xlsx
+++ b/KazApp_document/設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repository_kaz_app\kaz_app\KazApp_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C062C0-70C7-42AD-94F5-E3E527D16843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8617C696-6E45-48B9-9070-EC7A1C7AF4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{23010AEC-8D3D-48D3-938D-B3932852B25B}"/>
   </bookViews>
   <sheets>
     <sheet name="オブジェクト" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="1184">
   <si>
     <t>状態異常</t>
     <rPh sb="0" eb="2">
@@ -9468,7 +9468,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B38E66FE-6CF0-4EAE-97A5-1587F7EEF1C8}">
-  <dimension ref="B3:P97"/>
+  <dimension ref="B3:P98"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -11801,9 +11801,14 @@
         <v>INSERT INTO m_code VALUES ('code008',3,'使用モンスター','','',0,0.0,'');</v>
       </c>
     </row>
-    <row r="97" spans="16:16">
+    <row r="97" spans="11:16">
       <c r="P97" s="5">
         <v>444</v>
+      </c>
+    </row>
+    <row r="98" spans="11:16">
+      <c r="K98" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
